--- a/Buying List + BOM V2.xlsx
+++ b/Buying List + BOM V2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\angel\Desktop\Proyectos\FOC_BLDC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9774C82E-4424-4BD0-82A4-C183DC45129F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2233622B-394C-47EF-B610-6B4DE2A24993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Components" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="164">
   <si>
     <t>Component</t>
   </si>
@@ -520,6 +520,15 @@
   </si>
   <si>
     <t>M5 Thread Rod Joint End</t>
+  </si>
+  <si>
+    <t>5.1k</t>
+  </si>
+  <si>
+    <t>Can be changed by 0805 50V</t>
+  </si>
+  <si>
+    <t>More than 16</t>
   </si>
 </sst>
 </file>
@@ -883,7 +892,37 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="36">
+  <dxfs count="37">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF92D050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -891,6 +930,20 @@
         <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -924,6 +977,29 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -978,6 +1054,34 @@
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -999,12 +1103,70 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1077,6 +1239,53 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     </dxf>
     <dxf>
@@ -1086,6 +1295,20 @@
         <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -1122,232 +1345,6 @@
         <top/>
         <bottom/>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF92D050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <vertical/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <vertical/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -1420,6 +1417,28 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1434,48 +1453,48 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{57113999-89B8-4DCA-AAEB-0496B38A0B13}" name="Table1" displayName="Table1" ref="A1:K30" totalsRowCount="1" headerRowDxfId="35" dataDxfId="33" headerRowBorderDxfId="34" tableBorderDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{57113999-89B8-4DCA-AAEB-0496B38A0B13}" name="Table1" displayName="Table1" ref="A1:K30" totalsRowCount="1" headerRowDxfId="29" dataDxfId="27" headerRowBorderDxfId="28" tableBorderDxfId="26">
   <autoFilter ref="A1:K29" xr:uid="{57113999-89B8-4DCA-AAEB-0496B38A0B13}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{C01A5BB4-2776-4DA4-B397-20536FB6B151}" name="Component" dataDxfId="31" totalsRowDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{D16A6BB5-FB54-4A08-8F36-6F894F571CA2}" name="Supplier" dataDxfId="30" totalsRowDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{13E6D449-D029-4B98-A474-567EF4C137DD}" name="Unit Price" dataDxfId="29" totalsRowDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{BFC6BC80-26FB-482F-B354-EBAC0B59B079}" name="Quantity / Board" dataDxfId="28" totalsRowDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{60AEBA47-4243-42D3-988F-F3DB3204B15E}" name="Total Quantity 6 + 2" dataDxfId="27" totalsRowDxfId="6"/>
-    <tableColumn id="12" xr3:uid="{4B5F8A5D-14B9-498E-9411-2EEB2C426CA5}" name="Left to Purchase" dataDxfId="26" totalsRowDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{E17DAC7E-1E39-4AF4-8109-E85C3BEA4D94}" name="Shipping Costs" dataDxfId="25" totalsRowDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{80648434-14FA-49B4-BA1C-C16B6DFD9A61}" name="Purchased" dataDxfId="24" totalsRowDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{2A4D153E-2215-40C4-B217-8FADF5785568}" name="Arrived" dataDxfId="23" totalsRowDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{9BE18441-967B-45FF-8A88-16AF220F7381}" name="Total" totalsRowFunction="custom" dataDxfId="22" totalsRowDxfId="1">
+    <tableColumn id="1" xr3:uid="{C01A5BB4-2776-4DA4-B397-20536FB6B151}" name="Component" dataDxfId="25" totalsRowDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{D16A6BB5-FB54-4A08-8F36-6F894F571CA2}" name="Supplier" dataDxfId="23" totalsRowDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{13E6D449-D029-4B98-A474-567EF4C137DD}" name="Unit Price" dataDxfId="21" totalsRowDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{BFC6BC80-26FB-482F-B354-EBAC0B59B079}" name="Quantity / Board" dataDxfId="19" totalsRowDxfId="18"/>
+    <tableColumn id="8" xr3:uid="{60AEBA47-4243-42D3-988F-F3DB3204B15E}" name="Total Quantity 6 + 2" dataDxfId="17" totalsRowDxfId="16"/>
+    <tableColumn id="12" xr3:uid="{4B5F8A5D-14B9-498E-9411-2EEB2C426CA5}" name="Left to Purchase" dataDxfId="15" totalsRowDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{E17DAC7E-1E39-4AF4-8109-E85C3BEA4D94}" name="Shipping Costs" dataDxfId="13" totalsRowDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{80648434-14FA-49B4-BA1C-C16B6DFD9A61}" name="Purchased" dataDxfId="11" totalsRowDxfId="10"/>
+    <tableColumn id="9" xr3:uid="{2A4D153E-2215-40C4-B217-8FADF5785568}" name="Arrived" dataDxfId="9" totalsRowDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{9BE18441-967B-45FF-8A88-16AF220F7381}" name="Total" totalsRowFunction="custom" dataDxfId="7" totalsRowDxfId="6">
       <calculatedColumnFormula>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(Table1[Total])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{B8F06C12-DD71-45A3-886F-8113BE8A9BDA}" name="Link" dataDxfId="21" totalsRowDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{B8F06C12-DD71-45A3-886F-8113BE8A9BDA}" name="Link" dataDxfId="5" totalsRowDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{22595191-1704-4DAD-B045-FA2F04CF59FF}" name="Table2" displayName="Table2" ref="A1:I97" totalsRowShown="0">
-  <autoFilter ref="A1:I97" xr:uid="{22595191-1704-4DAD-B045-FA2F04CF59FF}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I97">
-    <sortCondition ref="B1:B97"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{22595191-1704-4DAD-B045-FA2F04CF59FF}" name="Table2" displayName="Table2" ref="A1:I98" totalsRowShown="0">
+  <autoFilter ref="A1:I98" xr:uid="{22595191-1704-4DAD-B045-FA2F04CF59FF}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I98">
+    <sortCondition ref="B1:B98"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{573F2863-704A-459C-9EBD-42757DB1F58F}" name="Id" dataDxfId="20">
+    <tableColumn id="1" xr3:uid="{573F2863-704A-459C-9EBD-42757DB1F58F}" name="Id" dataDxfId="36">
       <calculatedColumnFormula>ROW(Table2[[#This Row],[Footprint]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{94458B27-EAA7-4644-96D5-025617151FB9}" name="Footprint" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{E80410E2-6881-4DFC-8748-8A0D261433F2}" name="Quantity" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{1CA2020F-6B3F-4E8B-8012-03FDA5CF807D}" name="Designation" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{C119C6F9-CB21-43A0-B289-A2AD9A4E4274}" name="Voltage comp" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{07CA118E-230B-4E63-B486-A70F92B6979D}" name="Voltage requirements" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{94458B27-EAA7-4644-96D5-025617151FB9}" name="Footprint" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{E80410E2-6881-4DFC-8748-8A0D261433F2}" name="Quantity" dataDxfId="34"/>
+    <tableColumn id="4" xr3:uid="{1CA2020F-6B3F-4E8B-8012-03FDA5CF807D}" name="Designation" dataDxfId="33"/>
+    <tableColumn id="10" xr3:uid="{C119C6F9-CB21-43A0-B289-A2AD9A4E4274}" name="Voltage comp" dataDxfId="32"/>
+    <tableColumn id="9" xr3:uid="{07CA118E-230B-4E63-B486-A70F92B6979D}" name="Voltage requirements" dataDxfId="31"/>
     <tableColumn id="5" xr3:uid="{37D2A461-BCEF-4038-BCE9-6676ADE9155B}" name="Total">
       <calculatedColumnFormula>Table2[[#This Row],[Quantity]]*$M$3</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{4C6DF7CF-2E5F-4ECA-A520-C9BDA8B38EA1}" name="Personal Stock"/>
-    <tableColumn id="7" xr3:uid="{0BE67764-592A-43FD-8413-C7CDBA42BEAE}" name="BUY / HIVE" dataDxfId="14">
+    <tableColumn id="7" xr3:uid="{0BE67764-592A-43FD-8413-C7CDBA42BEAE}" name="BUY / HIVE" dataDxfId="30">
       <calculatedColumnFormula>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2688,12 +2707,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F30">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:I30">
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2709,7 +2728,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24286835-DDBE-4844-A8EA-1CAF4B158E48}">
-  <dimension ref="A1:M97"/>
+  <dimension ref="A1:M98"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.109375" style="32" customWidth="1"/>
@@ -2953,7 +2972,7 @@
         <v>8</v>
       </c>
       <c r="H8">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I8" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
@@ -3005,7 +3024,7 @@
         <v>72</v>
       </c>
       <c r="H10">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="I10" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
@@ -3057,7 +3076,7 @@
         <v>32</v>
       </c>
       <c r="H12">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="I12" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
@@ -3099,17 +3118,17 @@
         <v>123</v>
       </c>
       <c r="C14" s="32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>65</v>
+        <v>161</v>
       </c>
       <c r="G14">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H14">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I14" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
@@ -3125,17 +3144,17 @@
         <v>123</v>
       </c>
       <c r="C15" s="32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G15">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H15">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I15" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
@@ -3151,24 +3170,24 @@
         <v>123</v>
       </c>
       <c r="C16" s="32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G16">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H16">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I16" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>17</v>
@@ -3177,24 +3196,24 @@
         <v>123</v>
       </c>
       <c r="C17" s="32">
-        <v>2</v>
-      </c>
-      <c r="D17" s="30">
-        <v>56</v>
+        <v>1</v>
+      </c>
+      <c r="D17" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="G17">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H17">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I17" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>18</v>
@@ -3205,25 +3224,22 @@
       <c r="C18" s="32">
         <v>2</v>
       </c>
-      <c r="D18" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>145</v>
+      <c r="D18" s="30">
+        <v>56</v>
       </c>
       <c r="G18">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>16</v>
       </c>
       <c r="H18">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="I18" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>19</v>
@@ -3232,108 +3248,111 @@
         <v>123</v>
       </c>
       <c r="C19" s="32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="G19">
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>16</v>
+      </c>
+      <c r="H19">
+        <v>35</v>
+      </c>
+      <c r="I19" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>20</v>
+      </c>
+      <c r="B20" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="C20" s="32">
+        <v>1</v>
+      </c>
+      <c r="D20" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="G19">
+      <c r="G20">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>8</v>
       </c>
-      <c r="H19">
-        <v>25</v>
-      </c>
-      <c r="I19" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="42">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+      <c r="H20">
+        <v>50</v>
+      </c>
+      <c r="I20" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="42">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>21</v>
+      </c>
+      <c r="B21" s="43" t="s">
+        <v>123</v>
+      </c>
+      <c r="C21" s="44">
+        <v>1</v>
+      </c>
+      <c r="D21" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="E21" s="45" t="s">
+        <v>143</v>
+      </c>
+      <c r="F21" s="45"/>
+      <c r="G21" s="46">
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>8</v>
+      </c>
+      <c r="H21" s="46">
         <v>20</v>
       </c>
-      <c r="B20" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="C20" s="44">
-        <v>1</v>
-      </c>
-      <c r="D20" s="45" t="s">
-        <v>70</v>
-      </c>
-      <c r="E20" s="45" t="s">
-        <v>143</v>
-      </c>
-      <c r="F20" s="45"/>
-      <c r="G20" s="46">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
-      </c>
-      <c r="H20" s="46">
-        <v>20</v>
-      </c>
-      <c r="I20" s="47">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="34">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>21</v>
-      </c>
-      <c r="B21" s="35" t="s">
+      <c r="I21" s="47">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="34">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>22</v>
+      </c>
+      <c r="B22" s="35" t="s">
         <v>124</v>
       </c>
-      <c r="C21" s="36">
+      <c r="C22" s="36">
         <v>4</v>
       </c>
-      <c r="D21" s="37" t="s">
+      <c r="D22" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="E21" s="37"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="38">
+      <c r="E22" s="37"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="38">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>32</v>
       </c>
-      <c r="H21" s="38">
+      <c r="H22" s="38">
         <v>100</v>
       </c>
-      <c r="I21" s="39">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="40">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>22</v>
-      </c>
-      <c r="B22" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="C22" s="32">
-        <v>2</v>
-      </c>
-      <c r="D22" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="G22">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>16</v>
-      </c>
-      <c r="H22">
-        <v>30</v>
-      </c>
-      <c r="I22" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I22" s="39">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>23</v>
@@ -3342,24 +3361,24 @@
         <v>124</v>
       </c>
       <c r="C23" s="32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="30" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="G23">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H23">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="I23" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>24</v>
@@ -3368,24 +3387,24 @@
         <v>124</v>
       </c>
       <c r="C24" s="32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" s="30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G24">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H24">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I24" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>25</v>
@@ -3394,30 +3413,24 @@
         <v>124</v>
       </c>
       <c r="C25" s="32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D25" s="30" t="s">
-        <v>74</v>
-      </c>
-      <c r="E25" s="30" t="s">
-        <v>140</v>
-      </c>
-      <c r="F25" s="30" t="s">
-        <v>136</v>
+        <v>73</v>
       </c>
       <c r="G25">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="H25">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I25" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>26</v>
@@ -3426,24 +3439,30 @@
         <v>124</v>
       </c>
       <c r="C26" s="32">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D26" s="30" t="s">
-        <v>75</v>
+        <v>74</v>
+      </c>
+      <c r="E26" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="F26" s="30" t="s">
+        <v>136</v>
       </c>
       <c r="G26">
-        <f>Table2[[#This Row],[Quantity]]*M6</f>
-        <v>0</v>
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>32</v>
       </c>
       <c r="H26">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I26" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>27</v>
@@ -3455,53 +3474,47 @@
         <v>6</v>
       </c>
       <c r="D27" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="G27">
+        <f>Table2[[#This Row],[Quantity]]*M5</f>
+        <v>12</v>
+      </c>
+      <c r="H27">
+        <v>35</v>
+      </c>
+      <c r="I27" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>28</v>
+      </c>
+      <c r="B28" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="C28" s="32">
+        <v>6</v>
+      </c>
+      <c r="D28" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="G27">
+      <c r="G28">
         <f>Table2[[#This Row],[Quantity]]*($M$3-M6)</f>
         <v>48</v>
       </c>
-      <c r="H27">
-        <v>50</v>
-      </c>
-      <c r="I27" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="40">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>28</v>
-      </c>
-      <c r="B28" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="C28" s="32">
-        <v>1</v>
-      </c>
-      <c r="D28" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="E28" s="30" t="s">
-        <v>152</v>
-      </c>
-      <c r="G28">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
-      </c>
       <c r="H28">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="I28" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>8</v>
-      </c>
-      <c r="J28" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>29</v>
@@ -3510,24 +3523,30 @@
         <v>124</v>
       </c>
       <c r="C29" s="32">
-        <v>2</v>
-      </c>
-      <c r="D29" s="30">
-        <v>56</v>
+        <v>1</v>
+      </c>
+      <c r="D29" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="E29" s="30" t="s">
+        <v>152</v>
       </c>
       <c r="G29">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H29">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I29" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="J29" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>30</v>
@@ -3536,24 +3555,24 @@
         <v>124</v>
       </c>
       <c r="C30" s="32">
-        <v>1</v>
-      </c>
-      <c r="D30" s="30" t="s">
-        <v>141</v>
+        <v>2</v>
+      </c>
+      <c r="D30" s="30">
+        <v>56</v>
       </c>
       <c r="G30">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H30">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I30" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>31</v>
@@ -3562,30 +3581,24 @@
         <v>124</v>
       </c>
       <c r="C31" s="32">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D31" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="E31" s="30" t="s">
-        <v>143</v>
-      </c>
-      <c r="F31" s="30" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G31">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="H31">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I31" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>32</v>
@@ -3594,21 +3607,33 @@
         <v>124</v>
       </c>
       <c r="C32" s="32">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D32" s="30" t="s">
-        <v>139</v>
+        <v>79</v>
+      </c>
+      <c r="E32" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="F32" s="30" t="s">
+        <v>142</v>
       </c>
       <c r="G32">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="H32">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="I32" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
         <v>0</v>
+      </c>
+      <c r="J32" t="s">
+        <v>162</v>
+      </c>
+      <c r="L32" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
@@ -3622,15 +3647,15 @@
       <c r="C33" s="32">
         <v>1</v>
       </c>
-      <c r="D33" s="30">
-        <v>1100</v>
+      <c r="D33" s="30" t="s">
+        <v>139</v>
       </c>
       <c r="G33">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>8</v>
       </c>
       <c r="H33">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I33" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
@@ -3648,76 +3673,73 @@
       <c r="C34" s="32">
         <v>1</v>
       </c>
-      <c r="D34" s="30" t="s">
+      <c r="D34" s="30">
+        <v>1100</v>
+      </c>
+      <c r="G34">
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>8</v>
+      </c>
+      <c r="H34">
+        <v>20</v>
+      </c>
+      <c r="I34" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>35</v>
+      </c>
+      <c r="B35" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="C35" s="32">
+        <v>1</v>
+      </c>
+      <c r="D35" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="G34">
+      <c r="G35">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>8</v>
       </c>
-      <c r="H34">
+      <c r="H35">
         <v>35</v>
       </c>
-      <c r="I34" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="42">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>35</v>
-      </c>
-      <c r="B35" s="43" t="s">
+      <c r="I35" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="42">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>36</v>
+      </c>
+      <c r="B36" s="43" t="s">
         <v>124</v>
       </c>
-      <c r="C35" s="44">
-        <v>1</v>
-      </c>
-      <c r="D35" s="45" t="s">
+      <c r="C36" s="44">
+        <v>1</v>
+      </c>
+      <c r="D36" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="E35" s="45"/>
-      <c r="F35" s="45"/>
-      <c r="G35" s="46">
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="46">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>8</v>
       </c>
-      <c r="H35" s="46">
-        <v>16</v>
-      </c>
-      <c r="I35" s="47">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>36</v>
-      </c>
-      <c r="B36" s="31" t="s">
-        <v>125</v>
-      </c>
-      <c r="C36" s="32">
-        <v>1</v>
-      </c>
-      <c r="D36" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="G36">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
-      </c>
-      <c r="H36">
-        <v>5</v>
-      </c>
-      <c r="I36">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>3</v>
-      </c>
-      <c r="J36" t="s">
-        <v>19</v>
+      <c r="H36" s="46">
+        <v>30</v>
+      </c>
+      <c r="I36" s="47">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
@@ -3729,21 +3751,21 @@
         <v>125</v>
       </c>
       <c r="C37" s="32">
+        <v>1</v>
+      </c>
+      <c r="D37" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="G37">
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>8</v>
+      </c>
+      <c r="H37">
+        <v>5</v>
+      </c>
+      <c r="I37">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
         <v>3</v>
-      </c>
-      <c r="D37" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="G37">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>24</v>
-      </c>
-      <c r="H37">
-        <v>0</v>
-      </c>
-      <c r="I37">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>24</v>
       </c>
       <c r="J37" t="s">
         <v>19</v>
@@ -3758,24 +3780,24 @@
         <v>125</v>
       </c>
       <c r="C38" s="32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D38" s="30" t="s">
-        <v>80</v>
+        <v>59</v>
+      </c>
+      <c r="E38" s="30" t="s">
+        <v>145</v>
       </c>
       <c r="G38">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I38">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>8</v>
-      </c>
-      <c r="J38" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
@@ -3787,21 +3809,21 @@
         <v>125</v>
       </c>
       <c r="C39" s="32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D39" s="30" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G39">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H39">
         <v>0</v>
       </c>
       <c r="I39">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J39" t="s">
         <v>19</v>
@@ -3816,27 +3838,21 @@
         <v>125</v>
       </c>
       <c r="C40" s="32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40" s="30" t="s">
-        <v>81</v>
-      </c>
-      <c r="E40" s="30" t="s">
-        <v>140</v>
-      </c>
-      <c r="F40" s="30" t="s">
-        <v>144</v>
+        <v>77</v>
       </c>
       <c r="G40">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H40">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I40">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J40" t="s">
         <v>19</v>
@@ -3851,21 +3867,27 @@
         <v>125</v>
       </c>
       <c r="C41" s="32">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D41" s="30" t="s">
-        <v>82</v>
+        <v>81</v>
+      </c>
+      <c r="E41" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="F41" s="30" t="s">
+        <v>144</v>
       </c>
       <c r="G41">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="J41" t="s">
         <v>19</v>
@@ -3880,21 +3902,21 @@
         <v>125</v>
       </c>
       <c r="C42" s="32">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D42" s="30" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G42">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="H42">
         <v>0</v>
       </c>
       <c r="I42">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="J42" t="s">
         <v>19</v>
@@ -3906,27 +3928,27 @@
         <v>43</v>
       </c>
       <c r="B43" s="31" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C43" s="32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D43" s="30" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G43">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="H43">
         <v>0</v>
       </c>
       <c r="I43">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="J43" t="s">
-        <v>133</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
@@ -3935,75 +3957,78 @@
         <v>44</v>
       </c>
       <c r="B44" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="C44" s="32">
+        <v>1</v>
+      </c>
+      <c r="D44" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="G44">
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>8</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>8</v>
+      </c>
+      <c r="J44" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>45</v>
+      </c>
+      <c r="B45" s="31" t="s">
         <v>85</v>
       </c>
-      <c r="C44" s="32">
-        <v>1</v>
-      </c>
-      <c r="D44" s="30" t="s">
+      <c r="C45" s="32">
+        <v>1</v>
+      </c>
+      <c r="D45" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="G44">
+      <c r="G45">
         <f>Table2[[#This Row],[Quantity]]*M5</f>
         <v>2</v>
       </c>
-      <c r="H44">
-        <v>0</v>
-      </c>
-      <c r="I44">
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
         <v>2</v>
       </c>
-      <c r="J44" t="s">
+      <c r="J45" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A45" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>45</v>
-      </c>
-      <c r="B45" s="31" t="s">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>46</v>
+      </c>
+      <c r="B46" s="31" t="s">
         <v>85</v>
       </c>
-      <c r="C45" s="32">
-        <v>1</v>
-      </c>
-      <c r="D45" s="30" t="s">
+      <c r="C46" s="32">
+        <v>1</v>
+      </c>
+      <c r="D46" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="G45">
+      <c r="G46">
         <f>Table2[[#This Row],[Quantity]]*($M$3-M5)</f>
         <v>6</v>
       </c>
-      <c r="H45">
+      <c r="H46">
         <v>10</v>
-      </c>
-      <c r="I45">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A46" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>46</v>
-      </c>
-      <c r="B46" s="31" t="s">
-        <v>88</v>
-      </c>
-      <c r="C46" s="32">
-        <v>1</v>
-      </c>
-      <c r="D46" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="G46">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
-      </c>
-      <c r="H46">
-        <v>50</v>
       </c>
       <c r="I46">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
@@ -4016,24 +4041,24 @@
         <v>47</v>
       </c>
       <c r="B47" s="31" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C47" s="32">
         <v>1</v>
       </c>
       <c r="D47" s="30" t="s">
-        <v>90</v>
+        <v>131</v>
       </c>
       <c r="G47">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>8</v>
       </c>
       <c r="H47">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="I47">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
@@ -4042,13 +4067,13 @@
         <v>48</v>
       </c>
       <c r="B48" s="31" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C48" s="32">
         <v>1</v>
       </c>
       <c r="D48" s="30" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G48">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
@@ -4068,27 +4093,24 @@
         <v>49</v>
       </c>
       <c r="B49" s="31" t="s">
-        <v>146</v>
+        <v>91</v>
       </c>
       <c r="C49" s="32">
         <v>1</v>
       </c>
-      <c r="D49" s="30">
-        <v>603</v>
+      <c r="D49" s="30" t="s">
+        <v>92</v>
       </c>
       <c r="G49">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>8</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I49">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>8</v>
-      </c>
-      <c r="J49" t="s">
-        <v>149</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
@@ -4097,23 +4119,27 @@
         <v>50</v>
       </c>
       <c r="B50" s="31" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C50" s="32">
-        <v>2</v>
-      </c>
-      <c r="D50" s="30" t="s">
-        <v>148</v>
+        <v>1</v>
+      </c>
+      <c r="D50" s="30">
+        <v>603</v>
       </c>
       <c r="G50">
-        <v>12</v>
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>8</v>
       </c>
       <c r="H50">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I50">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="J50" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
@@ -4122,20 +4148,19 @@
         <v>51</v>
       </c>
       <c r="B51" s="31" t="s">
-        <v>93</v>
+        <v>147</v>
       </c>
       <c r="C51" s="32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D51" s="30" t="s">
-        <v>94</v>
+        <v>148</v>
       </c>
       <c r="G51">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H51">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="I51">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
@@ -4154,7 +4179,7 @@
         <v>1</v>
       </c>
       <c r="D52" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G52">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
@@ -4174,19 +4199,20 @@
         <v>53</v>
       </c>
       <c r="B53" s="31" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C53" s="32">
         <v>1</v>
       </c>
       <c r="D53" s="30" t="s">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="G53">
-        <v>2</v>
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>8</v>
       </c>
       <c r="H53">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="I53">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
@@ -4205,11 +4231,10 @@
         <v>1</v>
       </c>
       <c r="D54" s="30" t="s">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="G54">
-        <f>Table2[[#This Row],[Quantity]]*M6</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H54">
         <v>4</v>
@@ -4225,24 +4250,24 @@
         <v>55</v>
       </c>
       <c r="B55" s="31" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C55" s="32">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D55" s="30" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G55">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>48</v>
+        <f>Table2[[#This Row],[Quantity]]*M6</f>
+        <v>0</v>
       </c>
       <c r="H55">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="I55">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
@@ -4251,24 +4276,24 @@
         <v>56</v>
       </c>
       <c r="B56" s="31" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="C56" s="32">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D56" s="30" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="G56">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="H56">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I56">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
@@ -4277,24 +4302,24 @@
         <v>57</v>
       </c>
       <c r="B57" s="31" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="C57" s="32">
         <v>1</v>
       </c>
       <c r="D57" s="30" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="G57">
-        <f>Table2[[#This Row],[Quantity]]*M7</f>
-        <v>0</v>
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>8</v>
       </c>
       <c r="H57">
         <v>0</v>
       </c>
       <c r="I57">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
@@ -4309,44 +4334,44 @@
         <v>1</v>
       </c>
       <c r="D58" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="G58">
+        <f>Table2[[#This Row],[Quantity]]*M7</f>
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A59" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>59</v>
+      </c>
+      <c r="B59" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="C59" s="32">
+        <v>1</v>
+      </c>
+      <c r="D59" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="G58">
+      <c r="G59">
         <f>Table2[[#This Row],[Quantity]]*($M$3-M7)</f>
         <v>8</v>
       </c>
-      <c r="H58">
+      <c r="H59">
         <v>5</v>
       </c>
-      <c r="I58">
+      <c r="I59">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
         <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A59" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>59</v>
-      </c>
-      <c r="B59" s="31" t="s">
-        <v>103</v>
-      </c>
-      <c r="C59" s="32">
-        <v>5</v>
-      </c>
-      <c r="D59" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="G59">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>40</v>
-      </c>
-      <c r="H59">
-        <v>100</v>
-      </c>
-      <c r="I59">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
@@ -4355,24 +4380,24 @@
         <v>60</v>
       </c>
       <c r="B60" s="31" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C60" s="32">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D60" s="30" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G60">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="H60">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="I60">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
@@ -4381,50 +4406,50 @@
         <v>61</v>
       </c>
       <c r="B61" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="C61" s="32">
+        <v>1</v>
+      </c>
+      <c r="D61" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G61">
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>8</v>
+      </c>
+      <c r="H61">
+        <v>3</v>
+      </c>
+      <c r="I61">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A62" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>62</v>
+      </c>
+      <c r="B62" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="C61" s="32">
-        <v>1</v>
-      </c>
-      <c r="D61" s="30" t="s">
+      <c r="C62" s="32">
+        <v>1</v>
+      </c>
+      <c r="D62" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="G61">
+      <c r="G62">
         <f>Table2[[#This Row],[Quantity]]*($M$3-M7)</f>
         <v>8</v>
       </c>
-      <c r="H61">
+      <c r="H62">
         <v>3</v>
       </c>
-      <c r="I61">
+      <c r="I62">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
         <v>5</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A62" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>62</v>
-      </c>
-      <c r="B62" s="31" t="s">
-        <v>109</v>
-      </c>
-      <c r="C62" s="32">
-        <v>1</v>
-      </c>
-      <c r="D62" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="G62">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
-      </c>
-      <c r="H62">
-        <v>10</v>
-      </c>
-      <c r="I62">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
@@ -4433,20 +4458,20 @@
         <v>63</v>
       </c>
       <c r="B63" s="31" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C63" s="32">
         <v>1</v>
       </c>
       <c r="D63" s="30" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G63">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>8</v>
       </c>
       <c r="H63">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I63">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
@@ -4459,107 +4484,110 @@
         <v>64</v>
       </c>
       <c r="B64" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="C64" s="32">
+        <v>1</v>
+      </c>
+      <c r="D64" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="G64">
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>8</v>
+      </c>
+      <c r="H64">
+        <v>20</v>
+      </c>
+      <c r="I64">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A65" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>65</v>
+      </c>
+      <c r="B65" s="31" t="s">
         <v>113</v>
       </c>
-      <c r="C64" s="32">
+      <c r="C65" s="32">
         <v>2</v>
       </c>
-      <c r="D64" s="30" t="s">
+      <c r="D65" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="G64">
+      <c r="G65">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>16</v>
-      </c>
-      <c r="H64">
-        <v>10</v>
-      </c>
-      <c r="I64">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>6</v>
-      </c>
-      <c r="J64" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A65" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>65</v>
-      </c>
-      <c r="B65" s="31" t="s">
-        <v>115</v>
-      </c>
-      <c r="C65" s="32">
-        <v>1</v>
-      </c>
-      <c r="D65" s="30" t="s">
-        <v>116</v>
-      </c>
-      <c r="G65">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
       </c>
       <c r="H65">
         <v>10</v>
       </c>
       <c r="I65">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="J65" t="s">
+        <v>19</v>
+      </c>
+      <c r="K65" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>66</v>
       </c>
       <c r="B66" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="C66" s="32">
+        <v>1</v>
+      </c>
+      <c r="D66" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="G66">
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>8</v>
+      </c>
+      <c r="H66">
+        <v>10</v>
+      </c>
+      <c r="I66">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A67" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>67</v>
+      </c>
+      <c r="B67" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="C66" s="32">
-        <v>1</v>
-      </c>
-      <c r="D66" s="30" t="s">
+      <c r="C67" s="32">
+        <v>1</v>
+      </c>
+      <c r="D67" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="G66">
+      <c r="G67">
         <v>2</v>
       </c>
-      <c r="H66">
+      <c r="H67">
         <v>3</v>
       </c>
-      <c r="I66">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A67" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>67</v>
-      </c>
-      <c r="B67" s="31" t="s">
-        <v>121</v>
-      </c>
-      <c r="C67" s="32">
-        <v>2</v>
-      </c>
-      <c r="D67" s="30" t="s">
-        <v>128</v>
-      </c>
-      <c r="G67">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>16</v>
-      </c>
-      <c r="H67">
-        <v>8</v>
-      </c>
       <c r="I67">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>68</v>
@@ -4571,27 +4599,27 @@
         <v>2</v>
       </c>
       <c r="D68" s="30" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G68">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>16</v>
       </c>
       <c r="H68">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="I68">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>69</v>
       </c>
       <c r="B69" s="31" t="s">
-        <v>150</v>
+        <v>121</v>
       </c>
       <c r="C69" s="32">
         <v>2</v>
@@ -4600,17 +4628,18 @@
         <v>129</v>
       </c>
       <c r="G69">
-        <v>2</v>
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>16</v>
       </c>
       <c r="H69">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="I69">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>70</v>
@@ -4622,66 +4651,74 @@
         <v>2</v>
       </c>
       <c r="D70" s="30" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G70">
         <v>2</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I70">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>71</v>
       </c>
       <c r="B71" s="31" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C71" s="32">
         <v>2</v>
       </c>
       <c r="D71" s="30" t="s">
+        <v>128</v>
+      </c>
+      <c r="G71">
+        <v>2</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A72" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>72</v>
+      </c>
+      <c r="B72" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="C72" s="32">
+        <v>2</v>
+      </c>
+      <c r="D72" s="30" t="s">
         <v>154</v>
       </c>
-      <c r="F71" s="30" t="s">
+      <c r="F72" s="30" t="s">
         <v>145</v>
       </c>
-      <c r="G71">
+      <c r="G72">
         <f>Table2[[#This Row],[Quantity]]*M5</f>
         <v>4</v>
       </c>
-      <c r="H71">
+      <c r="H72">
         <v>4</v>
       </c>
-      <c r="I71">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A72" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>72</v>
-      </c>
-      <c r="G72">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>0</v>
-      </c>
-      <c r="H72">
-        <v>0</v>
-      </c>
       <c r="I72">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>73</v>
@@ -4698,7 +4735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>74</v>
@@ -4715,7 +4752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>75</v>
@@ -4732,7 +4769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>76</v>
@@ -4749,7 +4786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>77</v>
@@ -4766,7 +4803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>78</v>
@@ -4783,7 +4820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>79</v>
@@ -4800,7 +4837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>80</v>
@@ -5106,11 +5143,40 @@
         <v>0</v>
       </c>
     </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A98" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>98</v>
+      </c>
+      <c r="G98">
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>0</v>
+      </c>
+      <c r="H98">
+        <v>0</v>
+      </c>
+      <c r="I98">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="I1:I97">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+  <conditionalFormatting sqref="I1:I98">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O2:O45">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Buying List + BOM V2.xlsx
+++ b/Buying List + BOM V2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\angel\Desktop\Proyectos\FOC_BLDC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2233622B-394C-47EF-B610-6B4DE2A24993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0582BAA3-4B07-4ED3-8BC8-105521B64C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="169">
   <si>
     <t>Component</t>
   </si>
@@ -240,9 +240,6 @@
     <t>560pF</t>
   </si>
   <si>
-    <t>15k</t>
-  </si>
-  <si>
     <t>1nF</t>
   </si>
   <si>
@@ -486,9 +483,6 @@
     <t>Male Connector</t>
   </si>
   <si>
-    <t>Senior</t>
-  </si>
-  <si>
     <t>XT60</t>
   </si>
   <si>
@@ -529,6 +523,27 @@
   </si>
   <si>
     <t>More than 16</t>
+  </si>
+  <si>
+    <t>Higher voltage rating</t>
+  </si>
+  <si>
+    <t>35V</t>
+  </si>
+  <si>
+    <t>15pF</t>
+  </si>
+  <si>
+    <t>86.6k</t>
+  </si>
+  <si>
+    <t>42uH or 47uH</t>
+  </si>
+  <si>
+    <t>more than 2A</t>
+  </si>
+  <si>
+    <t>0603 - 600R, 100Mhz</t>
   </si>
 </sst>
 </file>
@@ -802,7 +817,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -887,22 +902,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="37">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="36">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1453,48 +1461,48 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{57113999-89B8-4DCA-AAEB-0496B38A0B13}" name="Table1" displayName="Table1" ref="A1:K30" totalsRowCount="1" headerRowDxfId="29" dataDxfId="27" headerRowBorderDxfId="28" tableBorderDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{57113999-89B8-4DCA-AAEB-0496B38A0B13}" name="Table1" displayName="Table1" ref="A1:K30" totalsRowCount="1" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25">
   <autoFilter ref="A1:K29" xr:uid="{57113999-89B8-4DCA-AAEB-0496B38A0B13}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{C01A5BB4-2776-4DA4-B397-20536FB6B151}" name="Component" dataDxfId="25" totalsRowDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{D16A6BB5-FB54-4A08-8F36-6F894F571CA2}" name="Supplier" dataDxfId="23" totalsRowDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{13E6D449-D029-4B98-A474-567EF4C137DD}" name="Unit Price" dataDxfId="21" totalsRowDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{BFC6BC80-26FB-482F-B354-EBAC0B59B079}" name="Quantity / Board" dataDxfId="19" totalsRowDxfId="18"/>
-    <tableColumn id="8" xr3:uid="{60AEBA47-4243-42D3-988F-F3DB3204B15E}" name="Total Quantity 6 + 2" dataDxfId="17" totalsRowDxfId="16"/>
-    <tableColumn id="12" xr3:uid="{4B5F8A5D-14B9-498E-9411-2EEB2C426CA5}" name="Left to Purchase" dataDxfId="15" totalsRowDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{E17DAC7E-1E39-4AF4-8109-E85C3BEA4D94}" name="Shipping Costs" dataDxfId="13" totalsRowDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{80648434-14FA-49B4-BA1C-C16B6DFD9A61}" name="Purchased" dataDxfId="11" totalsRowDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{2A4D153E-2215-40C4-B217-8FADF5785568}" name="Arrived" dataDxfId="9" totalsRowDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{9BE18441-967B-45FF-8A88-16AF220F7381}" name="Total" totalsRowFunction="custom" dataDxfId="7" totalsRowDxfId="6">
+    <tableColumn id="1" xr3:uid="{C01A5BB4-2776-4DA4-B397-20536FB6B151}" name="Component" dataDxfId="24" totalsRowDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{D16A6BB5-FB54-4A08-8F36-6F894F571CA2}" name="Supplier" dataDxfId="22" totalsRowDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{13E6D449-D029-4B98-A474-567EF4C137DD}" name="Unit Price" dataDxfId="20" totalsRowDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{BFC6BC80-26FB-482F-B354-EBAC0B59B079}" name="Quantity / Board" dataDxfId="18" totalsRowDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{60AEBA47-4243-42D3-988F-F3DB3204B15E}" name="Total Quantity 6 + 2" dataDxfId="16" totalsRowDxfId="15"/>
+    <tableColumn id="12" xr3:uid="{4B5F8A5D-14B9-498E-9411-2EEB2C426CA5}" name="Left to Purchase" dataDxfId="14" totalsRowDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{E17DAC7E-1E39-4AF4-8109-E85C3BEA4D94}" name="Shipping Costs" dataDxfId="12" totalsRowDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{80648434-14FA-49B4-BA1C-C16B6DFD9A61}" name="Purchased" dataDxfId="10" totalsRowDxfId="9"/>
+    <tableColumn id="9" xr3:uid="{2A4D153E-2215-40C4-B217-8FADF5785568}" name="Arrived" dataDxfId="8" totalsRowDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{9BE18441-967B-45FF-8A88-16AF220F7381}" name="Total" totalsRowFunction="custom" dataDxfId="6" totalsRowDxfId="5">
       <calculatedColumnFormula>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(Table1[Total])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{B8F06C12-DD71-45A3-886F-8113BE8A9BDA}" name="Link" dataDxfId="5" totalsRowDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{B8F06C12-DD71-45A3-886F-8113BE8A9BDA}" name="Link" dataDxfId="4" totalsRowDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{22595191-1704-4DAD-B045-FA2F04CF59FF}" name="Table2" displayName="Table2" ref="A1:I98" totalsRowShown="0">
-  <autoFilter ref="A1:I98" xr:uid="{22595191-1704-4DAD-B045-FA2F04CF59FF}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I98">
-    <sortCondition ref="B1:B98"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{22595191-1704-4DAD-B045-FA2F04CF59FF}" name="Table2" displayName="Table2" ref="A1:I101" totalsRowShown="0">
+  <autoFilter ref="A1:I101" xr:uid="{22595191-1704-4DAD-B045-FA2F04CF59FF}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I101">
+    <sortCondition ref="B1:B101"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{573F2863-704A-459C-9EBD-42757DB1F58F}" name="Id" dataDxfId="36">
+    <tableColumn id="1" xr3:uid="{573F2863-704A-459C-9EBD-42757DB1F58F}" name="Id" dataDxfId="35">
       <calculatedColumnFormula>ROW(Table2[[#This Row],[Footprint]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{94458B27-EAA7-4644-96D5-025617151FB9}" name="Footprint" dataDxfId="35"/>
-    <tableColumn id="3" xr3:uid="{E80410E2-6881-4DFC-8748-8A0D261433F2}" name="Quantity" dataDxfId="34"/>
-    <tableColumn id="4" xr3:uid="{1CA2020F-6B3F-4E8B-8012-03FDA5CF807D}" name="Designation" dataDxfId="33"/>
-    <tableColumn id="10" xr3:uid="{C119C6F9-CB21-43A0-B289-A2AD9A4E4274}" name="Voltage comp" dataDxfId="32"/>
-    <tableColumn id="9" xr3:uid="{07CA118E-230B-4E63-B486-A70F92B6979D}" name="Voltage requirements" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{94458B27-EAA7-4644-96D5-025617151FB9}" name="Footprint" dataDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{E80410E2-6881-4DFC-8748-8A0D261433F2}" name="Quantity" dataDxfId="33"/>
+    <tableColumn id="4" xr3:uid="{1CA2020F-6B3F-4E8B-8012-03FDA5CF807D}" name="Designation" dataDxfId="32"/>
+    <tableColumn id="10" xr3:uid="{C119C6F9-CB21-43A0-B289-A2AD9A4E4274}" name="Voltage comp" dataDxfId="31"/>
+    <tableColumn id="9" xr3:uid="{07CA118E-230B-4E63-B486-A70F92B6979D}" name="Voltage requirements" dataDxfId="30"/>
     <tableColumn id="5" xr3:uid="{37D2A461-BCEF-4038-BCE9-6676ADE9155B}" name="Total">
       <calculatedColumnFormula>Table2[[#This Row],[Quantity]]*$M$3</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{4C6DF7CF-2E5F-4ECA-A520-C9BDA8B38EA1}" name="Personal Stock"/>
-    <tableColumn id="7" xr3:uid="{0BE67764-592A-43FD-8413-C7CDBA42BEAE}" name="BUY / HIVE" dataDxfId="30">
+    <tableColumn id="7" xr3:uid="{0BE67764-592A-43FD-8413-C7CDBA42BEAE}" name="BUY / HIVE" dataDxfId="29">
       <calculatedColumnFormula>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1854,7 +1862,7 @@
     </row>
     <row r="3" spans="1:11" ht="24.6" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>20</v>
@@ -2431,7 +2439,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>32</v>
@@ -2463,7 +2471,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B21" s="11" t="s">
         <v>32</v>
@@ -2495,10 +2503,10 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C22" s="13">
         <v>0</v>
@@ -2527,10 +2535,10 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C23" s="13">
         <v>0</v>
@@ -2559,10 +2567,10 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C24" s="13">
         <v>0</v>
@@ -2591,7 +2599,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>20</v>
@@ -2707,12 +2715,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F30">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:I30">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2728,7 +2736,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24286835-DDBE-4844-A8EA-1CAF4B158E48}">
-  <dimension ref="A1:M98"/>
+  <dimension ref="A1:M101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.109375" style="32" customWidth="1"/>
@@ -2757,10 +2765,10 @@
         <v>51</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F1" s="30" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G1" t="s">
         <v>8</v>
@@ -2784,18 +2792,18 @@
         <v>2</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G2">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H2">
         <v>10</v>
       </c>
       <c r="I2">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J2" t="s">
         <v>19</v>
@@ -2807,7 +2815,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C3" s="32">
         <v>1</v>
@@ -2817,7 +2825,7 @@
       </c>
       <c r="G3">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H3">
         <v>50</v>
@@ -2830,7 +2838,7 @@
         <v>56</v>
       </c>
       <c r="M3" s="33">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2839,17 +2847,17 @@
         <v>4</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C4" s="32">
         <v>4</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G4">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H4">
         <v>40</v>
@@ -2867,7 +2875,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5" s="36">
         <v>1</v>
@@ -2879,7 +2887,7 @@
       <c r="F5" s="37"/>
       <c r="G5" s="38">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H5" s="38">
         <v>50</v>
@@ -2901,7 +2909,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C6" s="32">
         <v>1</v>
@@ -2911,7 +2919,7 @@
       </c>
       <c r="G6">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H6">
         <v>50</v>
@@ -2927,7 +2935,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C7" s="32">
         <v>14</v>
@@ -2936,14 +2944,14 @@
         <v>59</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F7" s="30" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G7">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="H7">
         <v>500</v>
@@ -2959,7 +2967,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C8" s="32">
         <v>1</v>
@@ -2969,7 +2977,7 @@
       </c>
       <c r="G8">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H8">
         <v>50</v>
@@ -2985,7 +2993,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C9" s="32">
         <v>2</v>
@@ -2995,7 +3003,7 @@
       </c>
       <c r="G9">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H9">
         <v>40</v>
@@ -3011,7 +3019,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C10" s="32">
         <v>9</v>
@@ -3021,7 +3029,7 @@
       </c>
       <c r="G10">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="H10">
         <v>150</v>
@@ -3037,7 +3045,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C11" s="32">
         <v>2</v>
@@ -3047,7 +3055,7 @@
       </c>
       <c r="G11">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H11">
         <v>40</v>
@@ -3063,7 +3071,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C12" s="32">
         <v>4</v>
@@ -3073,7 +3081,7 @@
       </c>
       <c r="G12">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H12">
         <v>70</v>
@@ -3089,17 +3097,17 @@
         <v>13</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C13" s="32">
         <v>1</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G13">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H13">
         <v>30</v>
@@ -3115,17 +3123,17 @@
         <v>14</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C14" s="32">
         <v>2</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G14">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H14">
         <v>50</v>
@@ -3141,7 +3149,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C15" s="32">
         <v>1</v>
@@ -3151,7 +3159,7 @@
       </c>
       <c r="G15">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H15">
         <v>20</v>
@@ -3167,7 +3175,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C16" s="32">
         <v>2</v>
@@ -3177,7 +3185,7 @@
       </c>
       <c r="G16">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H16">
         <v>25</v>
@@ -3187,23 +3195,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>17</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C17" s="32">
         <v>1</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>67</v>
+        <v>165</v>
       </c>
       <c r="G17">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H17">
         <v>40</v>
@@ -3213,13 +3221,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>18</v>
       </c>
       <c r="B18" s="31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C18" s="32">
         <v>2</v>
@@ -3229,7 +3237,7 @@
       </c>
       <c r="G18">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H18">
         <v>50</v>
@@ -3239,26 +3247,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>19</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C19" s="32">
         <v>2</v>
       </c>
       <c r="D19" s="30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E19" s="30" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G19">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H19">
         <v>35</v>
@@ -3268,23 +3276,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>20</v>
       </c>
       <c r="B20" s="31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C20" s="32">
         <v>1</v>
       </c>
       <c r="D20" s="30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G20">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H20">
         <v>50</v>
@@ -3294,27 +3302,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="42">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>21</v>
       </c>
       <c r="B21" s="43" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C21" s="44">
         <v>1</v>
       </c>
       <c r="D21" s="45" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E21" s="45" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F21" s="45"/>
       <c r="G21" s="46">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H21" s="46">
         <v>20</v>
@@ -3324,25 +3332,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="34">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>22</v>
       </c>
       <c r="B22" s="35" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C22" s="36">
         <v>4</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E22" s="37"/>
       <c r="F22" s="37"/>
       <c r="G22" s="38">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H22" s="38">
         <v>100</v>
@@ -3352,13 +3360,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>23</v>
       </c>
       <c r="B23" s="31" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C23" s="32">
         <v>2</v>
@@ -3368,7 +3376,7 @@
       </c>
       <c r="G23">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H23">
         <v>60</v>
@@ -3378,23 +3386,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>24</v>
       </c>
       <c r="B24" s="31" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C24" s="32">
         <v>1</v>
       </c>
       <c r="D24" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G24">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H24">
         <v>20</v>
@@ -3404,687 +3412,702 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>25</v>
       </c>
       <c r="B25" s="31" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C25" s="32">
+        <v>1</v>
+      </c>
+      <c r="D25" s="30" t="s">
+        <v>164</v>
+      </c>
+      <c r="G25">
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>7</v>
+      </c>
+      <c r="H25">
+        <v>30</v>
+      </c>
+      <c r="I25" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>26</v>
+      </c>
+      <c r="B26" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="C26" s="32">
         <v>2</v>
       </c>
-      <c r="D25" s="30" t="s">
+      <c r="D26" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="G26">
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>14</v>
+      </c>
+      <c r="H26">
+        <v>60</v>
+      </c>
+      <c r="I26" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>27</v>
+      </c>
+      <c r="B27" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="C27" s="32">
+        <v>4</v>
+      </c>
+      <c r="D27" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="G25">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>16</v>
-      </c>
-      <c r="H25">
-        <v>60</v>
-      </c>
-      <c r="I25" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="40">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>26</v>
-      </c>
-      <c r="B26" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="C26" s="32">
-        <v>4</v>
-      </c>
-      <c r="D26" s="30" t="s">
+      <c r="E27" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="F27" s="30" t="s">
+        <v>135</v>
+      </c>
+      <c r="G27">
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>28</v>
+      </c>
+      <c r="H27">
+        <v>50</v>
+      </c>
+      <c r="I27" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>28</v>
+      </c>
+      <c r="B28" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="C28" s="32">
+        <v>6</v>
+      </c>
+      <c r="D28" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="E26" s="30" t="s">
-        <v>140</v>
-      </c>
-      <c r="F26" s="30" t="s">
-        <v>136</v>
-      </c>
-      <c r="G26">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>32</v>
-      </c>
-      <c r="H26">
-        <v>50</v>
-      </c>
-      <c r="I26" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="40">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>27</v>
-      </c>
-      <c r="B27" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="C27" s="32">
-        <v>6</v>
-      </c>
-      <c r="D27" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="G27">
+      <c r="G28">
         <f>Table2[[#This Row],[Quantity]]*M5</f>
         <v>12</v>
       </c>
-      <c r="H27">
+      <c r="H28">
         <v>35</v>
       </c>
-      <c r="I27" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="40">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+      <c r="I28" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>29</v>
+      </c>
+      <c r="B29" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="C29" s="32">
+        <v>6</v>
+      </c>
+      <c r="D29" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="G29">
+        <f>Table2[[#This Row],[Quantity]]*($M$3-M6)</f>
+        <v>42</v>
+      </c>
+      <c r="H29">
+        <v>76</v>
+      </c>
+      <c r="I29" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>30</v>
+      </c>
+      <c r="B30" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="C30" s="32">
+        <v>1</v>
+      </c>
+      <c r="D30" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="E30" s="30" t="s">
+        <v>150</v>
+      </c>
+      <c r="G30">
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>7</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>7</v>
+      </c>
+      <c r="J30" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>31</v>
+      </c>
+      <c r="B31" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="C31" s="32">
+        <v>2</v>
+      </c>
+      <c r="D31" s="30">
+        <v>56</v>
+      </c>
+      <c r="G31">
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>14</v>
+      </c>
+      <c r="H31">
+        <v>50</v>
+      </c>
+      <c r="I31" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>32</v>
+      </c>
+      <c r="B32" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="C32" s="32">
+        <v>1</v>
+      </c>
+      <c r="D32" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="G32">
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>7</v>
+      </c>
+      <c r="H32">
+        <v>20</v>
+      </c>
+      <c r="I32" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>33</v>
+      </c>
+      <c r="B33" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="C33" s="32">
+        <v>4</v>
+      </c>
+      <c r="D33" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="E33" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="F33" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="G33">
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>28</v>
       </c>
-      <c r="B28" s="31" t="s">
+      <c r="H33">
+        <v>70</v>
+      </c>
+      <c r="I33" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+      <c r="J33" t="s">
+        <v>160</v>
+      </c>
+      <c r="L33" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>34</v>
+      </c>
+      <c r="B34" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="C34" s="32">
+        <v>1</v>
+      </c>
+      <c r="D34" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="G34">
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>7</v>
+      </c>
+      <c r="H34">
+        <v>50</v>
+      </c>
+      <c r="I34" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>35</v>
+      </c>
+      <c r="B35" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="C35" s="32">
+        <v>1</v>
+      </c>
+      <c r="D35" s="30">
+        <v>1100</v>
+      </c>
+      <c r="G35">
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>7</v>
+      </c>
+      <c r="H35">
+        <v>20</v>
+      </c>
+      <c r="I35" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>36</v>
+      </c>
+      <c r="B36" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="C36" s="32">
+        <v>1</v>
+      </c>
+      <c r="D36" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="G36">
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>7</v>
+      </c>
+      <c r="H36">
+        <v>35</v>
+      </c>
+      <c r="I36" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="42">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>37</v>
+      </c>
+      <c r="B37" s="43" t="s">
+        <v>123</v>
+      </c>
+      <c r="C37" s="44">
+        <v>1</v>
+      </c>
+      <c r="D37" s="45" t="s">
+        <v>55</v>
+      </c>
+      <c r="E37" s="45"/>
+      <c r="F37" s="45"/>
+      <c r="G37" s="46">
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>7</v>
+      </c>
+      <c r="H37" s="46">
+        <v>30</v>
+      </c>
+      <c r="I37" s="47">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>38</v>
+      </c>
+      <c r="B38" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="C28" s="32">
-        <v>6</v>
-      </c>
-      <c r="D28" s="30" t="s">
-        <v>76</v>
-      </c>
-      <c r="G28">
-        <f>Table2[[#This Row],[Quantity]]*($M$3-M6)</f>
-        <v>48</v>
-      </c>
-      <c r="H28">
-        <v>76</v>
-      </c>
-      <c r="I28" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="40">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>29</v>
-      </c>
-      <c r="B29" s="31" t="s">
+      <c r="C38" s="32">
+        <v>1</v>
+      </c>
+      <c r="D38" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="F38" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="G38">
+        <f>Table2[[#This Row],[Quantity]]*M3</f>
+        <v>7</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>7</v>
+      </c>
+      <c r="J38" t="s">
+        <v>19</v>
+      </c>
+      <c r="K38" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>39</v>
+      </c>
+      <c r="B39" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="C29" s="32">
-        <v>1</v>
-      </c>
-      <c r="D29" s="30" t="s">
+      <c r="C39" s="32">
+        <v>1</v>
+      </c>
+      <c r="D39" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="E29" s="30" t="s">
-        <v>152</v>
-      </c>
-      <c r="G29">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>8</v>
-      </c>
-      <c r="J29" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="40">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>30</v>
-      </c>
-      <c r="B30" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="C30" s="32">
+      <c r="F39" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="G39">
+        <f>Table2[[#This Row],[Quantity]]*M5</f>
         <v>2</v>
       </c>
-      <c r="D30" s="30">
-        <v>56</v>
-      </c>
-      <c r="G30">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>16</v>
-      </c>
-      <c r="H30">
-        <v>50</v>
-      </c>
-      <c r="I30" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="40">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>31</v>
-      </c>
-      <c r="B31" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="C31" s="32">
-        <v>1</v>
-      </c>
-      <c r="D31" s="30" t="s">
-        <v>141</v>
-      </c>
-      <c r="G31">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
-      </c>
-      <c r="H31">
-        <v>20</v>
-      </c>
-      <c r="I31" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="40">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>32</v>
-      </c>
-      <c r="B32" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="C32" s="32">
-        <v>4</v>
-      </c>
-      <c r="D32" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="E32" s="30" t="s">
-        <v>143</v>
-      </c>
-      <c r="F32" s="30" t="s">
-        <v>142</v>
-      </c>
-      <c r="G32">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>32</v>
-      </c>
-      <c r="H32">
-        <v>70</v>
-      </c>
-      <c r="I32" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-      <c r="J32" t="s">
-        <v>162</v>
-      </c>
-      <c r="L32" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" s="40">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>33</v>
-      </c>
-      <c r="B33" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="C33" s="32">
-        <v>1</v>
-      </c>
-      <c r="D33" s="30" t="s">
-        <v>139</v>
-      </c>
-      <c r="G33">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
-      </c>
-      <c r="H33">
-        <v>50</v>
-      </c>
-      <c r="I33" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" s="40">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>34</v>
-      </c>
-      <c r="B34" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="C34" s="32">
-        <v>1</v>
-      </c>
-      <c r="D34" s="30">
-        <v>1100</v>
-      </c>
-      <c r="G34">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
-      </c>
-      <c r="H34">
-        <v>20</v>
-      </c>
-      <c r="I34" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" s="40">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>35</v>
-      </c>
-      <c r="B35" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="C35" s="32">
-        <v>1</v>
-      </c>
-      <c r="D35" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="G35">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
-      </c>
-      <c r="H35">
-        <v>35</v>
-      </c>
-      <c r="I35" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="42">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>36</v>
-      </c>
-      <c r="B36" s="43" t="s">
-        <v>124</v>
-      </c>
-      <c r="C36" s="44">
-        <v>1</v>
-      </c>
-      <c r="D36" s="45" t="s">
-        <v>55</v>
-      </c>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="46">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
-      </c>
-      <c r="H36" s="46">
-        <v>30</v>
-      </c>
-      <c r="I36" s="47">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>37</v>
-      </c>
-      <c r="B37" s="31" t="s">
-        <v>125</v>
-      </c>
-      <c r="C37" s="32">
-        <v>1</v>
-      </c>
-      <c r="D37" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="G37">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
-      </c>
-      <c r="H37">
-        <v>5</v>
-      </c>
-      <c r="I37">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>3</v>
-      </c>
-      <c r="J37" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>38</v>
-      </c>
-      <c r="B38" s="31" t="s">
-        <v>125</v>
-      </c>
-      <c r="C38" s="32">
-        <v>3</v>
-      </c>
-      <c r="D38" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="E38" s="30" t="s">
-        <v>145</v>
-      </c>
-      <c r="G38">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>24</v>
-      </c>
-      <c r="H38">
-        <v>40</v>
-      </c>
-      <c r="I38">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>39</v>
-      </c>
-      <c r="B39" s="31" t="s">
-        <v>125</v>
-      </c>
-      <c r="C39" s="32">
-        <v>1</v>
-      </c>
-      <c r="D39" s="30" t="s">
-        <v>80</v>
-      </c>
-      <c r="G39">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
-      </c>
       <c r="H39">
         <v>0</v>
       </c>
       <c r="I39">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J39" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K39" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>40</v>
       </c>
       <c r="B40" s="31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C40" s="32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D40" s="30" t="s">
-        <v>77</v>
+        <v>59</v>
+      </c>
+      <c r="E40" s="30" t="s">
+        <v>144</v>
       </c>
       <c r="G40">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I40">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>16</v>
-      </c>
-      <c r="J40" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>41</v>
       </c>
       <c r="B41" s="31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C41" s="32">
         <v>1</v>
       </c>
       <c r="D41" s="30" t="s">
-        <v>81</v>
-      </c>
-      <c r="E41" s="30" t="s">
-        <v>140</v>
-      </c>
-      <c r="F41" s="30" t="s">
-        <v>144</v>
+        <v>79</v>
       </c>
       <c r="G41">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H41">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J41" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>42</v>
       </c>
       <c r="B42" s="31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C42" s="32">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D42" s="30" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="G42">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="H42">
         <v>0</v>
       </c>
       <c r="I42">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="J42" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>43</v>
       </c>
       <c r="B43" s="31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C43" s="32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D43" s="30" t="s">
-        <v>77</v>
+        <v>80</v>
+      </c>
+      <c r="E43" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="F43" s="30" t="s">
+        <v>143</v>
       </c>
       <c r="G43">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I43">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J43" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>44</v>
       </c>
       <c r="B44" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="C44" s="32">
+        <v>10</v>
+      </c>
+      <c r="D44" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="G44">
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>70</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>70</v>
+      </c>
+      <c r="J44" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>45</v>
+      </c>
+      <c r="B45" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="C45" s="32">
+        <v>3</v>
+      </c>
+      <c r="D45" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="G45">
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>21</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>21</v>
+      </c>
+      <c r="J45" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A46" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>46</v>
+      </c>
+      <c r="B46" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="C46" s="32">
+        <v>1</v>
+      </c>
+      <c r="D46" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="G46">
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>7</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>7</v>
+      </c>
+      <c r="J46" t="s">
         <v>132</v>
       </c>
-      <c r="C44" s="32">
-        <v>1</v>
-      </c>
-      <c r="D44" s="30" t="s">
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A47" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>47</v>
+      </c>
+      <c r="B47" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="G44">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
-      </c>
-      <c r="H44">
-        <v>0</v>
-      </c>
-      <c r="I44">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>8</v>
-      </c>
-      <c r="J44" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A45" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>45</v>
-      </c>
-      <c r="B45" s="31" t="s">
+      <c r="C47" s="32">
+        <v>1</v>
+      </c>
+      <c r="D47" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="C45" s="32">
-        <v>1</v>
-      </c>
-      <c r="D45" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="G45">
+      <c r="G47">
         <f>Table2[[#This Row],[Quantity]]*M5</f>
         <v>2</v>
       </c>
-      <c r="H45">
-        <v>0</v>
-      </c>
-      <c r="I45">
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
         <v>2</v>
       </c>
-      <c r="J45" t="s">
+      <c r="J47" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A46" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>46</v>
-      </c>
-      <c r="B46" s="31" t="s">
-        <v>85</v>
-      </c>
-      <c r="C46" s="32">
-        <v>1</v>
-      </c>
-      <c r="D46" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="G46">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A48" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>48</v>
+      </c>
+      <c r="B48" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="C48" s="32">
+        <v>1</v>
+      </c>
+      <c r="D48" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="G48">
         <f>Table2[[#This Row],[Quantity]]*($M$3-M5)</f>
-        <v>6</v>
-      </c>
-      <c r="H46">
+        <v>5</v>
+      </c>
+      <c r="H48">
         <v>10</v>
       </c>
-      <c r="I46">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>47</v>
-      </c>
-      <c r="B47" s="31" t="s">
-        <v>88</v>
-      </c>
-      <c r="C47" s="32">
-        <v>1</v>
-      </c>
-      <c r="D47" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="G47">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
-      </c>
-      <c r="H47">
-        <v>50</v>
-      </c>
-      <c r="I47">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A48" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>48</v>
-      </c>
-      <c r="B48" s="31" t="s">
-        <v>89</v>
-      </c>
-      <c r="C48" s="32">
-        <v>1</v>
-      </c>
-      <c r="D48" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="G48">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
-      </c>
-      <c r="H48">
-        <v>3</v>
-      </c>
       <c r="I48">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
@@ -4093,24 +4116,24 @@
         <v>49</v>
       </c>
       <c r="B49" s="31" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C49" s="32">
         <v>1</v>
       </c>
       <c r="D49" s="30" t="s">
-        <v>92</v>
+        <v>130</v>
       </c>
       <c r="G49">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H49">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="I49">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
@@ -4119,27 +4142,24 @@
         <v>50</v>
       </c>
       <c r="B50" s="31" t="s">
-        <v>146</v>
+        <v>88</v>
       </c>
       <c r="C50" s="32">
         <v>1</v>
       </c>
-      <c r="D50" s="30">
-        <v>603</v>
+      <c r="D50" s="30" t="s">
+        <v>89</v>
       </c>
       <c r="G50">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I50">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>8</v>
-      </c>
-      <c r="J50" t="s">
-        <v>149</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
@@ -4148,23 +4168,24 @@
         <v>51</v>
       </c>
       <c r="B51" s="31" t="s">
-        <v>147</v>
+        <v>90</v>
       </c>
       <c r="C51" s="32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D51" s="30" t="s">
-        <v>148</v>
+        <v>91</v>
       </c>
       <c r="G51">
-        <v>12</v>
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>7</v>
       </c>
       <c r="H51">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I51">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
@@ -4173,20 +4194,20 @@
         <v>52</v>
       </c>
       <c r="B52" s="31" t="s">
-        <v>93</v>
+        <v>145</v>
       </c>
       <c r="C52" s="32">
         <v>1</v>
       </c>
-      <c r="D52" s="30" t="s">
-        <v>94</v>
+      <c r="D52" s="50" t="s">
+        <v>168</v>
       </c>
       <c r="G52">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>7</v>
+      </c>
+      <c r="H52">
         <v>8</v>
-      </c>
-      <c r="H52">
-        <v>50</v>
       </c>
       <c r="I52">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
@@ -4199,20 +4220,19 @@
         <v>53</v>
       </c>
       <c r="B53" s="31" t="s">
-        <v>93</v>
+        <v>146</v>
       </c>
       <c r="C53" s="32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53" s="30" t="s">
-        <v>95</v>
+        <v>147</v>
       </c>
       <c r="G53">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H53">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="I53">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
@@ -4225,19 +4245,20 @@
         <v>54</v>
       </c>
       <c r="B54" s="31" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C54" s="32">
         <v>1</v>
       </c>
       <c r="D54" s="30" t="s">
-        <v>130</v>
+        <v>93</v>
       </c>
       <c r="G54">
-        <v>2</v>
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>7</v>
       </c>
       <c r="H54">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="I54">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
@@ -4250,20 +4271,20 @@
         <v>55</v>
       </c>
       <c r="B55" s="31" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C55" s="32">
         <v>1</v>
       </c>
       <c r="D55" s="30" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G55">
-        <f>Table2[[#This Row],[Quantity]]*M6</f>
-        <v>0</v>
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>7</v>
       </c>
       <c r="H55">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="I55">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
@@ -4276,24 +4297,23 @@
         <v>56</v>
       </c>
       <c r="B56" s="31" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C56" s="32">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D56" s="30" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="G56">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="H56">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="I56">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
@@ -4302,24 +4322,24 @@
         <v>57</v>
       </c>
       <c r="B57" s="31" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="C57" s="32">
         <v>1</v>
       </c>
       <c r="D57" s="30" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="G57">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
+        <f>Table2[[#This Row],[Quantity]]*M6</f>
+        <v>0</v>
       </c>
       <c r="H57">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I57">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
@@ -4328,24 +4348,24 @@
         <v>58</v>
       </c>
       <c r="B58" s="31" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C58" s="32">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D58" s="30" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G58">
-        <f>Table2[[#This Row],[Quantity]]*M7</f>
-        <v>0</v>
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>42</v>
       </c>
       <c r="H58">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I58">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
@@ -4354,24 +4374,24 @@
         <v>59</v>
       </c>
       <c r="B59" s="31" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="C59" s="32">
         <v>1</v>
       </c>
       <c r="D59" s="30" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="G59">
-        <f>Table2[[#This Row],[Quantity]]*($M$3-M7)</f>
-        <v>8</v>
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>7</v>
       </c>
       <c r="H59">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I59">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
@@ -4380,24 +4400,30 @@
         <v>60</v>
       </c>
       <c r="B60" s="31" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C60" s="32">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D60" s="30" t="s">
-        <v>104</v>
+        <v>100</v>
+      </c>
+      <c r="F60" s="30" t="s">
+        <v>167</v>
       </c>
       <c r="G60">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>40</v>
+        <f>Table2[[#This Row],[Quantity]]*M5</f>
+        <v>2</v>
       </c>
       <c r="H60">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="I60">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J60" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
@@ -4406,24 +4432,29 @@
         <v>61</v>
       </c>
       <c r="B61" s="31" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C61" s="32">
         <v>1</v>
       </c>
       <c r="D61" s="30" t="s">
-        <v>106</v>
+        <v>166</v>
+      </c>
+      <c r="F61" s="30" t="s">
+        <v>167</v>
       </c>
       <c r="G61">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H61">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I61">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="J61" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
@@ -4432,24 +4463,24 @@
         <v>62</v>
       </c>
       <c r="B62" s="31" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C62" s="32">
         <v>1</v>
       </c>
       <c r="D62" s="30" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="G62">
-        <f>Table2[[#This Row],[Quantity]]*($M$3-M7)</f>
-        <v>8</v>
+        <f>Table2[[#This Row],[Quantity]]*($M$3-M5)</f>
+        <v>5</v>
       </c>
       <c r="H62">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I62">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
@@ -4458,20 +4489,20 @@
         <v>63</v>
       </c>
       <c r="B63" s="31" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="C63" s="32">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D63" s="30" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="G63">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="H63">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="I63">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
@@ -4484,24 +4515,24 @@
         <v>64</v>
       </c>
       <c r="B64" s="31" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C64" s="32">
         <v>1</v>
       </c>
       <c r="D64" s="30" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G64">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H64">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I64">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
@@ -4510,30 +4541,24 @@
         <v>65</v>
       </c>
       <c r="B65" s="31" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C65" s="32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D65" s="30" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="G65">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>16</v>
+        <f>Table2[[#This Row],[Quantity]]*($M$3-M7)</f>
+        <v>7</v>
       </c>
       <c r="H65">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I65">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>6</v>
-      </c>
-      <c r="J65" t="s">
-        <v>19</v>
-      </c>
-      <c r="K65" t="s">
-        <v>163</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.3">
@@ -4542,17 +4567,17 @@
         <v>66</v>
       </c>
       <c r="B66" s="31" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C66" s="32">
         <v>1</v>
       </c>
       <c r="D66" s="30" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="G66">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H66">
         <v>10</v>
@@ -4568,19 +4593,20 @@
         <v>67</v>
       </c>
       <c r="B67" s="31" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C67" s="32">
         <v>1</v>
       </c>
       <c r="D67" s="30" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="G67">
-        <v>2</v>
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>7</v>
       </c>
       <c r="H67">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="I67">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
@@ -4593,24 +4619,30 @@
         <v>68</v>
       </c>
       <c r="B68" s="31" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="C68" s="32">
         <v>2</v>
       </c>
       <c r="D68" s="30" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="G68">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H68">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I68">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="J68" t="s">
+        <v>19</v>
+      </c>
+      <c r="K68" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.3">
@@ -4619,20 +4651,20 @@
         <v>69</v>
       </c>
       <c r="B69" s="31" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C69" s="32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D69" s="30" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="G69">
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H69">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I69">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
@@ -4645,19 +4677,19 @@
         <v>70</v>
       </c>
       <c r="B70" s="31" t="s">
-        <v>150</v>
+        <v>116</v>
       </c>
       <c r="C70" s="32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D70" s="30" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="G70">
         <v>2</v>
       </c>
       <c r="H70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I70">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
@@ -4670,23 +4702,24 @@
         <v>71</v>
       </c>
       <c r="B71" s="31" t="s">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="C71" s="32">
         <v>2</v>
       </c>
       <c r="D71" s="30" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G71">
-        <v>2</v>
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>14</v>
       </c>
       <c r="H71">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I71">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.3">
@@ -4695,74 +4728,99 @@
         <v>72</v>
       </c>
       <c r="B72" s="31" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="C72" s="32">
         <v>2</v>
       </c>
       <c r="D72" s="30" t="s">
-        <v>154</v>
-      </c>
-      <c r="F72" s="30" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="G72">
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>14</v>
+      </c>
+      <c r="H72">
+        <v>18</v>
+      </c>
+      <c r="I72">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A73" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>73</v>
+      </c>
+      <c r="B73" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="C73" s="32">
+        <v>2</v>
+      </c>
+      <c r="D73" s="30" t="s">
+        <v>128</v>
+      </c>
+      <c r="G73">
+        <v>2</v>
+      </c>
+      <c r="H73">
+        <v>2</v>
+      </c>
+      <c r="I73">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A74" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>74</v>
+      </c>
+      <c r="B74" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="C74" s="32">
+        <v>2</v>
+      </c>
+      <c r="D74" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="G74">
+        <v>2</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A75" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>75</v>
+      </c>
+      <c r="B75" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="C75" s="32">
+        <v>2</v>
+      </c>
+      <c r="D75" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="F75" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="G75">
         <f>Table2[[#This Row],[Quantity]]*M5</f>
         <v>4</v>
       </c>
-      <c r="H72">
+      <c r="H75">
         <v>4</v>
-      </c>
-      <c r="I72">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A73" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>73</v>
-      </c>
-      <c r="G73">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>0</v>
-      </c>
-      <c r="H73">
-        <v>0</v>
-      </c>
-      <c r="I73">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A74" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>74</v>
-      </c>
-      <c r="G74">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>0</v>
-      </c>
-      <c r="H74">
-        <v>0</v>
-      </c>
-      <c r="I74">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A75" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>75</v>
-      </c>
-      <c r="G75">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>0</v>
-      </c>
-      <c r="H75">
-        <v>0</v>
       </c>
       <c r="I75">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
@@ -5160,15 +5218,66 @@
         <v>0</v>
       </c>
     </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A99" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>99</v>
+      </c>
+      <c r="G99">
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>0</v>
+      </c>
+      <c r="H99">
+        <v>0</v>
+      </c>
+      <c r="I99">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A100" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>100</v>
+      </c>
+      <c r="G100">
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>0</v>
+      </c>
+      <c r="H100">
+        <v>0</v>
+      </c>
+      <c r="I100">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A101" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>101</v>
+      </c>
+      <c r="G101">
+        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+        <v>0</v>
+      </c>
+      <c r="H101">
+        <v>0</v>
+      </c>
+      <c r="I101">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="I1:I98">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+  <conditionalFormatting sqref="I1:I101">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O45">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="O2:O47">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/Buying List + BOM V2.xlsx
+++ b/Buying List + BOM V2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\angel\Desktop\Proyectos\FOC_BLDC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0582BAA3-4B07-4ED3-8BC8-105521B64C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{723EDD2A-6D59-4893-9D6B-1E4FF317C250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="173">
   <si>
     <t>Component</t>
   </si>
@@ -544,6 +544,18 @@
   </si>
   <si>
     <t>0603 - 600R, 100Mhz</t>
+  </si>
+  <si>
+    <t>Soldering Air Station</t>
+  </si>
+  <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>Main Asturion PCB + Smaller Stencil</t>
+  </si>
+  <si>
+    <t>2nd Component Order</t>
   </si>
 </sst>
 </file>
@@ -1461,8 +1473,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{57113999-89B8-4DCA-AAEB-0496B38A0B13}" name="Table1" displayName="Table1" ref="A1:K30" totalsRowCount="1" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25">
-  <autoFilter ref="A1:K29" xr:uid="{57113999-89B8-4DCA-AAEB-0496B38A0B13}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{57113999-89B8-4DCA-AAEB-0496B38A0B13}" name="Table1" displayName="Table1" ref="A1:K34" totalsRowCount="1" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25">
+  <autoFilter ref="A1:K33" xr:uid="{57113999-89B8-4DCA-AAEB-0496B38A0B13}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{C01A5BB4-2776-4DA4-B397-20536FB6B151}" name="Component" dataDxfId="24" totalsRowDxfId="23"/>
     <tableColumn id="2" xr3:uid="{D16A6BB5-FB54-4A08-8F36-6F894F571CA2}" name="Supplier" dataDxfId="22" totalsRowDxfId="21"/>
@@ -1773,7 +1785,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="58.109375" customWidth="1"/>
@@ -1887,7 +1899,7 @@
         <v>25</v>
       </c>
       <c r="I3" s="25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J3" s="26">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -2093,7 +2105,7 @@
         <v>25</v>
       </c>
       <c r="I9" s="25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J9" s="26">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -2226,10 +2238,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I13" s="25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J13" s="26">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -2260,10 +2272,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I14" s="25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J14" s="14">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -2621,7 +2633,7 @@
         <v>25</v>
       </c>
       <c r="I25" s="25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J25" s="26">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -2635,10 +2647,16 @@
       <c r="C26" s="13"/>
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
-      <c r="F26" s="29"/>
+      <c r="F26" s="29">
+        <v>0</v>
+      </c>
       <c r="G26" s="13"/>
-      <c r="H26" s="23"/>
-      <c r="I26" s="25"/>
+      <c r="H26" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="I26" s="25" t="s">
+        <v>25</v>
+      </c>
       <c r="J26" s="26">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
         <v>0</v>
@@ -2647,16 +2665,26 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" s="11"/>
+        <v>171</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="C27" s="13"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
+      <c r="D27" s="11">
+        <v>1</v>
+      </c>
+      <c r="E27" s="11">
+        <v>1</v>
+      </c>
       <c r="F27" s="29"/>
       <c r="G27" s="13"/>
-      <c r="H27" s="23"/>
-      <c r="I27" s="25"/>
+      <c r="H27" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="I27" s="25" t="s">
+        <v>26</v>
+      </c>
       <c r="J27" s="26">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
         <v>0</v>
@@ -2665,16 +2693,26 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="11"/>
+        <v>172</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>19</v>
+      </c>
       <c r="C28" s="13"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
+      <c r="D28" s="11">
+        <v>1</v>
+      </c>
+      <c r="E28" s="11">
+        <v>1</v>
+      </c>
       <c r="F28" s="29"/>
       <c r="G28" s="13"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="25"/>
+      <c r="H28" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="I28" s="25" t="s">
+        <v>26</v>
+      </c>
       <c r="J28" s="26">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
         <v>0</v>
@@ -2682,18 +2720,35 @@
       <c r="K28" s="11"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="12"/>
-      <c r="B29" s="11"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="29"/>
+      <c r="A29" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="C29" s="13">
+        <f>50*1.15</f>
+        <v>57.499999999999993</v>
+      </c>
+      <c r="D29" s="11">
+        <v>1</v>
+      </c>
+      <c r="E29" s="11">
+        <v>1</v>
+      </c>
+      <c r="F29" s="29">
+        <v>0</v>
+      </c>
       <c r="G29" s="13"/>
-      <c r="H29" s="23"/>
-      <c r="I29" s="25"/>
-      <c r="J29" s="14">
+      <c r="H29" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="I29" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="J29" s="26">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
-        <v>0</v>
+        <v>57.499999999999993</v>
       </c>
       <c r="K29" s="11"/>
     </row>
@@ -2707,19 +2762,87 @@
       <c r="G30" s="13"/>
       <c r="H30" s="23"/>
       <c r="I30" s="25"/>
-      <c r="J30" s="14">
+      <c r="J30" s="26">
+        <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
+        <v>0</v>
+      </c>
+      <c r="K30" s="11"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" s="11"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="23"/>
+      <c r="I31" s="25"/>
+      <c r="J31" s="26">
+        <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
+        <v>0</v>
+      </c>
+      <c r="K31" s="11"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" s="11"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="23"/>
+      <c r="I32" s="25"/>
+      <c r="J32" s="26">
+        <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
+        <v>0</v>
+      </c>
+      <c r="K32" s="11"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" s="12"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="23"/>
+      <c r="I33" s="25"/>
+      <c r="J33" s="14">
+        <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
+        <v>0</v>
+      </c>
+      <c r="K33" s="11"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34" s="12"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="23"/>
+      <c r="I34" s="25"/>
+      <c r="J34" s="14">
         <f>SUM(Table1[Total])</f>
-        <v>230.66</v>
-      </c>
-      <c r="K30" s="11"/>
+        <v>288.15999999999997</v>
+      </c>
+      <c r="K34" s="11"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F2:F30">
+  <conditionalFormatting sqref="F2:F34">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:I30">
+  <conditionalFormatting sqref="H2:I34">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
@@ -2859,12 +2982,9 @@
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>28</v>
       </c>
-      <c r="H4">
-        <v>40</v>
-      </c>
       <c r="I4">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="L4" s="33"/>
       <c r="M4" s="33"/>
@@ -2889,12 +3009,10 @@
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>7</v>
       </c>
-      <c r="H5" s="38">
-        <v>50</v>
-      </c>
+      <c r="H5" s="38"/>
       <c r="I5" s="39">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L5" s="33" t="s">
         <v>58</v>
@@ -2921,12 +3039,9 @@
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>7</v>
       </c>
-      <c r="H6">
-        <v>50</v>
-      </c>
       <c r="I6" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -2979,12 +3094,9 @@
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>7</v>
       </c>
-      <c r="H8">
-        <v>50</v>
-      </c>
       <c r="I8" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
@@ -3005,12 +3117,9 @@
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>14</v>
       </c>
-      <c r="H9">
-        <v>40</v>
-      </c>
       <c r="I9" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
@@ -3031,12 +3140,9 @@
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>63</v>
       </c>
-      <c r="H10">
-        <v>150</v>
-      </c>
       <c r="I10" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
@@ -3058,7 +3164,7 @@
         <v>14</v>
       </c>
       <c r="H11">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="I11" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
@@ -3083,12 +3189,9 @@
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>28</v>
       </c>
-      <c r="H12">
-        <v>70</v>
-      </c>
       <c r="I12" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
@@ -3109,12 +3212,9 @@
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>7</v>
       </c>
-      <c r="H13">
-        <v>30</v>
-      </c>
       <c r="I13" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
@@ -3135,12 +3235,9 @@
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>14</v>
       </c>
-      <c r="H14">
-        <v>50</v>
-      </c>
       <c r="I14" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
@@ -3187,12 +3284,9 @@
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>14</v>
       </c>
-      <c r="H16">
-        <v>25</v>
-      </c>
       <c r="I16" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
@@ -3213,12 +3307,9 @@
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>7</v>
       </c>
-      <c r="H17">
-        <v>40</v>
-      </c>
       <c r="I17" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
@@ -3239,12 +3330,9 @@
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>14</v>
       </c>
-      <c r="H18">
-        <v>50</v>
-      </c>
       <c r="I18" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
@@ -3268,12 +3356,9 @@
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>14</v>
       </c>
-      <c r="H19">
-        <v>35</v>
-      </c>
       <c r="I19" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
@@ -3294,12 +3379,9 @@
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>7</v>
       </c>
-      <c r="H20">
-        <v>50</v>
-      </c>
       <c r="I20" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3324,12 +3406,10 @@
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>7</v>
       </c>
-      <c r="H21" s="46">
-        <v>20</v>
-      </c>
+      <c r="H21" s="46"/>
       <c r="I21" s="47">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
@@ -3378,12 +3458,9 @@
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>14</v>
       </c>
-      <c r="H23">
-        <v>60</v>
-      </c>
       <c r="I23" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
@@ -3430,12 +3507,9 @@
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>7</v>
       </c>
-      <c r="H25">
-        <v>30</v>
-      </c>
       <c r="I25" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
@@ -3456,12 +3530,9 @@
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>14</v>
       </c>
-      <c r="H26">
-        <v>60</v>
-      </c>
       <c r="I26" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
@@ -3488,12 +3559,9 @@
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>28</v>
       </c>
-      <c r="H27">
-        <v>50</v>
-      </c>
       <c r="I27" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
@@ -3514,12 +3582,9 @@
         <f>Table2[[#This Row],[Quantity]]*M5</f>
         <v>12</v>
       </c>
-      <c r="H28">
-        <v>35</v>
-      </c>
       <c r="I28" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
@@ -3540,12 +3605,9 @@
         <f>Table2[[#This Row],[Quantity]]*($M$3-M6)</f>
         <v>42</v>
       </c>
-      <c r="H29">
-        <v>76</v>
-      </c>
       <c r="I29" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
@@ -3598,12 +3660,9 @@
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>14</v>
       </c>
-      <c r="H31">
-        <v>50</v>
-      </c>
       <c r="I31" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
@@ -3624,12 +3683,9 @@
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>7</v>
       </c>
-      <c r="H32">
-        <v>20</v>
-      </c>
       <c r="I32" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
@@ -3656,12 +3712,9 @@
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>28</v>
       </c>
-      <c r="H33">
-        <v>70</v>
-      </c>
       <c r="I33" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J33" t="s">
         <v>160</v>
@@ -3688,12 +3741,9 @@
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>7</v>
       </c>
-      <c r="H34">
-        <v>50</v>
-      </c>
       <c r="I34" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
@@ -3714,12 +3764,9 @@
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>7</v>
       </c>
-      <c r="H35">
-        <v>20</v>
-      </c>
       <c r="I35" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
@@ -3740,12 +3787,9 @@
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>7</v>
       </c>
-      <c r="H36">
-        <v>35</v>
-      </c>
       <c r="I36" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3768,12 +3812,10 @@
         <f>Table2[[#This Row],[Quantity]]*$M$3</f>
         <v>7</v>
       </c>
-      <c r="H37" s="46">
-        <v>30</v>
-      </c>
+      <c r="H37" s="46"/>
       <c r="I37" s="47">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
@@ -4207,11 +4249,11 @@
         <v>7</v>
       </c>
       <c r="H52">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I52">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">

--- a/Buying List + BOM V2.xlsx
+++ b/Buying List + BOM V2.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">

--- a/Buying List + BOM V2.xlsx
+++ b/Buying List + BOM V2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\angel\Desktop\Proyectos\FOC_BLDC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{723EDD2A-6D59-4893-9D6B-1E4FF317C250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EAE418D-A1CB-4F7E-81D7-6D46F05E6FC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="186">
   <si>
     <t>Component</t>
   </si>
@@ -51,9 +51,6 @@
     <t>Unit Price</t>
   </si>
   <si>
-    <t>Quantity</t>
-  </si>
-  <si>
     <t>Shipping Costs</t>
   </si>
   <si>
@@ -207,9 +204,6 @@
     <t>3.3k</t>
   </si>
   <si>
-    <t>Number of boards</t>
-  </si>
-  <si>
     <t>0.015uF</t>
   </si>
   <si>
@@ -234,9 +228,6 @@
     <t>100k</t>
   </si>
   <si>
-    <t>36pF</t>
-  </si>
-  <si>
     <t>560pF</t>
   </si>
   <si>
@@ -261,18 +252,12 @@
     <t>1uF</t>
   </si>
   <si>
-    <t>22R</t>
-  </si>
-  <si>
     <t>10R</t>
   </si>
   <si>
     <t>2.2uF</t>
   </si>
   <si>
-    <t>47uF</t>
-  </si>
-  <si>
     <t>0.1uF</t>
   </si>
   <si>
@@ -339,9 +324,6 @@
     <t>SM7850</t>
   </si>
   <si>
-    <t>22uH</t>
-  </si>
-  <si>
     <t>12uH</t>
   </si>
   <si>
@@ -435,9 +417,6 @@
     <t>B360A</t>
   </si>
   <si>
-    <t>Prior B3030</t>
-  </si>
-  <si>
     <t>Voltage requirements</t>
   </si>
   <si>
@@ -450,9 +429,6 @@
     <t>10V</t>
   </si>
   <si>
-    <t>1.5nF</t>
-  </si>
-  <si>
     <t>121R</t>
   </si>
   <si>
@@ -522,27 +498,12 @@
     <t>Can be changed by 0805 50V</t>
   </si>
   <si>
-    <t>More than 16</t>
-  </si>
-  <si>
-    <t>Higher voltage rating</t>
-  </si>
-  <si>
-    <t>35V</t>
-  </si>
-  <si>
     <t>15pF</t>
   </si>
   <si>
     <t>86.6k</t>
   </si>
   <si>
-    <t>42uH or 47uH</t>
-  </si>
-  <si>
-    <t>more than 2A</t>
-  </si>
-  <si>
     <t>0603 - 600R, 100Mhz</t>
   </si>
   <si>
@@ -556,6 +517,84 @@
   </si>
   <si>
     <t>2nd Component Order</t>
+  </si>
+  <si>
+    <t>Quantity Motor</t>
+  </si>
+  <si>
+    <t>Quantity Asturion</t>
+  </si>
+  <si>
+    <t>Number Asturion</t>
+  </si>
+  <si>
+    <t>Number of controllers</t>
+  </si>
+  <si>
+    <t>52.3k</t>
+  </si>
+  <si>
+    <t>Buzzer</t>
+  </si>
+  <si>
+    <t>6.8nF</t>
+  </si>
+  <si>
+    <t>27pF</t>
+  </si>
+  <si>
+    <t>330nF</t>
+  </si>
+  <si>
+    <t>LED 3 mm</t>
+  </si>
+  <si>
+    <t>Power Converter</t>
+  </si>
+  <si>
+    <t>TPS54560</t>
+  </si>
+  <si>
+    <t>Shift Register</t>
+  </si>
+  <si>
+    <t>74HC595</t>
+  </si>
+  <si>
+    <t>BJT Transistor</t>
+  </si>
+  <si>
+    <t>SS30101-Q</t>
+  </si>
+  <si>
+    <t>MOSFET Latch</t>
+  </si>
+  <si>
+    <t>IRF9540N</t>
+  </si>
+  <si>
+    <t>2N3904</t>
+  </si>
+  <si>
+    <t>21.5k</t>
+  </si>
+  <si>
+    <t>1M0</t>
+  </si>
+  <si>
+    <t>NRF24L01</t>
+  </si>
+  <si>
+    <t>Transceiver</t>
+  </si>
+  <si>
+    <t>TPS54160</t>
+  </si>
+  <si>
+    <t>Prior B330</t>
+  </si>
+  <si>
+    <t>25V</t>
   </si>
 </sst>
 </file>
@@ -829,7 +868,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -917,12 +956,19 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="36">
+  <dxfs count="37">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1453,6 +1499,9 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1470,6 +1519,23 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <bag type="Checkbox"/>
+  <bag type="XFControls">
+    <bagId k="CellControl">0</bagId>
+  </bag>
+  <bag type="XFComplement">
+    <bagId k="XFControls">1</bagId>
+  </bag>
+  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+</FeaturePropertyBags>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1496,22 +1562,23 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{22595191-1704-4DAD-B045-FA2F04CF59FF}" name="Table2" displayName="Table2" ref="A1:I101" totalsRowShown="0">
-  <autoFilter ref="A1:I101" xr:uid="{22595191-1704-4DAD-B045-FA2F04CF59FF}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I101">
-    <sortCondition ref="B1:B101"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{22595191-1704-4DAD-B045-FA2F04CF59FF}" name="Table2" displayName="Table2" ref="A1:J105" totalsRowShown="0">
+  <autoFilter ref="A1:J105" xr:uid="{22595191-1704-4DAD-B045-FA2F04CF59FF}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J105">
+    <sortCondition ref="B1:B105"/>
   </sortState>
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{573F2863-704A-459C-9EBD-42757DB1F58F}" name="Id" dataDxfId="35">
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{573F2863-704A-459C-9EBD-42757DB1F58F}" name="Id" dataDxfId="36">
       <calculatedColumnFormula>ROW(Table2[[#This Row],[Footprint]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{94458B27-EAA7-4644-96D5-025617151FB9}" name="Footprint" dataDxfId="34"/>
-    <tableColumn id="3" xr3:uid="{E80410E2-6881-4DFC-8748-8A0D261433F2}" name="Quantity" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{94458B27-EAA7-4644-96D5-025617151FB9}" name="Footprint" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{E80410E2-6881-4DFC-8748-8A0D261433F2}" name="Quantity Motor" dataDxfId="34"/>
+    <tableColumn id="11" xr3:uid="{F38A3F82-2312-4F72-A27B-A25BB01A905E}" name="Quantity Asturion" dataDxfId="33"/>
     <tableColumn id="4" xr3:uid="{1CA2020F-6B3F-4E8B-8012-03FDA5CF807D}" name="Designation" dataDxfId="32"/>
     <tableColumn id="10" xr3:uid="{C119C6F9-CB21-43A0-B289-A2AD9A4E4274}" name="Voltage comp" dataDxfId="31"/>
     <tableColumn id="9" xr3:uid="{07CA118E-230B-4E63-B486-A70F92B6979D}" name="Voltage requirements" dataDxfId="30"/>
     <tableColumn id="5" xr3:uid="{37D2A461-BCEF-4038-BCE9-6676ADE9155B}" name="Total">
-      <calculatedColumnFormula>Table2[[#This Row],[Quantity]]*$M$3</calculatedColumnFormula>
+      <calculatedColumnFormula>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{4C6DF7CF-2E5F-4ECA-A520-C9BDA8B38EA1}" name="Personal Stock"/>
     <tableColumn id="7" xr3:uid="{0BE67764-592A-43FD-8413-C7CDBA42BEAE}" name="BUY / HIVE" dataDxfId="29">
@@ -1811,25 +1878,25 @@
         <v>3</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="F1" s="27" t="s">
-        <v>44</v>
-      </c>
       <c r="G1" s="21" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="20" t="s">
-        <v>24</v>
-      </c>
       <c r="J1" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K1" s="6" t="s">
         <v>2</v>
@@ -1837,10 +1904,10 @@
     </row>
     <row r="2" spans="1:11" ht="24.6" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>6</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>7</v>
       </c>
       <c r="C2" s="9">
         <f>3.85</f>
@@ -1859,25 +1926,25 @@
         <v>7</v>
       </c>
       <c r="H2" s="22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I2" s="24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J2" s="10">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
         <v>10.85</v>
       </c>
       <c r="K2" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="24.6" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3" s="13">
         <f>30.91/2</f>
@@ -1896,10 +1963,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I3" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J3" s="26">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -1909,10 +1976,10 @@
     </row>
     <row r="4" spans="1:11" ht="24.6" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>11</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>12</v>
       </c>
       <c r="C4" s="13">
         <v>17.05</v>
@@ -1930,25 +1997,25 @@
         <v>0</v>
       </c>
       <c r="H4" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I4" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J4" s="14">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
         <v>34.1</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="18" t="s">
         <v>13</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>14</v>
       </c>
       <c r="C5" s="13">
         <v>0</v>
@@ -1966,25 +2033,25 @@
         <v>0</v>
       </c>
       <c r="H5" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I5" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J5" s="14">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
         <v>0</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6" s="13">
         <v>3.71</v>
@@ -2002,25 +2069,25 @@
         <v>1</v>
       </c>
       <c r="H6" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I6" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J6" s="14">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
         <v>15.84</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" s="13">
         <v>61.53</v>
@@ -2036,10 +2103,10 @@
       </c>
       <c r="G7" s="13"/>
       <c r="H7" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I7" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J7" s="14">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -2049,10 +2116,10 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C8" s="13">
         <v>13.23</v>
@@ -2068,10 +2135,10 @@
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I8" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J8" s="14">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -2081,10 +2148,10 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9" s="13">
         <v>28</v>
@@ -2102,10 +2169,10 @@
         <v>16</v>
       </c>
       <c r="H9" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I9" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J9" s="26">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -2115,10 +2182,10 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" s="13">
         <v>2.68</v>
@@ -2136,25 +2203,25 @@
         <v>0</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I10" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J10" s="14">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
         <v>8.0400000000000009</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11" s="13">
         <v>2.11</v>
@@ -2172,25 +2239,25 @@
         <v>0</v>
       </c>
       <c r="H11" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I11" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J11" s="14">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
         <v>4.22</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" s="13"/>
       <c r="D12" s="11">
@@ -2204,10 +2271,10 @@
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I12" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J12" s="14">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -2217,10 +2284,10 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C13" s="13">
         <v>0</v>
@@ -2238,10 +2305,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I13" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J13" s="26">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -2251,10 +2318,10 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C14" s="13">
         <v>0</v>
@@ -2272,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I14" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J14" s="14">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -2285,10 +2352,10 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="11" t="s">
         <v>31</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>32</v>
       </c>
       <c r="C15" s="13">
         <v>0</v>
@@ -2306,10 +2373,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I15" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J15" s="26">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -2319,10 +2386,10 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16" s="13">
         <v>0</v>
@@ -2340,10 +2407,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I16" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J16" s="26">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -2353,10 +2420,10 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C17" s="13">
         <v>0</v>
@@ -2374,10 +2441,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I17" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J17" s="26">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -2387,10 +2454,10 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>46</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>47</v>
       </c>
       <c r="C18" s="13">
         <v>0</v>
@@ -2406,10 +2473,10 @@
       </c>
       <c r="G18" s="13"/>
       <c r="H18" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I18" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J18" s="26">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -2419,10 +2486,10 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C19" s="13">
         <v>0</v>
@@ -2438,10 +2505,10 @@
       </c>
       <c r="G19" s="13"/>
       <c r="H19" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I19" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J19" s="26">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -2451,10 +2518,10 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C20" s="13">
         <v>0</v>
@@ -2470,10 +2537,10 @@
       </c>
       <c r="G20" s="13"/>
       <c r="H20" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I20" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J20" s="26">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -2483,10 +2550,10 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C21" s="13">
         <v>0</v>
@@ -2502,10 +2569,10 @@
       </c>
       <c r="G21" s="13"/>
       <c r="H21" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I21" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J21" s="26">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -2515,10 +2582,10 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C22" s="13">
         <v>0</v>
@@ -2534,10 +2601,10 @@
       </c>
       <c r="G22" s="13"/>
       <c r="H22" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I22" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J22" s="26">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -2547,10 +2614,10 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C23" s="13">
         <v>0</v>
@@ -2566,10 +2633,10 @@
       </c>
       <c r="G23" s="13"/>
       <c r="H23" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I23" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J23" s="26">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -2579,10 +2646,10 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C24" s="13">
         <v>0</v>
@@ -2598,10 +2665,10 @@
       </c>
       <c r="G24" s="13"/>
       <c r="H24" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I24" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J24" s="26">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -2611,10 +2678,10 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C25" s="13">
         <v>3.97</v>
@@ -2630,10 +2697,10 @@
       </c>
       <c r="G25" s="13"/>
       <c r="H25" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I25" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J25" s="26">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -2652,10 +2719,10 @@
       </c>
       <c r="G26" s="13"/>
       <c r="H26" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I26" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J26" s="26">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -2665,10 +2732,10 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="12" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C27" s="13"/>
       <c r="D27" s="11">
@@ -2680,10 +2747,10 @@
       <c r="F27" s="29"/>
       <c r="G27" s="13"/>
       <c r="H27" s="23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I27" s="25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J27" s="26">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -2693,10 +2760,10 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="12" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C28" s="13"/>
       <c r="D28" s="11">
@@ -2708,10 +2775,10 @@
       <c r="F28" s="29"/>
       <c r="G28" s="13"/>
       <c r="H28" s="23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I28" s="25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J28" s="26">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -2721,10 +2788,10 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="12" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="C29" s="13">
         <f>50*1.15</f>
@@ -2741,10 +2808,10 @@
       </c>
       <c r="G29" s="13"/>
       <c r="H29" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I29" s="25" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J29" s="26">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -2770,7 +2837,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="13"/>
@@ -2788,7 +2855,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="13"/>
@@ -2859,51 +2926,56 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24286835-DDBE-4844-A8EA-1CAF4B158E48}">
-  <dimension ref="A1:M101"/>
+  <dimension ref="A1:Q105"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.109375" style="32" customWidth="1"/>
     <col min="2" max="2" width="44.5546875" style="31" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" style="32" customWidth="1"/>
-    <col min="4" max="5" width="19" style="30" customWidth="1"/>
-    <col min="6" max="6" width="21.88671875" style="30" customWidth="1"/>
-    <col min="7" max="7" width="12.88671875" customWidth="1"/>
-    <col min="8" max="8" width="16.77734375" customWidth="1"/>
-    <col min="9" max="9" width="18.77734375" customWidth="1"/>
-    <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="12" max="12" width="23.5546875" customWidth="1"/>
+    <col min="3" max="4" width="21.6640625" style="32" customWidth="1"/>
+    <col min="5" max="6" width="19" style="30" customWidth="1"/>
+    <col min="7" max="7" width="21.88671875" style="30" customWidth="1"/>
+    <col min="8" max="8" width="12.88671875" customWidth="1"/>
+    <col min="9" max="9" width="16.77734375" customWidth="1"/>
+    <col min="10" max="10" width="18.77734375" customWidth="1"/>
+    <col min="11" max="11" width="15" customWidth="1"/>
+    <col min="12" max="12" width="19.44140625" customWidth="1"/>
+    <col min="13" max="13" width="23.5546875" customWidth="1"/>
+    <col min="16" max="16" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="C1" s="32" t="s">
+        <v>160</v>
+      </c>
+      <c r="D1" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="E1" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="32" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="30" t="s">
+      <c r="F1" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="G1" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
         <v>51</v>
       </c>
-      <c r="E1" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="F1" s="30" t="s">
-        <v>133</v>
-      </c>
-      <c r="G1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>52</v>
       </c>
-      <c r="I1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>2</v>
@@ -2914,778 +2986,979 @@
       <c r="C2" s="32">
         <v>2</v>
       </c>
-      <c r="D2" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="G2">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+      <c r="D2" s="32">
+        <v>0</v>
+      </c>
+      <c r="E2" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="H2">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
         <v>14</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>10</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
         <v>4</v>
       </c>
-      <c r="J2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>3</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C3" s="32">
         <v>1</v>
       </c>
-      <c r="D3" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="G3">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+      <c r="D3" s="32">
+        <v>1</v>
+      </c>
+      <c r="E3" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="H3">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>100</v>
+      </c>
+      <c r="J3">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="51" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" s="33" t="s">
+        <v>163</v>
+      </c>
+      <c r="N3" s="33">
         <v>7</v>
       </c>
-      <c r="H3">
-        <v>50</v>
-      </c>
-      <c r="I3">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-      <c r="L3" s="33" t="s">
-        <v>56</v>
-      </c>
-      <c r="M3" s="33">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P3" s="33" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q3" s="33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>4</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C4" s="32">
         <v>4</v>
       </c>
-      <c r="D4" s="30" t="s">
-        <v>149</v>
-      </c>
-      <c r="G4">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+      <c r="D4" s="32">
+        <v>0</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="H4">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
         <v>28</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
         <v>28</v>
       </c>
-      <c r="L4" s="33"/>
+      <c r="L4" s="51" t="b">
+        <v>0</v>
+      </c>
       <c r="M4" s="33"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N4" s="33"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="34">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>5</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C5" s="36">
-        <v>1</v>
-      </c>
-      <c r="D5" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="36">
+        <v>0</v>
+      </c>
+      <c r="E5" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="38">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>14</v>
+      </c>
+      <c r="I5" s="38"/>
+      <c r="J5" s="39">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>14</v>
+      </c>
+      <c r="L5" s="51" t="b">
+        <v>0</v>
+      </c>
+      <c r="M5" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="N5" s="33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>6</v>
+      </c>
+      <c r="B6" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="C6" s="32">
+        <v>0</v>
+      </c>
+      <c r="D6" s="32">
+        <v>1</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>153</v>
+      </c>
+      <c r="H6">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>1</v>
+      </c>
+      <c r="L6" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A7" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>7</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="C7" s="32">
+        <v>1</v>
+      </c>
+      <c r="D7" s="32">
+        <v>1</v>
+      </c>
+      <c r="E7" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="38">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>7</v>
-      </c>
-      <c r="H5" s="38"/>
-      <c r="I5" s="39">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>7</v>
-      </c>
-      <c r="L5" s="33" t="s">
+      <c r="H7">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>8</v>
+      </c>
+      <c r="J7" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>8</v>
+      </c>
+      <c r="L7" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>8</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="C8" s="32">
+        <v>14</v>
+      </c>
+      <c r="D8" s="32">
+        <v>4</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="G8" s="30" t="s">
+        <v>128</v>
+      </c>
+      <c r="H8">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>102</v>
+      </c>
+      <c r="I8">
+        <v>500</v>
+      </c>
+      <c r="J8" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A9" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>9</v>
+      </c>
+      <c r="B9" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="C9" s="32">
+        <v>1</v>
+      </c>
+      <c r="D9" s="32">
+        <v>1</v>
+      </c>
+      <c r="E9" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="M5" s="33">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="40">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>6</v>
-      </c>
-      <c r="B6" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="C6" s="32">
-        <v>1</v>
-      </c>
-      <c r="D6" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="G6">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>7</v>
-      </c>
-      <c r="I6" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" s="40">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>7</v>
-      </c>
-      <c r="B7" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="C7" s="32">
-        <v>14</v>
-      </c>
-      <c r="D7" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="E7" s="30" t="s">
-        <v>136</v>
-      </c>
-      <c r="F7" s="30" t="s">
-        <v>135</v>
-      </c>
-      <c r="G7">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>98</v>
-      </c>
-      <c r="H7">
-        <v>500</v>
-      </c>
-      <c r="I7" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="40">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+      <c r="H9">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
         <v>8</v>
       </c>
-      <c r="B8" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="C8" s="32">
-        <v>1</v>
-      </c>
-      <c r="D8" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="G8">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>7</v>
-      </c>
-      <c r="I8" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="40">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>9</v>
-      </c>
-      <c r="B9" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="C9" s="32">
-        <v>2</v>
-      </c>
-      <c r="D9" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>14</v>
-      </c>
-      <c r="I9" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J9" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>8</v>
+      </c>
+      <c r="L9" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>10</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C10" s="32">
         <v>9</v>
       </c>
-      <c r="D10" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="G10">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>63</v>
-      </c>
-      <c r="I10" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D10" s="32">
+        <v>3</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>66</v>
+      </c>
+      <c r="J10" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>66</v>
+      </c>
+      <c r="L10" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>11</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C11" s="32">
         <v>2</v>
       </c>
-      <c r="D11" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="G11">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+      <c r="D11" s="32">
+        <v>0</v>
+      </c>
+      <c r="E11" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="H11">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
         <v>14</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>100</v>
       </c>
-      <c r="I11" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J11" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>12</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C12" s="32">
+        <v>0</v>
+      </c>
+      <c r="D12" s="32">
+        <v>20</v>
+      </c>
+      <c r="E12" s="30">
+        <v>100</v>
+      </c>
+      <c r="H12">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>20</v>
+      </c>
+      <c r="J12" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>20</v>
+      </c>
+      <c r="L12" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A13" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>13</v>
+      </c>
+      <c r="B13" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="32">
         <v>4</v>
       </c>
-      <c r="D12" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="G12">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+      <c r="D13" s="32">
+        <v>0</v>
+      </c>
+      <c r="E13" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="H13">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
         <v>28</v>
       </c>
-      <c r="I12" s="41">
+      <c r="J13" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
         <v>28</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" s="40">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>13</v>
-      </c>
-      <c r="B13" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="C13" s="32">
-        <v>1</v>
-      </c>
-      <c r="D13" s="30" t="s">
-        <v>137</v>
-      </c>
-      <c r="G13">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>7</v>
-      </c>
-      <c r="I13" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L13" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>14</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C14" s="32">
         <v>2</v>
       </c>
-      <c r="D14" s="30" t="s">
-        <v>159</v>
-      </c>
-      <c r="G14">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+      <c r="D14" s="32">
+        <v>4</v>
+      </c>
+      <c r="E14" s="30" t="s">
+        <v>151</v>
+      </c>
+      <c r="H14">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>18</v>
+      </c>
+      <c r="J14" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>18</v>
+      </c>
+      <c r="L14" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A15" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>15</v>
+      </c>
+      <c r="B15" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="C15" s="32">
+        <v>2</v>
+      </c>
+      <c r="D15" s="32">
+        <v>2</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="H15">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>16</v>
+      </c>
+      <c r="J15" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>16</v>
+      </c>
+      <c r="L15" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A16" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>16</v>
+      </c>
+      <c r="B16" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="C16" s="32">
+        <v>1</v>
+      </c>
+      <c r="D16" s="32">
+        <v>1</v>
+      </c>
+      <c r="E16" s="30" t="s">
+        <v>154</v>
+      </c>
+      <c r="H16">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>8</v>
+      </c>
+      <c r="J16" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>8</v>
+      </c>
+      <c r="L16" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>17</v>
+      </c>
+      <c r="B17" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="C17" s="32">
+        <v>2</v>
+      </c>
+      <c r="D17" s="32">
+        <v>0</v>
+      </c>
+      <c r="E17" s="30">
+        <v>56</v>
+      </c>
+      <c r="H17">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
         <v>14</v>
       </c>
-      <c r="I14" s="41">
+      <c r="J17" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
         <v>14</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" s="40">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>15</v>
-      </c>
-      <c r="B15" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="C15" s="32">
-        <v>1</v>
-      </c>
-      <c r="D15" s="30" t="s">
+      <c r="L17" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>18</v>
+      </c>
+      <c r="B18" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="C18" s="32">
+        <v>3</v>
+      </c>
+      <c r="D18" s="32">
+        <v>1</v>
+      </c>
+      <c r="E18" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="F18" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="H18">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>22</v>
+      </c>
+      <c r="J18" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>22</v>
+      </c>
+      <c r="L18" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>19</v>
+      </c>
+      <c r="B19" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="C19" s="32">
+        <v>1</v>
+      </c>
+      <c r="D19" s="32">
+        <v>1</v>
+      </c>
+      <c r="E19" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="G15">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+      <c r="H19">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>8</v>
+      </c>
+      <c r="I19">
+        <v>20</v>
+      </c>
+      <c r="J19" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="42">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>20</v>
+      </c>
+      <c r="B20" s="43" t="s">
+        <v>116</v>
+      </c>
+      <c r="C20" s="44">
+        <v>1</v>
+      </c>
+      <c r="D20" s="44">
+        <v>0</v>
+      </c>
+      <c r="E20" s="45" t="s">
+        <v>66</v>
+      </c>
+      <c r="F20" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="G20" s="45"/>
+      <c r="H20" s="46">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
         <v>7</v>
       </c>
-      <c r="H15">
+      <c r="I20" s="46"/>
+      <c r="J20" s="47">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>7</v>
+      </c>
+      <c r="L20" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="34">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>21</v>
+      </c>
+      <c r="B21" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="C21" s="36">
+        <v>4</v>
+      </c>
+      <c r="D21" s="36">
+        <v>3</v>
+      </c>
+      <c r="E21" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="F21" s="37"/>
+      <c r="G21" s="37"/>
+      <c r="H21" s="38">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>31</v>
+      </c>
+      <c r="I21" s="38">
+        <v>100</v>
+      </c>
+      <c r="J21" s="39">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+      <c r="L21" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>22</v>
+      </c>
+      <c r="B22" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="C22" s="32">
+        <v>2</v>
+      </c>
+      <c r="D22" s="32">
+        <v>2</v>
+      </c>
+      <c r="E22" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="H22">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>16</v>
+      </c>
+      <c r="I22">
+        <v>200</v>
+      </c>
+      <c r="J22" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+      <c r="L22" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>23</v>
+      </c>
+      <c r="B23" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="C23" s="32">
+        <v>1</v>
+      </c>
+      <c r="D23" s="32">
+        <v>1</v>
+      </c>
+      <c r="E23" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="H23">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>8</v>
+      </c>
+      <c r="I23">
         <v>20</v>
       </c>
-      <c r="I15" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="40">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+      <c r="J23" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+      <c r="L23" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>24</v>
+      </c>
+      <c r="B24" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="C24" s="32">
+        <v>0</v>
+      </c>
+      <c r="D24" s="32">
+        <v>2</v>
+      </c>
+      <c r="E24" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="H24">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>2</v>
+      </c>
+      <c r="J24" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>2</v>
+      </c>
+      <c r="L24" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>25</v>
+      </c>
+      <c r="B25" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25" s="32">
+        <v>1</v>
+      </c>
+      <c r="D25" s="32">
+        <v>0</v>
+      </c>
+      <c r="E25" s="30" t="s">
+        <v>153</v>
+      </c>
+      <c r="H25">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>7</v>
+      </c>
+      <c r="J25" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>7</v>
+      </c>
+      <c r="L25" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>26</v>
+      </c>
+      <c r="B26" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="C26" s="32">
+        <v>0</v>
+      </c>
+      <c r="D26" s="32">
+        <v>2</v>
+      </c>
+      <c r="E26" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="H26">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>2</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>2</v>
+      </c>
+      <c r="L26" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>27</v>
+      </c>
+      <c r="B27" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="C27" s="32">
+        <v>2</v>
+      </c>
+      <c r="D27" s="32">
+        <v>2</v>
+      </c>
+      <c r="E27" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="H27">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
         <v>16</v>
       </c>
-      <c r="B16" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="C16" s="32">
+      <c r="J27" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>16</v>
+      </c>
+      <c r="L27" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>28</v>
+      </c>
+      <c r="B28" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="C28" s="32">
+        <v>4</v>
+      </c>
+      <c r="D28" s="32">
+        <v>3</v>
+      </c>
+      <c r="E28" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="F28" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="G28" s="30" t="s">
+        <v>128</v>
+      </c>
+      <c r="H28">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>31</v>
+      </c>
+      <c r="J28" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>31</v>
+      </c>
+      <c r="L28" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>29</v>
+      </c>
+      <c r="B29" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="C29" s="32">
+        <v>0</v>
+      </c>
+      <c r="D29" s="32">
+        <v>1</v>
+      </c>
+      <c r="E29" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="H29">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>1</v>
+      </c>
+      <c r="J29" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>1</v>
+      </c>
+      <c r="L29" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>30</v>
+      </c>
+      <c r="B30" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="C30" s="32">
+        <v>6</v>
+      </c>
+      <c r="D30" s="32">
+        <v>0</v>
+      </c>
+      <c r="E30" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="H30">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>42</v>
+      </c>
+      <c r="J30" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>42</v>
+      </c>
+      <c r="L30" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>31</v>
+      </c>
+      <c r="B31" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="C31" s="32">
+        <v>1</v>
+      </c>
+      <c r="D31" s="32">
+        <v>0</v>
+      </c>
+      <c r="E31" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="F31" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="H31">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>7</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>7</v>
+      </c>
+      <c r="K31" t="s">
+        <v>18</v>
+      </c>
+      <c r="L31" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>32</v>
+      </c>
+      <c r="B32" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="C32" s="32">
         <v>2</v>
       </c>
-      <c r="D16" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="G16">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+      <c r="D32" s="32">
+        <v>0</v>
+      </c>
+      <c r="E32" s="30">
+        <v>56</v>
+      </c>
+      <c r="H32">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
         <v>14</v>
       </c>
-      <c r="I16" s="41">
+      <c r="J32" s="41">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
         <v>14</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="40">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>17</v>
-      </c>
-      <c r="B17" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="C17" s="32">
-        <v>1</v>
-      </c>
-      <c r="D17" s="30" t="s">
-        <v>165</v>
-      </c>
-      <c r="G17">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>7</v>
-      </c>
-      <c r="I17" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="40">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>18</v>
-      </c>
-      <c r="B18" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="C18" s="32">
-        <v>2</v>
-      </c>
-      <c r="D18" s="30">
-        <v>56</v>
-      </c>
-      <c r="G18">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>14</v>
-      </c>
-      <c r="I18" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="40">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>19</v>
-      </c>
-      <c r="B19" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="C19" s="32">
-        <v>2</v>
-      </c>
-      <c r="D19" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="E19" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="G19">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>14</v>
-      </c>
-      <c r="I19" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="40">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>20</v>
-      </c>
-      <c r="B20" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="C20" s="32">
-        <v>1</v>
-      </c>
-      <c r="D20" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="G20">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>7</v>
-      </c>
-      <c r="I20" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="42">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>21</v>
-      </c>
-      <c r="B21" s="43" t="s">
-        <v>122</v>
-      </c>
-      <c r="C21" s="44">
-        <v>1</v>
-      </c>
-      <c r="D21" s="45" t="s">
-        <v>69</v>
-      </c>
-      <c r="E21" s="45" t="s">
-        <v>142</v>
-      </c>
-      <c r="F21" s="45"/>
-      <c r="G21" s="46">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>7</v>
-      </c>
-      <c r="H21" s="46"/>
-      <c r="I21" s="47">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="34">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>22</v>
-      </c>
-      <c r="B22" s="35" t="s">
-        <v>123</v>
-      </c>
-      <c r="C22" s="36">
-        <v>4</v>
-      </c>
-      <c r="D22" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="E22" s="37"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="38">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>28</v>
-      </c>
-      <c r="H22" s="38">
-        <v>100</v>
-      </c>
-      <c r="I22" s="39">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="40">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>23</v>
-      </c>
-      <c r="B23" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="C23" s="32">
-        <v>2</v>
-      </c>
-      <c r="D23" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="G23">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>14</v>
-      </c>
-      <c r="I23" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="40">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>24</v>
-      </c>
-      <c r="B24" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="C24" s="32">
-        <v>1</v>
-      </c>
-      <c r="D24" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="G24">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>7</v>
-      </c>
-      <c r="H24">
-        <v>20</v>
-      </c>
-      <c r="I24" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="40">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>25</v>
-      </c>
-      <c r="B25" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="C25" s="32">
-        <v>1</v>
-      </c>
-      <c r="D25" s="30" t="s">
-        <v>164</v>
-      </c>
-      <c r="G25">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>7</v>
-      </c>
-      <c r="I25" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="40">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>26</v>
-      </c>
-      <c r="B26" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="C26" s="32">
-        <v>2</v>
-      </c>
-      <c r="D26" s="30" t="s">
-        <v>72</v>
-      </c>
-      <c r="G26">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>14</v>
-      </c>
-      <c r="I26" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="40">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>27</v>
-      </c>
-      <c r="B27" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="C27" s="32">
-        <v>4</v>
-      </c>
-      <c r="D27" s="30" t="s">
-        <v>73</v>
-      </c>
-      <c r="E27" s="30" t="s">
-        <v>139</v>
-      </c>
-      <c r="F27" s="30" t="s">
-        <v>135</v>
-      </c>
-      <c r="G27">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>28</v>
-      </c>
-      <c r="I27" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="40">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>28</v>
-      </c>
-      <c r="B28" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="C28" s="32">
-        <v>6</v>
-      </c>
-      <c r="D28" s="30" t="s">
-        <v>74</v>
-      </c>
-      <c r="G28">
-        <f>Table2[[#This Row],[Quantity]]*M5</f>
-        <v>12</v>
-      </c>
-      <c r="I28" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" s="40">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>29</v>
-      </c>
-      <c r="B29" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="C29" s="32">
-        <v>6</v>
-      </c>
-      <c r="D29" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="G29">
-        <f>Table2[[#This Row],[Quantity]]*($M$3-M6)</f>
-        <v>42</v>
-      </c>
-      <c r="I29" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="40">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>30</v>
-      </c>
-      <c r="B30" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="C30" s="32">
-        <v>1</v>
-      </c>
-      <c r="D30" s="30" t="s">
-        <v>76</v>
-      </c>
-      <c r="E30" s="30" t="s">
-        <v>150</v>
-      </c>
-      <c r="G30">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>7</v>
-      </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
-      <c r="I30" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>7</v>
-      </c>
-      <c r="J30" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="40">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>31</v>
-      </c>
-      <c r="B31" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="C31" s="32">
-        <v>2</v>
-      </c>
-      <c r="D31" s="30">
-        <v>56</v>
-      </c>
-      <c r="G31">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>14</v>
-      </c>
-      <c r="I31" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" s="40">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>32</v>
-      </c>
-      <c r="B32" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="C32" s="32">
-        <v>1</v>
-      </c>
-      <c r="D32" s="30" t="s">
-        <v>140</v>
-      </c>
-      <c r="G32">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>7</v>
-      </c>
-      <c r="I32" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>7</v>
+      <c r="L32" s="51" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
@@ -3694,33 +3967,27 @@
         <v>33</v>
       </c>
       <c r="B33" s="31" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C33" s="32">
-        <v>4</v>
-      </c>
-      <c r="D33" s="30" t="s">
-        <v>78</v>
+        <v>0</v>
+      </c>
+      <c r="D33" s="32">
+        <v>2</v>
       </c>
       <c r="E33" s="30" t="s">
-        <v>142</v>
-      </c>
-      <c r="F33" s="30" t="s">
-        <v>141</v>
-      </c>
-      <c r="G33">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>28</v>
-      </c>
-      <c r="I33" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>28</v>
-      </c>
-      <c r="J33" t="s">
-        <v>160</v>
-      </c>
-      <c r="L33" t="s">
-        <v>19</v>
+        <v>179</v>
+      </c>
+      <c r="H33">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>2</v>
+      </c>
+      <c r="J33" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>2</v>
+      </c>
+      <c r="L33" s="51" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
@@ -3729,21 +3996,30 @@
         <v>34</v>
       </c>
       <c r="B34" s="31" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C34" s="32">
         <v>1</v>
       </c>
-      <c r="D34" s="30" t="s">
-        <v>138</v>
-      </c>
-      <c r="G34">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>7</v>
-      </c>
-      <c r="I34" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>7</v>
+      <c r="D34" s="32">
+        <v>1</v>
+      </c>
+      <c r="E34" s="30" t="s">
+        <v>164</v>
+      </c>
+      <c r="H34">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>8</v>
+      </c>
+      <c r="I34">
+        <v>50</v>
+      </c>
+      <c r="J34" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+      <c r="L34" s="51" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
@@ -3752,21 +4028,27 @@
         <v>35</v>
       </c>
       <c r="B35" s="31" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C35" s="32">
         <v>1</v>
       </c>
-      <c r="D35" s="30">
-        <v>1100</v>
-      </c>
-      <c r="G35">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>7</v>
-      </c>
-      <c r="I35" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>7</v>
+      <c r="D35" s="32">
+        <v>1</v>
+      </c>
+      <c r="E35" s="30" t="s">
+        <v>132</v>
+      </c>
+      <c r="H35">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>8</v>
+      </c>
+      <c r="J35" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>8</v>
+      </c>
+      <c r="L35" s="51" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
@@ -3775,1551 +4057,2004 @@
         <v>36</v>
       </c>
       <c r="B36" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="C36" s="32">
+        <v>4</v>
+      </c>
+      <c r="D36" s="32">
+        <v>8</v>
+      </c>
+      <c r="E36" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="F36" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="G36" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="H36">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>36</v>
+      </c>
+      <c r="I36">
+        <v>100</v>
+      </c>
+      <c r="J36" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+      <c r="K36" t="s">
+        <v>152</v>
+      </c>
+      <c r="L36" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>37</v>
+      </c>
+      <c r="B37" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="C37" s="32">
+        <v>1</v>
+      </c>
+      <c r="D37" s="32">
+        <v>1</v>
+      </c>
+      <c r="E37" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="H37">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>8</v>
+      </c>
+      <c r="J37" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>8</v>
+      </c>
+      <c r="L37" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>38</v>
+      </c>
+      <c r="B38" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="C38" s="32">
+        <v>1</v>
+      </c>
+      <c r="D38" s="32">
+        <v>1</v>
+      </c>
+      <c r="E38" s="30">
+        <v>1100</v>
+      </c>
+      <c r="H38">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>8</v>
+      </c>
+      <c r="J38" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>8</v>
+      </c>
+      <c r="L38" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="42">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>39</v>
+      </c>
+      <c r="B39" s="43" t="s">
+        <v>117</v>
+      </c>
+      <c r="C39" s="44">
+        <v>1</v>
+      </c>
+      <c r="D39" s="44">
+        <v>6</v>
+      </c>
+      <c r="E39" s="45" t="s">
+        <v>62</v>
+      </c>
+      <c r="F39" s="45"/>
+      <c r="G39" s="45"/>
+      <c r="H39" s="46">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>13</v>
+      </c>
+      <c r="I39" s="46"/>
+      <c r="J39" s="47">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>13</v>
+      </c>
+      <c r="L39" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" s="34">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>40</v>
+      </c>
+      <c r="B40" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="C40" s="36">
+        <v>2</v>
+      </c>
+      <c r="D40" s="36">
+        <v>6</v>
+      </c>
+      <c r="E40" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="F40" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="G40" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="H40" s="38">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>20</v>
+      </c>
+      <c r="I40" s="38">
+        <v>40</v>
+      </c>
+      <c r="J40" s="39">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+      <c r="K40" t="s">
+        <v>18</v>
+      </c>
+      <c r="L40" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>41</v>
+      </c>
+      <c r="B41" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="C41" s="32">
+        <v>3</v>
+      </c>
+      <c r="D41" s="32">
+        <v>0</v>
+      </c>
+      <c r="E41" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="F41" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="H41">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>21</v>
+      </c>
+      <c r="I41">
+        <v>200</v>
+      </c>
+      <c r="J41" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+      <c r="L41" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>42</v>
+      </c>
+      <c r="B42" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="C42" s="32">
+        <v>0</v>
+      </c>
+      <c r="D42" s="32">
+        <v>1</v>
+      </c>
+      <c r="E42" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="H42">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>1</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>1</v>
+      </c>
+      <c r="L42" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>43</v>
+      </c>
+      <c r="B43" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="C43" s="32">
+        <v>0</v>
+      </c>
+      <c r="D43" s="32">
+        <v>1</v>
+      </c>
+      <c r="E43" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="H43">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>1</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>1</v>
+      </c>
+      <c r="L43" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>44</v>
+      </c>
+      <c r="B44" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="C44" s="32">
+        <v>0</v>
+      </c>
+      <c r="D44" s="32">
+        <v>1</v>
+      </c>
+      <c r="E44" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="H44">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>1</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>1</v>
+      </c>
+      <c r="L44" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>45</v>
+      </c>
+      <c r="B45" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="C45" s="32">
+        <v>0</v>
+      </c>
+      <c r="D45" s="32">
+        <v>5</v>
+      </c>
+      <c r="E45" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="H45">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>5</v>
+      </c>
+      <c r="I45">
+        <v>100</v>
+      </c>
+      <c r="J45" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+      <c r="L45" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A46" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>46</v>
+      </c>
+      <c r="B46" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="C46" s="32">
+        <v>0</v>
+      </c>
+      <c r="D46" s="32">
+        <v>1</v>
+      </c>
+      <c r="E46" s="30">
+        <v>470</v>
+      </c>
+      <c r="H46">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>1</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>1</v>
+      </c>
+      <c r="L46" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A47" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>47</v>
+      </c>
+      <c r="B47" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="C47" s="32">
+        <v>0</v>
+      </c>
+      <c r="D47" s="32">
+        <v>1</v>
+      </c>
+      <c r="E47" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="H47">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>1</v>
+      </c>
+      <c r="I47">
+        <v>50</v>
+      </c>
+      <c r="J47" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+      <c r="L47" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A48" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>48</v>
+      </c>
+      <c r="B48" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="C48" s="32">
+        <v>11</v>
+      </c>
+      <c r="D48" s="32">
+        <v>10</v>
+      </c>
+      <c r="E48" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="H48">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>87</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>87</v>
+      </c>
+      <c r="K48" t="s">
+        <v>18</v>
+      </c>
+      <c r="L48" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A49" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>49</v>
+      </c>
+      <c r="B49" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="C49" s="32">
+        <v>2</v>
+      </c>
+      <c r="D49" s="32">
+        <v>2</v>
+      </c>
+      <c r="E49" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="H49">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>16</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>16</v>
+      </c>
+      <c r="L49" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A50" s="40">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>50</v>
+      </c>
+      <c r="B50" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="C50" s="32">
+        <v>5</v>
+      </c>
+      <c r="D50" s="32">
+        <v>0</v>
+      </c>
+      <c r="E50" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="H50">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>35</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50" s="41">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>35</v>
+      </c>
+      <c r="K50" t="s">
+        <v>18</v>
+      </c>
+      <c r="L50" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A51" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>51</v>
+      </c>
+      <c r="B51" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="C51" s="32">
+        <v>1</v>
+      </c>
+      <c r="D51" s="32">
+        <v>3</v>
+      </c>
+      <c r="E51" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="H51">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>10</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>10</v>
+      </c>
+      <c r="K51" t="s">
+        <v>184</v>
+      </c>
+      <c r="L51" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A52" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>52</v>
+      </c>
+      <c r="B52" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="C52" s="32">
+        <v>1</v>
+      </c>
+      <c r="D52" s="32">
+        <v>1</v>
+      </c>
+      <c r="E52" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="H52">
+        <v>10</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>10</v>
+      </c>
+      <c r="K52" t="s">
+        <v>18</v>
+      </c>
+      <c r="L52" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A53" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>53</v>
+      </c>
+      <c r="B53" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="C53" s="32">
+        <v>1</v>
+      </c>
+      <c r="D53" s="32">
+        <v>0</v>
+      </c>
+      <c r="E53" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="H53">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>7</v>
+      </c>
+      <c r="I53">
+        <v>10</v>
+      </c>
+      <c r="J53">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+      <c r="L53" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A54" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>54</v>
+      </c>
+      <c r="B54" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="C54" s="32">
+        <v>1</v>
+      </c>
+      <c r="D54" s="32">
+        <v>1</v>
+      </c>
+      <c r="E54" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="H54">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>8</v>
+      </c>
+      <c r="I54">
+        <v>50</v>
+      </c>
+      <c r="J54">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+      <c r="L54" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A55" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>55</v>
+      </c>
+      <c r="B55" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="C55" s="32">
+        <v>1</v>
+      </c>
+      <c r="D55" s="32">
+        <v>0</v>
+      </c>
+      <c r="E55" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="H55">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>7</v>
+      </c>
+      <c r="I55">
+        <v>1</v>
+      </c>
+      <c r="J55">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>6</v>
+      </c>
+      <c r="L55" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A56" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>56</v>
+      </c>
+      <c r="B56" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="C56" s="32">
+        <v>1</v>
+      </c>
+      <c r="D56" s="32">
+        <v>1</v>
+      </c>
+      <c r="E56" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="H56">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>8</v>
+      </c>
+      <c r="I56">
+        <v>3</v>
+      </c>
+      <c r="J56">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>5</v>
+      </c>
+      <c r="L56" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A57" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>57</v>
+      </c>
+      <c r="B57" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="C57" s="32">
+        <v>1</v>
+      </c>
+      <c r="D57" s="32">
+        <v>1</v>
+      </c>
+      <c r="E57" s="50" t="s">
+        <v>155</v>
+      </c>
+      <c r="H57">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>8</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>8</v>
+      </c>
+      <c r="L57" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A58" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>58</v>
+      </c>
+      <c r="B58" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="C58" s="32">
+        <v>2</v>
+      </c>
+      <c r="D58" s="32">
+        <v>0</v>
+      </c>
+      <c r="E58" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="H58">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>14</v>
+      </c>
+      <c r="I58">
+        <v>14</v>
+      </c>
+      <c r="J58">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+      <c r="L58" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A59" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>59</v>
+      </c>
+      <c r="B59" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="C59" s="32">
+        <v>1</v>
+      </c>
+      <c r="D59" s="32">
+        <v>1</v>
+      </c>
+      <c r="E59" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="H59">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>8</v>
+      </c>
+      <c r="I59">
+        <v>50</v>
+      </c>
+      <c r="J59">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+      <c r="L59" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A60" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>60</v>
+      </c>
+      <c r="B60" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="C60" s="32">
+        <v>1</v>
+      </c>
+      <c r="D60" s="32">
+        <v>1</v>
+      </c>
+      <c r="E60" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="H60">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>8</v>
+      </c>
+      <c r="I60">
+        <v>50</v>
+      </c>
+      <c r="J60">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+      <c r="L60" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A61" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>61</v>
+      </c>
+      <c r="B61" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="C61" s="32">
+        <v>1</v>
+      </c>
+      <c r="D61" s="32">
+        <v>0</v>
+      </c>
+      <c r="E61" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="C36" s="32">
-        <v>1</v>
-      </c>
-      <c r="D36" s="30" t="s">
+      <c r="H61">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>7</v>
+      </c>
+      <c r="I61">
+        <v>4</v>
+      </c>
+      <c r="J61">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>3</v>
+      </c>
+      <c r="L61" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A62" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>62</v>
+      </c>
+      <c r="B62" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="C62" s="32">
+        <v>1</v>
+      </c>
+      <c r="D62" s="32">
+        <v>0</v>
+      </c>
+      <c r="E62" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="H62">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>7</v>
+      </c>
+      <c r="I62">
+        <v>4</v>
+      </c>
+      <c r="J62">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>3</v>
+      </c>
+      <c r="L62" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A63" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>63</v>
+      </c>
+      <c r="B63" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="C63" s="32">
+        <v>6</v>
+      </c>
+      <c r="D63" s="32">
+        <v>0</v>
+      </c>
+      <c r="E63" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="H63">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>42</v>
+      </c>
+      <c r="I63">
+        <v>18</v>
+      </c>
+      <c r="J63">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>24</v>
+      </c>
+      <c r="L63" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A64" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>64</v>
       </c>
-      <c r="G36">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+      <c r="B64" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="C64" s="32">
+        <v>1</v>
+      </c>
+      <c r="D64" s="32">
+        <v>1</v>
+      </c>
+      <c r="E64" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="H64">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>8</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>8</v>
+      </c>
+      <c r="L64" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A65" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>65</v>
+      </c>
+      <c r="B65" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="C65" s="32">
+        <v>1</v>
+      </c>
+      <c r="D65" s="32">
+        <v>3</v>
+      </c>
+      <c r="E65" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="H65">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>10</v>
+      </c>
+      <c r="I65">
+        <v>5</v>
+      </c>
+      <c r="J65">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>5</v>
+      </c>
+      <c r="L65" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A66" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>66</v>
+      </c>
+      <c r="B66" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="C66" s="32">
+        <v>5</v>
+      </c>
+      <c r="D66" s="32">
+        <v>5</v>
+      </c>
+      <c r="E66" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="H66">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>40</v>
+      </c>
+      <c r="I66">
+        <v>100</v>
+      </c>
+      <c r="J66">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+      <c r="L66" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A67" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>67</v>
+      </c>
+      <c r="B67" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="C67" s="32">
+        <v>1</v>
+      </c>
+      <c r="D67" s="32">
+        <v>1</v>
+      </c>
+      <c r="E67" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="H67">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>8</v>
+      </c>
+      <c r="I67">
+        <v>3</v>
+      </c>
+      <c r="J67">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>5</v>
+      </c>
+      <c r="L67" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A68" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>68</v>
+      </c>
+      <c r="B68" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="C68" s="32">
+        <v>1</v>
+      </c>
+      <c r="D68" s="32">
+        <v>0</v>
+      </c>
+      <c r="E68" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="H68">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
         <v>7</v>
       </c>
-      <c r="I36" s="41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="42">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>37</v>
-      </c>
-      <c r="B37" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="C37" s="44">
-        <v>1</v>
-      </c>
-      <c r="D37" s="45" t="s">
-        <v>55</v>
-      </c>
-      <c r="E37" s="45"/>
-      <c r="F37" s="45"/>
-      <c r="G37" s="46">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>7</v>
-      </c>
-      <c r="H37" s="46"/>
-      <c r="I37" s="47">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>38</v>
-      </c>
-      <c r="B38" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="C38" s="32">
-        <v>1</v>
-      </c>
-      <c r="D38" s="30" t="s">
-        <v>80</v>
-      </c>
-      <c r="F38" s="30" t="s">
-        <v>163</v>
-      </c>
-      <c r="G38">
-        <f>Table2[[#This Row],[Quantity]]*M3</f>
-        <v>7</v>
-      </c>
-      <c r="H38">
-        <v>0</v>
-      </c>
-      <c r="I38">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>7</v>
-      </c>
-      <c r="J38" t="s">
-        <v>19</v>
-      </c>
-      <c r="K38" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>39</v>
-      </c>
-      <c r="B39" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="C39" s="32">
-        <v>1</v>
-      </c>
-      <c r="D39" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="F39" s="30" t="s">
-        <v>163</v>
-      </c>
-      <c r="G39">
-        <f>Table2[[#This Row],[Quantity]]*M5</f>
-        <v>2</v>
-      </c>
-      <c r="H39">
-        <v>0</v>
-      </c>
-      <c r="I39">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>2</v>
-      </c>
-      <c r="J39" t="s">
-        <v>19</v>
-      </c>
-      <c r="K39" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>40</v>
-      </c>
-      <c r="B40" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="C40" s="32">
+      <c r="I68">
         <v>3</v>
       </c>
-      <c r="D40" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="E40" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="G40">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>21</v>
-      </c>
-      <c r="H40">
-        <v>40</v>
-      </c>
-      <c r="I40">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>41</v>
-      </c>
-      <c r="B41" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="C41" s="32">
-        <v>1</v>
-      </c>
-      <c r="D41" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="G41">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>7</v>
-      </c>
-      <c r="H41">
-        <v>0</v>
-      </c>
-      <c r="I41">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>7</v>
-      </c>
-      <c r="J41" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>42</v>
-      </c>
-      <c r="B42" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="C42" s="32">
-        <v>2</v>
-      </c>
-      <c r="D42" s="30" t="s">
-        <v>76</v>
-      </c>
-      <c r="G42">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>14</v>
-      </c>
-      <c r="H42">
-        <v>0</v>
-      </c>
-      <c r="I42">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>14</v>
-      </c>
-      <c r="J42" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>43</v>
-      </c>
-      <c r="B43" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="C43" s="32">
-        <v>1</v>
-      </c>
-      <c r="D43" s="30" t="s">
-        <v>80</v>
-      </c>
-      <c r="E43" s="30" t="s">
-        <v>139</v>
-      </c>
-      <c r="F43" s="30" t="s">
-        <v>143</v>
-      </c>
-      <c r="G43">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>7</v>
-      </c>
-      <c r="H43">
-        <v>30</v>
-      </c>
-      <c r="I43">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-      <c r="J43" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A44" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>44</v>
-      </c>
-      <c r="B44" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="C44" s="32">
+      <c r="J68">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>4</v>
+      </c>
+      <c r="L68" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A69" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>69</v>
+      </c>
+      <c r="B69" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="C69" s="32">
+        <v>1</v>
+      </c>
+      <c r="D69" s="32">
+        <v>1</v>
+      </c>
+      <c r="E69" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="H69">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>8</v>
+      </c>
+      <c r="I69">
         <v>10</v>
       </c>
-      <c r="D44" s="30" t="s">
-        <v>81</v>
-      </c>
-      <c r="G44">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
+      <c r="J69">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+      <c r="L69" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A70" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>70</v>
       </c>
-      <c r="H44">
-        <v>0</v>
-      </c>
-      <c r="I44">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>70</v>
-      </c>
-      <c r="J44" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A45" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>45</v>
-      </c>
-      <c r="B45" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="C45" s="32">
-        <v>3</v>
-      </c>
-      <c r="D45" s="30" t="s">
-        <v>76</v>
-      </c>
-      <c r="G45">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>21</v>
-      </c>
-      <c r="H45">
-        <v>0</v>
-      </c>
-      <c r="I45">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>21</v>
-      </c>
-      <c r="J45" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A46" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>46</v>
-      </c>
-      <c r="B46" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="C46" s="32">
-        <v>1</v>
-      </c>
-      <c r="D46" s="30" t="s">
-        <v>83</v>
-      </c>
-      <c r="G46">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>7</v>
-      </c>
-      <c r="H46">
-        <v>0</v>
-      </c>
-      <c r="I46">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>7</v>
-      </c>
-      <c r="J46" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A47" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>47</v>
-      </c>
-      <c r="B47" s="31" t="s">
-        <v>84</v>
-      </c>
-      <c r="C47" s="32">
-        <v>1</v>
-      </c>
-      <c r="D47" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="G47">
-        <f>Table2[[#This Row],[Quantity]]*M5</f>
-        <v>2</v>
-      </c>
-      <c r="H47">
-        <v>0</v>
-      </c>
-      <c r="I47">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>2</v>
-      </c>
-      <c r="J47" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A48" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>48</v>
-      </c>
-      <c r="B48" s="31" t="s">
-        <v>84</v>
-      </c>
-      <c r="C48" s="32">
-        <v>1</v>
-      </c>
-      <c r="D48" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="G48">
-        <f>Table2[[#This Row],[Quantity]]*($M$3-M5)</f>
-        <v>5</v>
-      </c>
-      <c r="H48">
-        <v>10</v>
-      </c>
-      <c r="I48">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A49" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>49</v>
-      </c>
-      <c r="B49" s="31" t="s">
-        <v>87</v>
-      </c>
-      <c r="C49" s="32">
-        <v>1</v>
-      </c>
-      <c r="D49" s="30" t="s">
-        <v>130</v>
-      </c>
-      <c r="G49">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>7</v>
-      </c>
-      <c r="H49">
-        <v>50</v>
-      </c>
-      <c r="I49">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A50" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>50</v>
-      </c>
-      <c r="B50" s="31" t="s">
-        <v>88</v>
-      </c>
-      <c r="C50" s="32">
-        <v>1</v>
-      </c>
-      <c r="D50" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="G50">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>7</v>
-      </c>
-      <c r="H50">
-        <v>3</v>
-      </c>
-      <c r="I50">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>51</v>
-      </c>
-      <c r="B51" s="31" t="s">
-        <v>90</v>
-      </c>
-      <c r="C51" s="32">
-        <v>1</v>
-      </c>
-      <c r="D51" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="G51">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>7</v>
-      </c>
-      <c r="H51">
-        <v>3</v>
-      </c>
-      <c r="I51">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A52" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>52</v>
-      </c>
-      <c r="B52" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="C52" s="32">
-        <v>1</v>
-      </c>
-      <c r="D52" s="50" t="s">
-        <v>168</v>
-      </c>
-      <c r="G52">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>7</v>
-      </c>
-      <c r="H52">
-        <v>0</v>
-      </c>
-      <c r="I52">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A53" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>53</v>
-      </c>
-      <c r="B53" s="31" t="s">
-        <v>146</v>
-      </c>
-      <c r="C53" s="32">
-        <v>2</v>
-      </c>
-      <c r="D53" s="30" t="s">
-        <v>147</v>
-      </c>
-      <c r="G53">
-        <v>12</v>
-      </c>
-      <c r="H53">
-        <v>14</v>
-      </c>
-      <c r="I53">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A54" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>54</v>
-      </c>
-      <c r="B54" s="31" t="s">
-        <v>92</v>
-      </c>
-      <c r="C54" s="32">
-        <v>1</v>
-      </c>
-      <c r="D54" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="G54">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>7</v>
-      </c>
-      <c r="H54">
-        <v>50</v>
-      </c>
-      <c r="I54">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A55" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>55</v>
-      </c>
-      <c r="B55" s="31" t="s">
-        <v>92</v>
-      </c>
-      <c r="C55" s="32">
-        <v>1</v>
-      </c>
-      <c r="D55" s="30" t="s">
-        <v>94</v>
-      </c>
-      <c r="G55">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>7</v>
-      </c>
-      <c r="H55">
-        <v>50</v>
-      </c>
-      <c r="I55">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A56" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>56</v>
-      </c>
-      <c r="B56" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="C56" s="32">
-        <v>1</v>
-      </c>
-      <c r="D56" s="30" t="s">
-        <v>129</v>
-      </c>
-      <c r="G56">
-        <v>2</v>
-      </c>
-      <c r="H56">
-        <v>4</v>
-      </c>
-      <c r="I56">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A57" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>57</v>
-      </c>
-      <c r="B57" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="C57" s="32">
-        <v>1</v>
-      </c>
-      <c r="D57" s="30" t="s">
-        <v>96</v>
-      </c>
-      <c r="G57">
-        <f>Table2[[#This Row],[Quantity]]*M6</f>
-        <v>0</v>
-      </c>
-      <c r="H57">
-        <v>4</v>
-      </c>
-      <c r="I57">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A58" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>58</v>
-      </c>
-      <c r="B58" s="31" t="s">
-        <v>97</v>
-      </c>
-      <c r="C58" s="32">
-        <v>6</v>
-      </c>
-      <c r="D58" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="G58">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>42</v>
-      </c>
-      <c r="H58">
-        <v>21</v>
-      </c>
-      <c r="I58">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A59" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>59</v>
-      </c>
-      <c r="B59" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="C59" s="32">
-        <v>1</v>
-      </c>
-      <c r="D59" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="G59">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>7</v>
-      </c>
-      <c r="H59">
-        <v>0</v>
-      </c>
-      <c r="I59">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A60" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>60</v>
-      </c>
-      <c r="B60" s="31" t="s">
-        <v>99</v>
-      </c>
-      <c r="C60" s="32">
-        <v>1</v>
-      </c>
-      <c r="D60" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="F60" s="30" t="s">
-        <v>167</v>
-      </c>
-      <c r="G60">
-        <f>Table2[[#This Row],[Quantity]]*M5</f>
-        <v>2</v>
-      </c>
-      <c r="H60">
-        <v>1</v>
-      </c>
-      <c r="I60">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>1</v>
-      </c>
-      <c r="J60" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A61" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>61</v>
-      </c>
-      <c r="B61" s="31" t="s">
-        <v>99</v>
-      </c>
-      <c r="C61" s="32">
-        <v>1</v>
-      </c>
-      <c r="D61" s="30" t="s">
-        <v>166</v>
-      </c>
-      <c r="F61" s="30" t="s">
-        <v>167</v>
-      </c>
-      <c r="G61">
-        <v>1</v>
-      </c>
-      <c r="H61">
-        <v>0</v>
-      </c>
-      <c r="I61">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>1</v>
-      </c>
-      <c r="J61" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A62" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>62</v>
-      </c>
-      <c r="B62" s="31" t="s">
-        <v>99</v>
-      </c>
-      <c r="C62" s="32">
-        <v>1</v>
-      </c>
-      <c r="D62" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="G62">
-        <f>Table2[[#This Row],[Quantity]]*($M$3-M5)</f>
-        <v>5</v>
-      </c>
-      <c r="H62">
-        <v>5</v>
-      </c>
-      <c r="I62">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A63" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>63</v>
-      </c>
-      <c r="B63" s="31" t="s">
-        <v>102</v>
-      </c>
-      <c r="C63" s="32">
-        <v>5</v>
-      </c>
-      <c r="D63" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="G63">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>35</v>
-      </c>
-      <c r="H63">
-        <v>100</v>
-      </c>
-      <c r="I63">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A64" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>64</v>
-      </c>
-      <c r="B64" s="31" t="s">
+      <c r="B70" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="C64" s="32">
-        <v>1</v>
-      </c>
-      <c r="D64" s="30" t="s">
+      <c r="C70" s="32">
+        <v>1</v>
+      </c>
+      <c r="D70" s="32">
+        <v>1</v>
+      </c>
+      <c r="E70" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="G64">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>7</v>
-      </c>
-      <c r="H64">
-        <v>3</v>
-      </c>
-      <c r="I64">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A65" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>65</v>
-      </c>
-      <c r="B65" s="31" t="s">
+      <c r="H70">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>8</v>
+      </c>
+      <c r="I70">
+        <v>20</v>
+      </c>
+      <c r="J70">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+      <c r="L70" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A71" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>71</v>
+      </c>
+      <c r="B71" s="31" t="s">
         <v>106</v>
-      </c>
-      <c r="C65" s="32">
-        <v>1</v>
-      </c>
-      <c r="D65" s="30" t="s">
-        <v>107</v>
-      </c>
-      <c r="G65">
-        <f>Table2[[#This Row],[Quantity]]*($M$3-M7)</f>
-        <v>7</v>
-      </c>
-      <c r="H65">
-        <v>3</v>
-      </c>
-      <c r="I65">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A66" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>66</v>
-      </c>
-      <c r="B66" s="31" t="s">
-        <v>108</v>
-      </c>
-      <c r="C66" s="32">
-        <v>1</v>
-      </c>
-      <c r="D66" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="G66">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>7</v>
-      </c>
-      <c r="H66">
-        <v>10</v>
-      </c>
-      <c r="I66">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A67" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>67</v>
-      </c>
-      <c r="B67" s="31" t="s">
-        <v>110</v>
-      </c>
-      <c r="C67" s="32">
-        <v>1</v>
-      </c>
-      <c r="D67" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="G67">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>7</v>
-      </c>
-      <c r="H67">
-        <v>20</v>
-      </c>
-      <c r="I67">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A68" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>68</v>
-      </c>
-      <c r="B68" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="C68" s="32">
-        <v>2</v>
-      </c>
-      <c r="D68" s="30" t="s">
-        <v>113</v>
-      </c>
-      <c r="G68">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>14</v>
-      </c>
-      <c r="H68">
-        <v>10</v>
-      </c>
-      <c r="I68">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>4</v>
-      </c>
-      <c r="J68" t="s">
-        <v>19</v>
-      </c>
-      <c r="K68" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A69" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>69</v>
-      </c>
-      <c r="B69" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="C69" s="32">
-        <v>1</v>
-      </c>
-      <c r="D69" s="30" t="s">
-        <v>115</v>
-      </c>
-      <c r="G69">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>7</v>
-      </c>
-      <c r="H69">
-        <v>10</v>
-      </c>
-      <c r="I69">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A70" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>70</v>
-      </c>
-      <c r="B70" s="31" t="s">
-        <v>116</v>
-      </c>
-      <c r="C70" s="32">
-        <v>1</v>
-      </c>
-      <c r="D70" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="G70">
-        <v>2</v>
-      </c>
-      <c r="H70">
-        <v>3</v>
-      </c>
-      <c r="I70">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A71" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>71</v>
-      </c>
-      <c r="B71" s="31" t="s">
-        <v>120</v>
       </c>
       <c r="C71" s="32">
         <v>2</v>
       </c>
-      <c r="D71" s="30" t="s">
-        <v>127</v>
-      </c>
-      <c r="G71">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>14</v>
+      <c r="D71" s="32">
+        <v>2</v>
+      </c>
+      <c r="E71" s="30" t="s">
+        <v>107</v>
       </c>
       <c r="H71">
+        <v>20</v>
+      </c>
+      <c r="I71">
+        <v>5</v>
+      </c>
+      <c r="J71">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>15</v>
+      </c>
+      <c r="K71" t="s">
+        <v>18</v>
+      </c>
+      <c r="L71" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A72" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>72</v>
+      </c>
+      <c r="B72" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="C72" s="32">
+        <v>1</v>
+      </c>
+      <c r="D72" s="32">
+        <v>1</v>
+      </c>
+      <c r="E72" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="H72">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
         <v>8</v>
       </c>
-      <c r="I71">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A72" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>72</v>
-      </c>
-      <c r="B72" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="C72" s="32">
-        <v>2</v>
-      </c>
-      <c r="D72" s="30" t="s">
-        <v>128</v>
-      </c>
-      <c r="G72">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>14</v>
-      </c>
-      <c r="H72">
-        <v>18</v>
-      </c>
       <c r="I72">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="J72">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+      <c r="L72" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>73</v>
       </c>
       <c r="B73" s="31" t="s">
-        <v>148</v>
+        <v>110</v>
       </c>
       <c r="C73" s="32">
-        <v>2</v>
-      </c>
-      <c r="D73" s="30" t="s">
-        <v>128</v>
-      </c>
-      <c r="G73">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="D73" s="32">
+        <v>1</v>
+      </c>
+      <c r="E73" s="30" t="s">
+        <v>111</v>
       </c>
       <c r="H73">
-        <v>2</v>
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>1</v>
       </c>
       <c r="I73">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="J73">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+      <c r="L73" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>74</v>
       </c>
       <c r="B74" s="31" t="s">
-        <v>148</v>
+        <v>114</v>
       </c>
       <c r="C74" s="32">
         <v>2</v>
       </c>
-      <c r="D74" s="30" t="s">
-        <v>127</v>
-      </c>
-      <c r="G74">
-        <v>2</v>
+      <c r="D74" s="32">
+        <v>5</v>
+      </c>
+      <c r="E74" s="30" t="s">
+        <v>121</v>
       </c>
       <c r="H74">
-        <v>0</v>
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>19</v>
       </c>
       <c r="I74">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="J74">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>11</v>
+      </c>
+      <c r="L74" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>75</v>
       </c>
       <c r="B75" s="31" t="s">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="C75" s="32">
         <v>2</v>
       </c>
-      <c r="D75" s="30" t="s">
-        <v>152</v>
-      </c>
-      <c r="F75" s="30" t="s">
+      <c r="D75" s="32">
+        <v>4</v>
+      </c>
+      <c r="E75" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="H75">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>18</v>
+      </c>
+      <c r="I75">
+        <v>18</v>
+      </c>
+      <c r="J75">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+      <c r="L75" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A76" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>76</v>
+      </c>
+      <c r="B76" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="C76" s="32">
+        <v>0</v>
+      </c>
+      <c r="D76" s="32">
+        <v>1</v>
+      </c>
+      <c r="E76" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="H76">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>1</v>
+      </c>
+      <c r="I76">
+        <v>2</v>
+      </c>
+      <c r="J76">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+      <c r="L76" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A77" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>77</v>
+      </c>
+      <c r="B77" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="C77" s="32">
+        <v>0</v>
+      </c>
+      <c r="D77" s="32">
+        <v>2</v>
+      </c>
+      <c r="E77" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="H77">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>2</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>2</v>
+      </c>
+      <c r="L77" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A78" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>78</v>
+      </c>
+      <c r="B78" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="C78" s="32">
+        <v>2</v>
+      </c>
+      <c r="D78" s="32">
+        <v>2</v>
+      </c>
+      <c r="E78" s="30" t="s">
         <v>144</v>
       </c>
-      <c r="G75">
-        <f>Table2[[#This Row],[Quantity]]*M5</f>
+      <c r="G78" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="H78">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>16</v>
+      </c>
+      <c r="I78">
         <v>4</v>
       </c>
-      <c r="H75">
-        <v>4</v>
-      </c>
-      <c r="I75">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A76" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>76</v>
-      </c>
-      <c r="G76">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>0</v>
-      </c>
-      <c r="H76">
-        <v>0</v>
-      </c>
-      <c r="I76">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A77" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>77</v>
-      </c>
-      <c r="G77">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>0</v>
-      </c>
-      <c r="H77">
-        <v>0</v>
-      </c>
-      <c r="I77">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A78" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>78</v>
-      </c>
-      <c r="G78">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>0</v>
-      </c>
-      <c r="H78">
-        <v>0</v>
-      </c>
-      <c r="I78">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J78">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>12</v>
+      </c>
+      <c r="L78" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>79</v>
       </c>
-      <c r="G79">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>0</v>
+      <c r="B79" s="31" t="s">
+        <v>165</v>
+      </c>
+      <c r="C79" s="32">
+        <v>0</v>
+      </c>
+      <c r="D79" s="32">
+        <v>1</v>
       </c>
       <c r="H79">
-        <v>0</v>
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>1</v>
       </c>
       <c r="I79">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="J79">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+      <c r="L79" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>80</v>
       </c>
-      <c r="G80">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>0</v>
+      <c r="B80" s="31" t="s">
+        <v>169</v>
+      </c>
+      <c r="C80" s="32">
+        <v>0</v>
+      </c>
+      <c r="D80" s="32">
+        <v>20</v>
       </c>
       <c r="H80">
-        <v>0</v>
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>20</v>
       </c>
       <c r="I80">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+      <c r="J80">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+      <c r="L80" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>81</v>
       </c>
-      <c r="G81">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>0</v>
+      <c r="B81" s="31" t="s">
+        <v>170</v>
+      </c>
+      <c r="C81" s="32">
+        <v>0</v>
+      </c>
+      <c r="D81" s="32">
+        <v>1</v>
+      </c>
+      <c r="E81" s="30" t="s">
+        <v>183</v>
       </c>
       <c r="H81">
-        <v>0</v>
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>1</v>
       </c>
       <c r="I81">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>1</v>
+      </c>
+      <c r="L81" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>82</v>
       </c>
-      <c r="G82">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>0</v>
+      <c r="B82" s="31" t="s">
+        <v>170</v>
+      </c>
+      <c r="C82" s="32">
+        <v>0</v>
+      </c>
+      <c r="D82" s="32">
+        <v>2</v>
+      </c>
+      <c r="E82" s="30" t="s">
+        <v>171</v>
       </c>
       <c r="H82">
-        <v>0</v>
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>2</v>
       </c>
       <c r="I82">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>2</v>
+      </c>
+      <c r="L82" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>83</v>
       </c>
-      <c r="G83">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>0</v>
+      <c r="B83" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="C83" s="32">
+        <v>0</v>
+      </c>
+      <c r="D83" s="32">
+        <v>3</v>
+      </c>
+      <c r="E83" s="30" t="s">
+        <v>173</v>
       </c>
       <c r="H83">
-        <v>0</v>
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>3</v>
       </c>
       <c r="I83">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>3</v>
+      </c>
+      <c r="L83" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>84</v>
       </c>
-      <c r="G84">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>0</v>
+      <c r="B84" s="31" t="s">
+        <v>174</v>
+      </c>
+      <c r="C84" s="32">
+        <v>0</v>
+      </c>
+      <c r="D84" s="32">
+        <v>2</v>
+      </c>
+      <c r="E84" s="30" t="s">
+        <v>175</v>
       </c>
       <c r="H84">
-        <v>0</v>
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>2</v>
       </c>
       <c r="I84">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>2</v>
+      </c>
+      <c r="L84" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>85</v>
       </c>
-      <c r="G85">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>0</v>
+      <c r="B85" s="31" t="s">
+        <v>176</v>
+      </c>
+      <c r="C85" s="32">
+        <v>0</v>
+      </c>
+      <c r="D85" s="32">
+        <v>1</v>
+      </c>
+      <c r="E85" s="30" t="s">
+        <v>177</v>
       </c>
       <c r="H85">
-        <v>0</v>
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>1</v>
       </c>
       <c r="I85">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>1</v>
+      </c>
+      <c r="L85" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>86</v>
       </c>
-      <c r="G86">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>0</v>
+      <c r="B86" s="31" t="s">
+        <v>174</v>
+      </c>
+      <c r="C86" s="32">
+        <v>0</v>
+      </c>
+      <c r="D86" s="32">
+        <v>1</v>
+      </c>
+      <c r="E86" s="30" t="s">
+        <v>178</v>
       </c>
       <c r="H86">
-        <v>0</v>
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>1</v>
       </c>
       <c r="I86">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>1</v>
+      </c>
+      <c r="L86" s="51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>87</v>
       </c>
-      <c r="G87">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>0</v>
+      <c r="B87" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="C87" s="32">
+        <v>0</v>
+      </c>
+      <c r="D87" s="32">
+        <v>1</v>
+      </c>
+      <c r="E87" s="30" t="s">
+        <v>181</v>
       </c>
       <c r="H87">
-        <v>0</v>
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>1</v>
       </c>
       <c r="I87">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>1</v>
+      </c>
+      <c r="L87" s="51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>88</v>
       </c>
-      <c r="G88">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>0</v>
-      </c>
       <c r="H88">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
         <v>0</v>
       </c>
       <c r="I88">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>89</v>
       </c>
-      <c r="G89">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>0</v>
-      </c>
       <c r="H89">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
         <v>0</v>
       </c>
       <c r="I89">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>90</v>
       </c>
-      <c r="G90">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>0</v>
-      </c>
       <c r="H90">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
         <v>0</v>
       </c>
       <c r="I90">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>91</v>
       </c>
-      <c r="G91">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>0</v>
-      </c>
       <c r="H91">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
         <v>0</v>
       </c>
       <c r="I91">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>92</v>
       </c>
-      <c r="G92">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>0</v>
-      </c>
       <c r="H92">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
         <v>0</v>
       </c>
       <c r="I92">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>93</v>
       </c>
-      <c r="G93">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>0</v>
-      </c>
       <c r="H93">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
         <v>0</v>
       </c>
       <c r="I93">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>94</v>
       </c>
-      <c r="G94">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>0</v>
-      </c>
       <c r="H94">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
         <v>0</v>
       </c>
       <c r="I94">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>95</v>
       </c>
-      <c r="G95">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>0</v>
-      </c>
       <c r="H95">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
         <v>0</v>
       </c>
       <c r="I95">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>96</v>
       </c>
-      <c r="G96">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>0</v>
-      </c>
       <c r="H96">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
         <v>0</v>
       </c>
       <c r="I96">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>97</v>
       </c>
-      <c r="G97">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>0</v>
-      </c>
       <c r="H97">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
         <v>0</v>
       </c>
       <c r="I97">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>98</v>
       </c>
-      <c r="G98">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>0</v>
-      </c>
       <c r="H98">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
         <v>0</v>
       </c>
       <c r="I98">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>99</v>
       </c>
-      <c r="G99">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>0</v>
-      </c>
       <c r="H99">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
         <v>0</v>
       </c>
       <c r="I99">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>100</v>
       </c>
-      <c r="G100">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>0</v>
-      </c>
       <c r="H100">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
         <v>0</v>
       </c>
       <c r="I100">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>101</v>
       </c>
-      <c r="G101">
-        <f>Table2[[#This Row],[Quantity]]*$M$3</f>
-        <v>0</v>
-      </c>
       <c r="H101">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
         <v>0</v>
       </c>
       <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A102" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>102</v>
+      </c>
+      <c r="H102">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>0</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+      <c r="J102">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A103" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>103</v>
+      </c>
+      <c r="H103">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>0</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A104" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>104</v>
+      </c>
+      <c r="H104">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>0</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+      <c r="J104">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A105" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>105</v>
+      </c>
+      <c r="H105">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>0</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="J105">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="I1:I101">
+  <conditionalFormatting sqref="J1:J105">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O47">
-    <cfRule type="colorScale" priority="5">
+  <conditionalFormatting sqref="P4:P52 P2">
+    <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/Buying List + BOM V2.xlsx
+++ b/Buying List + BOM V2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\angel\Desktop\Proyectos\FOC_BLDC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EAE418D-A1CB-4F7E-81D7-6D46F05E6FC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E85FDE78-A7E1-4C7D-91E3-90B77E3AD7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Components" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="187">
   <si>
     <t>Component</t>
   </si>
@@ -318,9 +318,6 @@
     <t>MOSFET</t>
   </si>
   <si>
-    <t>FH4008GS</t>
-  </si>
-  <si>
     <t>SM7850</t>
   </si>
   <si>
@@ -595,6 +592,12 @@
   </si>
   <si>
     <t>25V</t>
+  </si>
+  <si>
+    <t>FH4008GS (IRFH7440)</t>
+  </si>
+  <si>
+    <t>Female 90</t>
   </si>
 </sst>
 </file>
@@ -971,58 +974,6 @@
   <dxfs count="37">
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF92D050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -1043,29 +994,6 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -1120,6 +1048,172 @@
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF92D050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1148,58 +1242,12 @@
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
         <vertical/>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     </dxf>
     <dxf>
       <font>
@@ -1322,25 +1370,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -1385,32 +1414,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -1542,30 +1545,30 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{57113999-89B8-4DCA-AAEB-0496B38A0B13}" name="Table1" displayName="Table1" ref="A1:K34" totalsRowCount="1" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25">
   <autoFilter ref="A1:K33" xr:uid="{57113999-89B8-4DCA-AAEB-0496B38A0B13}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{C01A5BB4-2776-4DA4-B397-20536FB6B151}" name="Component" dataDxfId="24" totalsRowDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{D16A6BB5-FB54-4A08-8F36-6F894F571CA2}" name="Supplier" dataDxfId="22" totalsRowDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{13E6D449-D029-4B98-A474-567EF4C137DD}" name="Unit Price" dataDxfId="20" totalsRowDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{BFC6BC80-26FB-482F-B354-EBAC0B59B079}" name="Quantity / Board" dataDxfId="18" totalsRowDxfId="17"/>
-    <tableColumn id="8" xr3:uid="{60AEBA47-4243-42D3-988F-F3DB3204B15E}" name="Total Quantity 6 + 2" dataDxfId="16" totalsRowDxfId="15"/>
-    <tableColumn id="12" xr3:uid="{4B5F8A5D-14B9-498E-9411-2EEB2C426CA5}" name="Left to Purchase" dataDxfId="14" totalsRowDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{E17DAC7E-1E39-4AF4-8109-E85C3BEA4D94}" name="Shipping Costs" dataDxfId="12" totalsRowDxfId="11"/>
-    <tableColumn id="10" xr3:uid="{80648434-14FA-49B4-BA1C-C16B6DFD9A61}" name="Purchased" dataDxfId="10" totalsRowDxfId="9"/>
-    <tableColumn id="9" xr3:uid="{2A4D153E-2215-40C4-B217-8FADF5785568}" name="Arrived" dataDxfId="8" totalsRowDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{9BE18441-967B-45FF-8A88-16AF220F7381}" name="Total" totalsRowFunction="custom" dataDxfId="6" totalsRowDxfId="5">
+    <tableColumn id="1" xr3:uid="{C01A5BB4-2776-4DA4-B397-20536FB6B151}" name="Component" dataDxfId="24" totalsRowDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{D16A6BB5-FB54-4A08-8F36-6F894F571CA2}" name="Supplier" dataDxfId="23" totalsRowDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{13E6D449-D029-4B98-A474-567EF4C137DD}" name="Unit Price" dataDxfId="21" totalsRowDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{BFC6BC80-26FB-482F-B354-EBAC0B59B079}" name="Quantity / Board" dataDxfId="20" totalsRowDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{60AEBA47-4243-42D3-988F-F3DB3204B15E}" name="Total Quantity 6 + 2" dataDxfId="18" totalsRowDxfId="17"/>
+    <tableColumn id="12" xr3:uid="{4B5F8A5D-14B9-498E-9411-2EEB2C426CA5}" name="Left to Purchase" dataDxfId="16" totalsRowDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{E17DAC7E-1E39-4AF4-8109-E85C3BEA4D94}" name="Shipping Costs" dataDxfId="14" totalsRowDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{80648434-14FA-49B4-BA1C-C16B6DFD9A61}" name="Purchased" dataDxfId="13" totalsRowDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{2A4D153E-2215-40C4-B217-8FADF5785568}" name="Arrived" dataDxfId="12" totalsRowDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{9BE18441-967B-45FF-8A88-16AF220F7381}" name="Total" totalsRowFunction="custom" dataDxfId="11" totalsRowDxfId="0">
       <calculatedColumnFormula>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(Table1[Total])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{B8F06C12-DD71-45A3-886F-8113BE8A9BDA}" name="Link" dataDxfId="4" totalsRowDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{B8F06C12-DD71-45A3-886F-8113BE8A9BDA}" name="Link" dataDxfId="10" totalsRowDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{22595191-1704-4DAD-B045-FA2F04CF59FF}" name="Table2" displayName="Table2" ref="A1:J105" totalsRowShown="0">
-  <autoFilter ref="A1:J105" xr:uid="{22595191-1704-4DAD-B045-FA2F04CF59FF}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J105">
-    <sortCondition ref="B1:B105"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{22595191-1704-4DAD-B045-FA2F04CF59FF}" name="Table2" displayName="Table2" ref="A1:J106" totalsRowShown="0">
+  <autoFilter ref="A1:J106" xr:uid="{22595191-1704-4DAD-B045-FA2F04CF59FF}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J106">
+    <sortCondition ref="B1:B106"/>
   </sortState>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{573F2863-704A-459C-9EBD-42757DB1F58F}" name="Id" dataDxfId="36">
@@ -1852,7 +1855,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="58.109375" customWidth="1"/>
@@ -1941,7 +1944,7 @@
     </row>
     <row r="3" spans="1:11" ht="24.6" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>19</v>
@@ -2518,7 +2521,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>31</v>
@@ -2550,7 +2553,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B21" s="11" t="s">
         <v>31</v>
@@ -2582,10 +2585,10 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="B22" s="11" t="s">
         <v>145</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>146</v>
       </c>
       <c r="C22" s="13">
         <v>0</v>
@@ -2614,10 +2617,10 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C23" s="13">
         <v>0</v>
@@ -2646,10 +2649,10 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C24" s="13">
         <v>0</v>
@@ -2678,7 +2681,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>19</v>
@@ -2732,66 +2735,77 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C27" s="13"/>
+      <c r="C27" s="13">
+        <v>11.15</v>
+      </c>
       <c r="D27" s="11">
         <v>1</v>
       </c>
       <c r="E27" s="11">
         <v>1</v>
       </c>
-      <c r="F27" s="29"/>
-      <c r="G27" s="13"/>
+      <c r="F27" s="29">
+        <v>0</v>
+      </c>
+      <c r="G27" s="13">
+        <f>35.16-11.15</f>
+        <v>24.009999999999998</v>
+      </c>
       <c r="H27" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I27" s="25" t="s">
         <v>25</v>
       </c>
       <c r="J27" s="26">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
-        <v>0</v>
+        <v>35.159999999999997</v>
       </c>
       <c r="K27" s="11"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C28" s="13"/>
+      <c r="C28" s="13">
+        <v>154.83000000000001</v>
+      </c>
       <c r="D28" s="11">
         <v>1</v>
       </c>
       <c r="E28" s="11">
         <v>1</v>
       </c>
-      <c r="F28" s="29"/>
+      <c r="F28" s="29">
+        <v>0</v>
+      </c>
       <c r="G28" s="13"/>
       <c r="H28" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I28" s="25" t="s">
         <v>25</v>
       </c>
       <c r="J28" s="26">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Total Quantity 6 + 2]]+Table1[[#This Row],[Shipping Costs]]</f>
-        <v>0</v>
+        <v>154.83000000000001</v>
       </c>
       <c r="K28" s="11"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="B29" s="11" t="s">
         <v>156</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>157</v>
       </c>
       <c r="C29" s="13">
         <f>50*1.15</f>
@@ -2899,18 +2913,42 @@
       <c r="I34" s="25"/>
       <c r="J34" s="14">
         <f>SUM(Table1[Total])</f>
-        <v>288.15999999999997</v>
+        <v>478.15</v>
       </c>
       <c r="K34" s="11"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G44"/>
+      <c r="H44"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G45"/>
+      <c r="H45"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G46"/>
+      <c r="H46"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G47"/>
+      <c r="H47"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G48"/>
+      <c r="H48"/>
+    </row>
+    <row r="49" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G49"/>
+      <c r="H49"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F34">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:I34">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2926,7 +2964,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24286835-DDBE-4844-A8EA-1CAF4B158E48}">
-  <dimension ref="A1:Q105"/>
+  <dimension ref="A1:S106"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.109375" style="32" customWidth="1"/>
@@ -2943,7 +2981,7 @@
     <col min="16" max="16" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" s="32" t="s">
         <v>48</v>
       </c>
@@ -2951,19 +2989,19 @@
         <v>49</v>
       </c>
       <c r="C1" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1" s="32" t="s">
         <v>160</v>
-      </c>
-      <c r="D1" s="32" t="s">
-        <v>161</v>
       </c>
       <c r="E1" s="30" t="s">
         <v>50</v>
       </c>
       <c r="F1" s="30" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H1" t="s">
         <v>7</v>
@@ -2975,7 +3013,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>2</v>
@@ -3009,14 +3047,18 @@
       <c r="L2" s="51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S2">
+        <f>IF(L2,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>3</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C3" s="32">
         <v>1</v>
@@ -3042,25 +3084,29 @@
         <v>1</v>
       </c>
       <c r="M3" s="33" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="N3" s="33">
         <v>7</v>
       </c>
       <c r="P3" s="33" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q3" s="33">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S3">
+        <f>IF(L3,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>4</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C4" s="32">
         <v>4</v>
@@ -3069,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H4">
         <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
@@ -3080,18 +3126,22 @@
         <v>28</v>
       </c>
       <c r="L4" s="51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="33"/>
       <c r="N4" s="33"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S4">
+        <f>IF(L4,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="34">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>5</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C5" s="36">
         <v>2</v>
@@ -3114,7 +3164,7 @@
         <v>14</v>
       </c>
       <c r="L5" s="51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="33" t="s">
         <v>56</v>
@@ -3122,14 +3172,18 @@
       <c r="N5" s="33">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S5">
+        <f>IF(L5,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>6</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C6" s="32">
         <v>0</v>
@@ -3138,7 +3192,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="30" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H6">
         <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
@@ -3152,16 +3206,20 @@
         <v>1</v>
       </c>
       <c r="L6" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <f>IF(L6,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>7</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C7" s="32">
         <v>1</v>
@@ -3181,16 +3239,20 @@
         <v>8</v>
       </c>
       <c r="L7" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <f>IF(L7,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>8</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C8" s="32">
         <v>14</v>
@@ -3202,10 +3264,10 @@
         <v>57</v>
       </c>
       <c r="F8" s="30" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G8" s="30" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H8">
         <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
@@ -3221,14 +3283,18 @@
       <c r="L8" s="51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S8">
+        <f>IF(L8,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>9</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C9" s="32">
         <v>1</v>
@@ -3248,16 +3314,20 @@
         <v>8</v>
       </c>
       <c r="L9" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <f>IF(L9,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>10</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C10" s="32">
         <v>9</v>
@@ -3277,16 +3347,20 @@
         <v>66</v>
       </c>
       <c r="L10" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S10">
+        <f>IF(L10,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>11</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C11" s="32">
         <v>2</v>
@@ -3311,14 +3385,18 @@
       <c r="L11" s="51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S11">
+        <f>IF(L11,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>12</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C12" s="32">
         <v>0</v>
@@ -3338,16 +3416,20 @@
         <v>20</v>
       </c>
       <c r="L12" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S12">
+        <f>IF(L12,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>13</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C13" s="32">
         <v>4</v>
@@ -3367,16 +3449,20 @@
         <v>28</v>
       </c>
       <c r="L13" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S13">
+        <f>IF(L13,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>14</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C14" s="32">
         <v>2</v>
@@ -3385,7 +3471,7 @@
         <v>4</v>
       </c>
       <c r="E14" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H14">
         <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
@@ -3396,16 +3482,20 @@
         <v>18</v>
       </c>
       <c r="L14" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S14">
+        <f>IF(L14,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>15</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C15" s="32">
         <v>2</v>
@@ -3425,16 +3515,20 @@
         <v>16</v>
       </c>
       <c r="L15" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S15">
+        <f>IF(L15,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>16</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C16" s="32">
         <v>1</v>
@@ -3443,7 +3537,7 @@
         <v>1</v>
       </c>
       <c r="E16" s="30" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H16">
         <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
@@ -3454,16 +3548,20 @@
         <v>8</v>
       </c>
       <c r="L16" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S16">
+        <f>IF(L16,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>17</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C17" s="32">
         <v>2</v>
@@ -3483,16 +3581,20 @@
         <v>14</v>
       </c>
       <c r="L17" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S17">
+        <f>IF(L17,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>18</v>
       </c>
       <c r="B18" s="31" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C18" s="32">
         <v>3</v>
@@ -3504,7 +3606,7 @@
         <v>64</v>
       </c>
       <c r="F18" s="30" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H18">
         <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
@@ -3515,16 +3617,20 @@
         <v>22</v>
       </c>
       <c r="L18" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S18">
+        <f>IF(L18,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>19</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C19" s="32">
         <v>1</v>
@@ -3549,14 +3655,18 @@
       <c r="L19" s="51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S19">
+        <f>IF(L19,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="42">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>20</v>
       </c>
       <c r="B20" s="43" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C20" s="44">
         <v>1</v>
@@ -3568,7 +3678,7 @@
         <v>66</v>
       </c>
       <c r="F20" s="45" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G20" s="45"/>
       <c r="H20" s="46">
@@ -3581,16 +3691,20 @@
         <v>7</v>
       </c>
       <c r="L20" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S20">
+        <f>IF(L20,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" s="34">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>21</v>
       </c>
       <c r="B21" s="35" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C21" s="36">
         <v>4</v>
@@ -3617,14 +3731,18 @@
       <c r="L21" s="51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="S21">
+        <f>IF(L21,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>22</v>
       </c>
       <c r="B22" s="31" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C22" s="32">
         <v>2</v>
@@ -3649,14 +3767,18 @@
       <c r="L22" s="51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="S22">
+        <f>IF(L22,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>23</v>
       </c>
       <c r="B23" s="31" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C23" s="32">
         <v>1</v>
@@ -3681,14 +3803,18 @@
       <c r="L23" s="51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="S23">
+        <f>IF(L23,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>24</v>
       </c>
       <c r="B24" s="31" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C24" s="32">
         <v>0</v>
@@ -3697,7 +3823,7 @@
         <v>2</v>
       </c>
       <c r="E24" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H24">
         <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
@@ -3708,16 +3834,20 @@
         <v>2</v>
       </c>
       <c r="L24" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S24">
+        <f>IF(L24,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>25</v>
       </c>
       <c r="B25" s="31" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C25" s="32">
         <v>1</v>
@@ -3726,7 +3856,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="30" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H25">
         <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
@@ -3737,16 +3867,20 @@
         <v>7</v>
       </c>
       <c r="L25" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S25">
+        <f>IF(L25,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>26</v>
       </c>
       <c r="B26" s="31" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C26" s="32">
         <v>0</v>
@@ -3755,7 +3889,7 @@
         <v>2</v>
       </c>
       <c r="E26" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H26">
         <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
@@ -3769,16 +3903,20 @@
         <v>2</v>
       </c>
       <c r="L26" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S26">
+        <f>IF(L26,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>27</v>
       </c>
       <c r="B27" s="31" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C27" s="32">
         <v>2</v>
@@ -3798,16 +3936,20 @@
         <v>16</v>
       </c>
       <c r="L27" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S27">
+        <f>IF(L27,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>28</v>
       </c>
       <c r="B28" s="31" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C28" s="32">
         <v>4</v>
@@ -3819,10 +3961,10 @@
         <v>70</v>
       </c>
       <c r="F28" s="30" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G28" s="30" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H28">
         <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
@@ -3833,16 +3975,20 @@
         <v>31</v>
       </c>
       <c r="L28" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S28">
+        <f>IF(L28,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>29</v>
       </c>
       <c r="B29" s="31" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C29" s="32">
         <v>0</v>
@@ -3862,16 +4008,20 @@
         <v>1</v>
       </c>
       <c r="L29" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S29">
+        <f>IF(L29,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>30</v>
       </c>
       <c r="B30" s="31" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C30" s="32">
         <v>6</v>
@@ -3891,16 +4041,20 @@
         <v>42</v>
       </c>
       <c r="L30" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S30">
+        <f>IF(L30,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>31</v>
       </c>
       <c r="B31" s="31" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C31" s="32">
         <v>1</v>
@@ -3912,7 +4066,7 @@
         <v>72</v>
       </c>
       <c r="F31" s="30" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H31">
         <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
@@ -3929,16 +4083,20 @@
         <v>18</v>
       </c>
       <c r="L31" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S31">
+        <f>IF(L31,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>32</v>
       </c>
       <c r="B32" s="31" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C32" s="32">
         <v>2</v>
@@ -3958,16 +4116,20 @@
         <v>14</v>
       </c>
       <c r="L32" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S32">
+        <f>IF(L32,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>33</v>
       </c>
       <c r="B33" s="31" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C33" s="32">
         <v>0</v>
@@ -3976,7 +4138,7 @@
         <v>2</v>
       </c>
       <c r="E33" s="30" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H33">
         <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
@@ -3987,16 +4149,20 @@
         <v>2</v>
       </c>
       <c r="L33" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S33">
+        <f>IF(L33,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A34" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>34</v>
       </c>
       <c r="B34" s="31" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C34" s="32">
         <v>1</v>
@@ -4005,7 +4171,7 @@
         <v>1</v>
       </c>
       <c r="E34" s="30" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H34">
         <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
@@ -4021,14 +4187,18 @@
       <c r="L34" s="51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="S34">
+        <f>IF(L34,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A35" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>35</v>
       </c>
       <c r="B35" s="31" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C35" s="32">
         <v>1</v>
@@ -4037,7 +4207,7 @@
         <v>1</v>
       </c>
       <c r="E35" s="30" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H35">
         <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
@@ -4048,16 +4218,20 @@
         <v>8</v>
       </c>
       <c r="L35" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S35">
+        <f>IF(L35,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>36</v>
       </c>
       <c r="B36" s="31" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C36" s="32">
         <v>4</v>
@@ -4069,10 +4243,10 @@
         <v>73</v>
       </c>
       <c r="F36" s="30" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G36" s="30" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H36">
         <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
@@ -4086,19 +4260,23 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L36" s="51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="S36">
+        <f>IF(L36,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>37</v>
       </c>
       <c r="B37" s="31" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C37" s="32">
         <v>1</v>
@@ -4107,7 +4285,7 @@
         <v>1</v>
       </c>
       <c r="E37" s="30" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H37">
         <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
@@ -4118,16 +4296,20 @@
         <v>8</v>
       </c>
       <c r="L37" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S37">
+        <f>IF(L37,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>38</v>
       </c>
       <c r="B38" s="31" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C38" s="32">
         <v>1</v>
@@ -4147,16 +4329,20 @@
         <v>8</v>
       </c>
       <c r="L38" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="S38">
+        <f>IF(L38,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="42">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>39</v>
       </c>
       <c r="B39" s="43" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C39" s="44">
         <v>1</v>
@@ -4179,16 +4365,20 @@
         <v>13</v>
       </c>
       <c r="L39" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S39">
+        <f>IF(L39,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A40" s="34">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>40</v>
       </c>
       <c r="B40" s="35" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C40" s="36">
         <v>2</v>
@@ -4200,10 +4390,10 @@
         <v>75</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H40" s="38">
         <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
@@ -4222,14 +4412,18 @@
       <c r="L40" s="51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="S40">
+        <f>IF(L40,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A41" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>41</v>
       </c>
       <c r="B41" s="31" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C41" s="32">
         <v>3</v>
@@ -4241,7 +4435,7 @@
         <v>57</v>
       </c>
       <c r="F41" s="30" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H41">
         <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
@@ -4257,14 +4451,18 @@
       <c r="L41" s="51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="S41">
+        <f>IF(L41,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A42" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>42</v>
       </c>
       <c r="B42" s="31" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C42" s="32">
         <v>0</v>
@@ -4273,7 +4471,7 @@
         <v>1</v>
       </c>
       <c r="E42" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H42">
         <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
@@ -4287,16 +4485,20 @@
         <v>1</v>
       </c>
       <c r="L42" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S42">
+        <f>IF(L42,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A43" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>43</v>
       </c>
       <c r="B43" s="31" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C43" s="32">
         <v>0</v>
@@ -4305,7 +4507,7 @@
         <v>1</v>
       </c>
       <c r="E43" s="30" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H43">
         <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
@@ -4319,16 +4521,20 @@
         <v>1</v>
       </c>
       <c r="L43" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S43">
+        <f>IF(L43,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A44" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>44</v>
       </c>
       <c r="B44" s="31" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C44" s="32">
         <v>0</v>
@@ -4351,16 +4557,20 @@
         <v>1</v>
       </c>
       <c r="L44" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S44">
+        <f>IF(L44,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A45" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>45</v>
       </c>
       <c r="B45" s="31" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C45" s="32">
         <v>0</v>
@@ -4385,14 +4595,18 @@
       <c r="L45" s="51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="S45">
+        <f>IF(L45,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A46" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>46</v>
       </c>
       <c r="B46" s="31" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C46" s="32">
         <v>0</v>
@@ -4415,16 +4629,20 @@
         <v>1</v>
       </c>
       <c r="L46" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S46">
+        <f>IF(L46,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A47" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>47</v>
       </c>
       <c r="B47" s="31" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C47" s="32">
         <v>0</v>
@@ -4449,14 +4667,18 @@
       <c r="L47" s="51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="S47">
+        <f>IF(L47,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A48" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>48</v>
       </c>
       <c r="B48" s="31" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C48" s="32">
         <v>11</v>
@@ -4482,16 +4704,20 @@
         <v>18</v>
       </c>
       <c r="L48" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S48">
+        <f>IF(L48,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>49</v>
       </c>
       <c r="B49" s="31" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C49" s="32">
         <v>2</v>
@@ -4514,16 +4740,20 @@
         <v>16</v>
       </c>
       <c r="L49" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S49">
+        <f>IF(L49,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A50" s="40">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>50</v>
       </c>
       <c r="B50" s="31" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C50" s="32">
         <v>5</v>
@@ -4549,16 +4779,20 @@
         <v>18</v>
       </c>
       <c r="L50" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S50">
+        <f>IF(L50,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A51" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>51</v>
       </c>
       <c r="B51" s="31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C51" s="32">
         <v>1</v>
@@ -4581,13 +4815,17 @@
         <v>10</v>
       </c>
       <c r="K51" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L51" s="51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="S51">
+        <f>IF(L51,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A52" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>52</v>
@@ -4620,8 +4858,12 @@
       <c r="L52" s="51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="S52">
+        <f>IF(L52,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A53" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>53</v>
@@ -4652,8 +4894,12 @@
       <c r="L53" s="51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="S53">
+        <f>IF(L53,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A54" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>54</v>
@@ -4668,7 +4914,7 @@
         <v>1</v>
       </c>
       <c r="E54" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H54">
         <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
@@ -4684,8 +4930,12 @@
       <c r="L54" s="51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="S54">
+        <f>IF(L54,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A55" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>55</v>
@@ -4716,8 +4966,12 @@
       <c r="L55" s="51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="S55">
+        <f>IF(L55,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A56" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>56</v>
@@ -4748,46 +5002,54 @@
       <c r="L56" s="51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="S56">
+        <f>IF(L56,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A57" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>57</v>
       </c>
       <c r="B57" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="C57" s="32">
+        <v>1</v>
+      </c>
+      <c r="D57" s="32">
+        <v>1</v>
+      </c>
+      <c r="E57" s="50" t="s">
+        <v>154</v>
+      </c>
+      <c r="H57">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>8</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>8</v>
+      </c>
+      <c r="L57" s="51" t="b">
+        <v>1</v>
+      </c>
+      <c r="S57">
+        <f>IF(L57,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A58" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>58</v>
+      </c>
+      <c r="B58" s="31" t="s">
         <v>137</v>
-      </c>
-      <c r="C57" s="32">
-        <v>1</v>
-      </c>
-      <c r="D57" s="32">
-        <v>1</v>
-      </c>
-      <c r="E57" s="50" t="s">
-        <v>155</v>
-      </c>
-      <c r="H57">
-        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
-        <v>8</v>
-      </c>
-      <c r="I57">
-        <v>0</v>
-      </c>
-      <c r="J57">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>8</v>
-      </c>
-      <c r="L57" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A58" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>58</v>
-      </c>
-      <c r="B58" s="31" t="s">
-        <v>138</v>
       </c>
       <c r="C58" s="32">
         <v>2</v>
@@ -4796,7 +5058,7 @@
         <v>0</v>
       </c>
       <c r="E58" s="30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H58">
         <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
@@ -4812,8 +5074,12 @@
       <c r="L58" s="51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="S58">
+        <f>IF(L58,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A59" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>59</v>
@@ -4844,8 +5110,12 @@
       <c r="L59" s="51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="S59">
+        <f>IF(L59,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A60" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>60</v>
@@ -4876,8 +5146,12 @@
       <c r="L60" s="51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="S60">
+        <f>IF(L60,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A61" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>61</v>
@@ -4892,7 +5166,7 @@
         <v>0</v>
       </c>
       <c r="E61" s="30" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H61">
         <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
@@ -4908,8 +5182,11 @@
       <c r="L61" s="51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="S61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A62" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>62</v>
@@ -4940,8 +5217,11 @@
       <c r="L62" s="51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="S62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A63" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>63</v>
@@ -4956,7 +5236,7 @@
         <v>0</v>
       </c>
       <c r="E63" s="30" t="s">
-        <v>93</v>
+        <v>185</v>
       </c>
       <c r="H63">
         <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
@@ -4972,24 +5252,28 @@
       <c r="L63" s="51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="S63">
+        <f>IF(L63,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A64" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>64</v>
       </c>
       <c r="B64" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="C64" s="32">
+        <v>1</v>
+      </c>
+      <c r="D64" s="32">
+        <v>1</v>
+      </c>
+      <c r="E64" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="C64" s="32">
-        <v>1</v>
-      </c>
-      <c r="D64" s="32">
-        <v>1</v>
-      </c>
-      <c r="E64" s="30" t="s">
-        <v>113</v>
-      </c>
       <c r="H64">
         <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
         <v>8</v>
@@ -5004,14 +5288,18 @@
       <c r="L64" s="51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="S64">
+        <f>IF(L64,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A65" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>65</v>
       </c>
       <c r="B65" s="31" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C65" s="32">
         <v>1</v>
@@ -5020,7 +5308,7 @@
         <v>3</v>
       </c>
       <c r="E65" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H65">
         <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
@@ -5036,14 +5324,18 @@
       <c r="L65" s="51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="S65">
+        <f>IF(L65,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A66" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>66</v>
       </c>
       <c r="B66" s="31" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C66" s="32">
         <v>5</v>
@@ -5052,7 +5344,7 @@
         <v>5</v>
       </c>
       <c r="E66" s="30" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H66">
         <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
@@ -5068,23 +5360,27 @@
       <c r="L66" s="51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="S66">
+        <f>IF(L66,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A67" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>67</v>
       </c>
       <c r="B67" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="C67" s="32">
+        <v>1</v>
+      </c>
+      <c r="D67" s="32">
+        <v>1</v>
+      </c>
+      <c r="E67" s="30" t="s">
         <v>98</v>
-      </c>
-      <c r="C67" s="32">
-        <v>1</v>
-      </c>
-      <c r="D67" s="32">
-        <v>1</v>
-      </c>
-      <c r="E67" s="30" t="s">
-        <v>99</v>
       </c>
       <c r="H67">
         <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
@@ -5100,23 +5396,27 @@
       <c r="L67" s="51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="S67">
+        <f>IF(L67,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A68" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>68</v>
       </c>
       <c r="B68" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="C68" s="32">
+        <v>1</v>
+      </c>
+      <c r="D68" s="32">
+        <v>0</v>
+      </c>
+      <c r="E68" s="30" t="s">
         <v>100</v>
-      </c>
-      <c r="C68" s="32">
-        <v>1</v>
-      </c>
-      <c r="D68" s="32">
-        <v>0</v>
-      </c>
-      <c r="E68" s="30" t="s">
-        <v>101</v>
       </c>
       <c r="H68">
         <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
@@ -5132,23 +5432,27 @@
       <c r="L68" s="51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="S68">
+        <f>IF(L68,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A69" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>69</v>
       </c>
       <c r="B69" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="C69" s="32">
+        <v>1</v>
+      </c>
+      <c r="D69" s="32">
+        <v>1</v>
+      </c>
+      <c r="E69" s="30" t="s">
         <v>102</v>
-      </c>
-      <c r="C69" s="32">
-        <v>1</v>
-      </c>
-      <c r="D69" s="32">
-        <v>1</v>
-      </c>
-      <c r="E69" s="30" t="s">
-        <v>103</v>
       </c>
       <c r="H69">
         <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
@@ -5164,23 +5468,27 @@
       <c r="L69" s="51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="S69">
+        <f>IF(L69,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A70" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>70</v>
       </c>
       <c r="B70" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="C70" s="32">
+        <v>1</v>
+      </c>
+      <c r="D70" s="32">
+        <v>1</v>
+      </c>
+      <c r="E70" s="30" t="s">
         <v>104</v>
-      </c>
-      <c r="C70" s="32">
-        <v>1</v>
-      </c>
-      <c r="D70" s="32">
-        <v>1</v>
-      </c>
-      <c r="E70" s="30" t="s">
-        <v>105</v>
       </c>
       <c r="H70">
         <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
@@ -5196,14 +5504,18 @@
       <c r="L70" s="51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="S70">
+        <f>IF(L70,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A71" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>71</v>
       </c>
       <c r="B71" s="31" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C71" s="32">
         <v>2</v>
@@ -5212,7 +5524,7 @@
         <v>2</v>
       </c>
       <c r="E71" s="30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H71">
         <v>20</v>
@@ -5230,23 +5542,27 @@
       <c r="L71" s="51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="S71">
+        <f>IF(L71,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A72" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>72</v>
       </c>
       <c r="B72" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="C72" s="32">
+        <v>1</v>
+      </c>
+      <c r="D72" s="32">
+        <v>1</v>
+      </c>
+      <c r="E72" s="30" t="s">
         <v>108</v>
-      </c>
-      <c r="C72" s="32">
-        <v>1</v>
-      </c>
-      <c r="D72" s="32">
-        <v>1</v>
-      </c>
-      <c r="E72" s="30" t="s">
-        <v>109</v>
       </c>
       <c r="H72">
         <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
@@ -5262,23 +5578,27 @@
       <c r="L72" s="51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="S72">
+        <f>IF(L72,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A73" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>73</v>
       </c>
       <c r="B73" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="C73" s="32">
+        <v>0</v>
+      </c>
+      <c r="D73" s="32">
+        <v>1</v>
+      </c>
+      <c r="E73" s="30" t="s">
         <v>110</v>
-      </c>
-      <c r="C73" s="32">
-        <v>0</v>
-      </c>
-      <c r="D73" s="32">
-        <v>1</v>
-      </c>
-      <c r="E73" s="30" t="s">
-        <v>111</v>
       </c>
       <c r="H73">
         <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
@@ -5294,110 +5614,126 @@
       <c r="L73" s="51" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="S73">
+        <f>IF(L73,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A74" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>74</v>
       </c>
       <c r="B74" s="31" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C74" s="32">
         <v>2</v>
       </c>
       <c r="D74" s="32">
+        <v>0</v>
+      </c>
+      <c r="E74" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="H74">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>14</v>
+      </c>
+      <c r="I74">
+        <v>6</v>
+      </c>
+      <c r="J74">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>8</v>
+      </c>
+      <c r="L74" s="51" t="b">
+        <v>1</v>
+      </c>
+      <c r="S74">
+        <f>IF(L74,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A75" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>75</v>
+      </c>
+      <c r="B75" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="C75" s="32">
+        <v>0</v>
+      </c>
+      <c r="D75" s="32">
         <v>5</v>
       </c>
-      <c r="E74" s="30" t="s">
+      <c r="E75" s="30" t="s">
+        <v>120</v>
+      </c>
+      <c r="H75">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>5</v>
+      </c>
+      <c r="I75">
+        <v>1</v>
+      </c>
+      <c r="J75">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>4</v>
+      </c>
+      <c r="L75" s="51" t="b">
+        <v>1</v>
+      </c>
+      <c r="S75">
+        <f>IF(L75,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A76" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>76</v>
+      </c>
+      <c r="B76" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="C76" s="32">
+        <v>2</v>
+      </c>
+      <c r="D76" s="32">
+        <v>4</v>
+      </c>
+      <c r="E76" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="H74">
-        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
-        <v>19</v>
-      </c>
-      <c r="I74">
-        <v>8</v>
-      </c>
-      <c r="J74">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>11</v>
-      </c>
-      <c r="L74" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A75" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>75</v>
-      </c>
-      <c r="B75" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="C75" s="32">
-        <v>2</v>
-      </c>
-      <c r="D75" s="32">
-        <v>4</v>
-      </c>
-      <c r="E75" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="H75">
+      <c r="H76">
         <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
         <v>18</v>
       </c>
-      <c r="I75">
+      <c r="I76">
         <v>18</v>
       </c>
-      <c r="J75">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-      <c r="L75" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A76" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>76</v>
-      </c>
-      <c r="B76" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="C76" s="32">
-        <v>0</v>
-      </c>
-      <c r="D76" s="32">
-        <v>1</v>
-      </c>
-      <c r="E76" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="H76">
-        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
-        <v>1</v>
-      </c>
-      <c r="I76">
-        <v>2</v>
-      </c>
       <c r="J76">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
         <v>0</v>
       </c>
       <c r="L76" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S76">
+        <f>IF(L76,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A77" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>77</v>
       </c>
       <c r="B77" s="31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C77" s="32">
         <v>0</v>
@@ -5413,542 +5749,607 @@
         <v>2</v>
       </c>
       <c r="I77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L77" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="S77">
+        <f>IF(L77,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A78" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>78</v>
       </c>
       <c r="B78" s="31" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C78" s="32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D78" s="32">
         <v>2</v>
       </c>
       <c r="E78" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="G78" s="30" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="H78">
         <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>2</v>
+      </c>
+      <c r="I78">
+        <v>1</v>
+      </c>
+      <c r="J78">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>1</v>
+      </c>
+      <c r="L78" s="51" t="b">
+        <v>1</v>
+      </c>
+      <c r="S78">
+        <f>IF(L78,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A79" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>79</v>
+      </c>
+      <c r="B79" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="C79" s="32">
+        <v>2</v>
+      </c>
+      <c r="D79" s="32">
+        <v>2</v>
+      </c>
+      <c r="E79" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="G79" s="30" t="s">
+        <v>135</v>
+      </c>
+      <c r="H79">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
         <v>16</v>
       </c>
-      <c r="I78">
+      <c r="I79">
         <v>4</v>
       </c>
-      <c r="J78">
+      <c r="J79">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
         <v>12</v>
       </c>
-      <c r="L78" s="51" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A79" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>79</v>
-      </c>
-      <c r="B79" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="C79" s="32">
-        <v>0</v>
-      </c>
-      <c r="D79" s="32">
-        <v>1</v>
-      </c>
-      <c r="H79">
-        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
-        <v>1</v>
-      </c>
-      <c r="I79">
+      <c r="L79" s="51" t="b">
+        <v>1</v>
+      </c>
+      <c r="S79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A80" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>80</v>
+      </c>
+      <c r="B80" s="31" t="s">
+        <v>164</v>
+      </c>
+      <c r="C80" s="32">
+        <v>0</v>
+      </c>
+      <c r="D80" s="32">
+        <v>1</v>
+      </c>
+      <c r="H80">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>1</v>
+      </c>
+      <c r="I80">
         <v>5</v>
       </c>
-      <c r="J79">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-      <c r="L79" s="51" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A80" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>80</v>
-      </c>
-      <c r="B80" s="31" t="s">
+      <c r="J80">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+      <c r="L80" s="51" t="b">
+        <v>1</v>
+      </c>
+      <c r="S80">
+        <f>IF(L80,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A81" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>81</v>
+      </c>
+      <c r="B81" s="31" t="s">
+        <v>168</v>
+      </c>
+      <c r="C81" s="32">
+        <v>0</v>
+      </c>
+      <c r="D81" s="32">
+        <v>20</v>
+      </c>
+      <c r="H81">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>20</v>
+      </c>
+      <c r="I81">
+        <v>100</v>
+      </c>
+      <c r="J81">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+      <c r="L81" s="51" t="b">
+        <v>1</v>
+      </c>
+      <c r="S81">
+        <f>IF(L81,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A82" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>82</v>
+      </c>
+      <c r="B82" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="C80" s="32">
-        <v>0</v>
-      </c>
-      <c r="D80" s="32">
-        <v>20</v>
-      </c>
-      <c r="H80">
-        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
-        <v>20</v>
-      </c>
-      <c r="I80">
+      <c r="C82" s="32">
+        <v>0</v>
+      </c>
+      <c r="D82" s="32">
+        <v>1</v>
+      </c>
+      <c r="E82" s="30" t="s">
+        <v>182</v>
+      </c>
+      <c r="H82">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>1</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>1</v>
+      </c>
+      <c r="L82" s="51" t="b">
+        <v>1</v>
+      </c>
+      <c r="S82">
+        <f>IF(L82,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A83" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>83</v>
+      </c>
+      <c r="B83" s="31" t="s">
+        <v>169</v>
+      </c>
+      <c r="C83" s="32">
+        <v>0</v>
+      </c>
+      <c r="D83" s="32">
+        <v>2</v>
+      </c>
+      <c r="E83" s="30" t="s">
+        <v>170</v>
+      </c>
+      <c r="H83">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>2</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>2</v>
+      </c>
+      <c r="L83" s="51" t="b">
+        <v>1</v>
+      </c>
+      <c r="S83">
+        <f>IF(L83,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A84" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>84</v>
+      </c>
+      <c r="B84" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="C84" s="32">
+        <v>0</v>
+      </c>
+      <c r="D84" s="32">
+        <v>3</v>
+      </c>
+      <c r="E84" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="H84">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>3</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>3</v>
+      </c>
+      <c r="L84" s="51" t="b">
+        <v>1</v>
+      </c>
+      <c r="S84">
+        <f>IF(L84,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A85" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>85</v>
+      </c>
+      <c r="B85" s="31" t="s">
+        <v>173</v>
+      </c>
+      <c r="C85" s="32">
+        <v>0</v>
+      </c>
+      <c r="D85" s="32">
+        <v>2</v>
+      </c>
+      <c r="E85" s="30" t="s">
+        <v>174</v>
+      </c>
+      <c r="H85">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>2</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>2</v>
+      </c>
+      <c r="L85" s="51" t="b">
+        <v>1</v>
+      </c>
+      <c r="S85">
+        <f>IF(L85,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A86" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>86</v>
+      </c>
+      <c r="B86" s="31" t="s">
+        <v>175</v>
+      </c>
+      <c r="C86" s="32">
+        <v>0</v>
+      </c>
+      <c r="D86" s="32">
+        <v>1</v>
+      </c>
+      <c r="E86" s="30" t="s">
+        <v>176</v>
+      </c>
+      <c r="H86">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>1</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>1</v>
+      </c>
+      <c r="L86" s="51" t="b">
+        <v>1</v>
+      </c>
+      <c r="S86">
+        <f>IF(L86,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A87" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>87</v>
+      </c>
+      <c r="B87" s="31" t="s">
+        <v>173</v>
+      </c>
+      <c r="C87" s="32">
+        <v>0</v>
+      </c>
+      <c r="D87" s="32">
+        <v>1</v>
+      </c>
+      <c r="E87" s="30" t="s">
+        <v>177</v>
+      </c>
+      <c r="H87">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>1</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>1</v>
+      </c>
+      <c r="L87" s="51" t="b">
+        <v>1</v>
+      </c>
+      <c r="S87">
+        <f>IF(L87,1,0)*IF(Table2[[#This Row],[BUY / HIVE]]&gt;0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A88" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>88</v>
+      </c>
+      <c r="B88" s="31" t="s">
+        <v>181</v>
+      </c>
+      <c r="C88" s="32">
+        <v>0</v>
+      </c>
+      <c r="D88" s="32">
+        <v>1</v>
+      </c>
+      <c r="E88" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="H88">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>1</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>1</v>
+      </c>
+      <c r="L88" s="51" t="b">
+        <v>1</v>
+      </c>
+      <c r="S88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A89" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>89</v>
+      </c>
+      <c r="H89">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>0</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A90" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>90</v>
+      </c>
+      <c r="H90">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>0</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A91" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>91</v>
+      </c>
+      <c r="H91">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>0</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A92" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>92</v>
+      </c>
+      <c r="H92">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>0</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A93" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>93</v>
+      </c>
+      <c r="H93">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>0</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A94" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>94</v>
+      </c>
+      <c r="H94">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>0</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A95" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>95</v>
+      </c>
+      <c r="H95">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>0</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A96" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>96</v>
+      </c>
+      <c r="H96">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>0</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A97" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>97</v>
+      </c>
+      <c r="H97">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>0</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+      <c r="S97">
+        <f>SUM(S2:S88)</f>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A98" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>98</v>
+      </c>
+      <c r="H98">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>0</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A99" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>99</v>
+      </c>
+      <c r="H99">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>0</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A100" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>100</v>
       </c>
-      <c r="J80">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-      <c r="L80" s="51" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A81" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>81</v>
-      </c>
-      <c r="B81" s="31" t="s">
-        <v>170</v>
-      </c>
-      <c r="C81" s="32">
-        <v>0</v>
-      </c>
-      <c r="D81" s="32">
-        <v>1</v>
-      </c>
-      <c r="E81" s="30" t="s">
-        <v>183</v>
-      </c>
-      <c r="H81">
-        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
-        <v>1</v>
-      </c>
-      <c r="I81">
-        <v>0</v>
-      </c>
-      <c r="J81">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>1</v>
-      </c>
-      <c r="L81" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A82" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>82</v>
-      </c>
-      <c r="B82" s="31" t="s">
-        <v>170</v>
-      </c>
-      <c r="C82" s="32">
-        <v>0</v>
-      </c>
-      <c r="D82" s="32">
-        <v>2</v>
-      </c>
-      <c r="E82" s="30" t="s">
-        <v>171</v>
-      </c>
-      <c r="H82">
-        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
-        <v>2</v>
-      </c>
-      <c r="I82">
-        <v>0</v>
-      </c>
-      <c r="J82">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>2</v>
-      </c>
-      <c r="L82" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A83" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>83</v>
-      </c>
-      <c r="B83" s="31" t="s">
-        <v>172</v>
-      </c>
-      <c r="C83" s="32">
-        <v>0</v>
-      </c>
-      <c r="D83" s="32">
-        <v>3</v>
-      </c>
-      <c r="E83" s="30" t="s">
-        <v>173</v>
-      </c>
-      <c r="H83">
-        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
-        <v>3</v>
-      </c>
-      <c r="I83">
-        <v>0</v>
-      </c>
-      <c r="J83">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>3</v>
-      </c>
-      <c r="L83" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A84" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>84</v>
-      </c>
-      <c r="B84" s="31" t="s">
-        <v>174</v>
-      </c>
-      <c r="C84" s="32">
-        <v>0</v>
-      </c>
-      <c r="D84" s="32">
-        <v>2</v>
-      </c>
-      <c r="E84" s="30" t="s">
-        <v>175</v>
-      </c>
-      <c r="H84">
-        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
-        <v>2</v>
-      </c>
-      <c r="I84">
-        <v>0</v>
-      </c>
-      <c r="J84">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>2</v>
-      </c>
-      <c r="L84" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A85" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>85</v>
-      </c>
-      <c r="B85" s="31" t="s">
-        <v>176</v>
-      </c>
-      <c r="C85" s="32">
-        <v>0</v>
-      </c>
-      <c r="D85" s="32">
-        <v>1</v>
-      </c>
-      <c r="E85" s="30" t="s">
-        <v>177</v>
-      </c>
-      <c r="H85">
-        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
-        <v>1</v>
-      </c>
-      <c r="I85">
-        <v>0</v>
-      </c>
-      <c r="J85">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>1</v>
-      </c>
-      <c r="L85" s="51" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A86" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>86</v>
-      </c>
-      <c r="B86" s="31" t="s">
-        <v>174</v>
-      </c>
-      <c r="C86" s="32">
-        <v>0</v>
-      </c>
-      <c r="D86" s="32">
-        <v>1</v>
-      </c>
-      <c r="E86" s="30" t="s">
-        <v>178</v>
-      </c>
-      <c r="H86">
-        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
-        <v>1</v>
-      </c>
-      <c r="I86">
-        <v>0</v>
-      </c>
-      <c r="J86">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>1</v>
-      </c>
-      <c r="L86" s="51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A87" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>87</v>
-      </c>
-      <c r="B87" s="31" t="s">
-        <v>182</v>
-      </c>
-      <c r="C87" s="32">
-        <v>0</v>
-      </c>
-      <c r="D87" s="32">
-        <v>1</v>
-      </c>
-      <c r="E87" s="30" t="s">
-        <v>181</v>
-      </c>
-      <c r="H87">
-        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
-        <v>1</v>
-      </c>
-      <c r="I87">
-        <v>0</v>
-      </c>
-      <c r="J87">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>1</v>
-      </c>
-      <c r="L87" s="51" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A88" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>88</v>
-      </c>
-      <c r="H88">
-        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
-        <v>0</v>
-      </c>
-      <c r="I88">
-        <v>0</v>
-      </c>
-      <c r="J88">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A89" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>89</v>
-      </c>
-      <c r="H89">
-        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
-        <v>0</v>
-      </c>
-      <c r="I89">
-        <v>0</v>
-      </c>
-      <c r="J89">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A90" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>90</v>
-      </c>
-      <c r="H90">
-        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
-        <v>0</v>
-      </c>
-      <c r="I90">
-        <v>0</v>
-      </c>
-      <c r="J90">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A91" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>91</v>
-      </c>
-      <c r="H91">
-        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
-        <v>0</v>
-      </c>
-      <c r="I91">
-        <v>0</v>
-      </c>
-      <c r="J91">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A92" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>92</v>
-      </c>
-      <c r="H92">
-        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
-        <v>0</v>
-      </c>
-      <c r="I92">
-        <v>0</v>
-      </c>
-      <c r="J92">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A93" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>93</v>
-      </c>
-      <c r="H93">
-        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
-        <v>0</v>
-      </c>
-      <c r="I93">
-        <v>0</v>
-      </c>
-      <c r="J93">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A94" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>94</v>
-      </c>
-      <c r="H94">
-        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
-        <v>0</v>
-      </c>
-      <c r="I94">
-        <v>0</v>
-      </c>
-      <c r="J94">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A95" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>95</v>
-      </c>
-      <c r="H95">
-        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
-        <v>0</v>
-      </c>
-      <c r="I95">
-        <v>0</v>
-      </c>
-      <c r="J95">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A96" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>96</v>
-      </c>
-      <c r="H96">
-        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
-        <v>0</v>
-      </c>
-      <c r="I96">
-        <v>0</v>
-      </c>
-      <c r="J96">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A97" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>97</v>
-      </c>
-      <c r="H97">
-        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
-        <v>0</v>
-      </c>
-      <c r="I97">
-        <v>0</v>
-      </c>
-      <c r="J97">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A98" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>98</v>
-      </c>
-      <c r="H98">
-        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
-        <v>0</v>
-      </c>
-      <c r="I98">
-        <v>0</v>
-      </c>
-      <c r="J98">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A99" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>99</v>
-      </c>
-      <c r="H99">
-        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
-        <v>0</v>
-      </c>
-      <c r="I99">
-        <v>0</v>
-      </c>
-      <c r="J99">
-        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A100" s="32">
-        <f>ROW(Table2[[#This Row],[Footprint]])</f>
-        <v>100</v>
-      </c>
       <c r="H100">
         <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
         <v>0</v>
@@ -5961,7 +6362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A101" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>101</v>
@@ -5978,7 +6379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A102" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>102</v>
@@ -5995,7 +6396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A103" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>103</v>
@@ -6012,7 +6413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A104" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>104</v>
@@ -6029,7 +6430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A105" s="32">
         <f>ROW(Table2[[#This Row],[Footprint]])</f>
         <v>105</v>
@@ -6042,19 +6443,48 @@
         <v>0</v>
       </c>
       <c r="J105">
+        <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A106" s="32">
+        <f>ROW(Table2[[#This Row],[Footprint]])</f>
+        <v>106</v>
+      </c>
+      <c r="H106">
+        <f>Table2[[#This Row],[Quantity Motor]]*$N$3+Table2[[#This Row],[Quantity Asturion]]*$Q$3</f>
+        <v>0</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+      <c r="J106">
         <f>IF(Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]]&lt;=0,0,Table2[[#This Row],[Total]]-Table2[[#This Row],[Personal Stock]])</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="J1:J105">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+  <conditionalFormatting sqref="J1:J106">
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P4:P52 P2">
-    <cfRule type="colorScale" priority="32">
+    <cfRule type="colorScale" priority="33">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S2:S88">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
